--- a/data/Delivery.xlsx
+++ b/data/Delivery.xlsx
@@ -1898,7 +1898,7 @@
   <cols>
     <col min="3" max="3" width="13.28515625" style="6" customWidth="1"/>
     <col min="4" max="4" width="12.85546875" customWidth="1"/>
-    <col min="5" max="5" width="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="25.85546875" customWidth="1"/>
     <col min="12" max="16" width="12.7109375" customWidth="1"/>
   </cols>
@@ -2455,8 +2455,8 @@
         <v>95045.454545454544</v>
       </c>
       <c r="E28" s="10">
-        <f>D28+D31+D32</f>
-        <v>115045.45454545454</v>
+        <f>D28-SUM(L31:L37)*12</f>
+        <v>119583.33333333333</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.25">

--- a/data/Delivery.xlsx
+++ b/data/Delivery.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Delivery Business\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Delivery Business\DeliveryStudy\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="64">
   <si>
     <t>Average order value</t>
   </si>
@@ -214,16 +214,21 @@
   </si>
   <si>
     <t>SyTRA+Tax</t>
+  </si>
+  <si>
+    <t>Number of Orders</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="3">
+  <numFmts count="5">
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="_([$SYP]\ * #,##0_);_([$SYP]\ * \(#,##0\);_([$SYP]\ * &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="171" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -319,14 +324,15 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="5">
+  <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
@@ -360,9 +366,11 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="5">
+  <cellStyles count="6">
     <cellStyle name="Accent3" xfId="4" builtinId="37"/>
+    <cellStyle name="Comma" xfId="5" builtinId="3"/>
     <cellStyle name="Currency" xfId="2" builtinId="4"/>
     <cellStyle name="Input" xfId="3" builtinId="20"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -657,181 +665,181 @@
                   <c:v>5416.6666666666679</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>22154.545454545463</c:v>
+                  <c:v>20109.090909090919</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>38892.424242424255</c:v>
+                  <c:v>34801.515151515167</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>55630.303030303054</c:v>
+                  <c:v>49493.939393939421</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>72368.181818181853</c:v>
+                  <c:v>64186.363636363676</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>89106.060606060651</c:v>
+                  <c:v>78878.787878787931</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>105843.93939393945</c:v>
+                  <c:v>93571.212121212186</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>122581.81818181825</c:v>
+                  <c:v>108263.63636363644</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>139319.69696969705</c:v>
+                  <c:v>122956.0606060607</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>156057.57575757583</c:v>
+                  <c:v>137648.48484848495</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>172795.45454545462</c:v>
+                  <c:v>152340.9090909092</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>102995.45454545459</c:v>
+                  <c:v>80495.454545454646</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>145242.42424242431</c:v>
+                  <c:v>121351.51515151527</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>187489.39393939404</c:v>
+                  <c:v>162207.57575757589</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>229736.36363636376</c:v>
+                  <c:v>203063.63636363653</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>271983.33333333349</c:v>
+                  <c:v>243919.69696969714</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>314230.30303030321</c:v>
+                  <c:v>284775.75757575774</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>356477.27272727294</c:v>
+                  <c:v>325631.81818181835</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>398724.24242424266</c:v>
+                  <c:v>366487.87878787896</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>440971.21212121239</c:v>
+                  <c:v>407343.93939393957</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>483218.18181818211</c:v>
+                  <c:v>448200.00000000017</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>525465.15151515184</c:v>
+                  <c:v>489056.06060606078</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>567712.12121212156</c:v>
+                  <c:v>529912.12121212145</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>402421.21212121251</c:v>
+                  <c:v>363230.30303030327</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>486824.24242424284</c:v>
+                  <c:v>450251.51515151543</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>571227.27272727317</c:v>
+                  <c:v>537272.72727272753</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>655630.30303030345</c:v>
+                  <c:v>624293.93939393968</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>740033.33333333372</c:v>
+                  <c:v>711315.15151515184</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>824436.363636364</c:v>
+                  <c:v>798336.363636364</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>908839.39393939427</c:v>
+                  <c:v>885357.57575757615</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>993242.42424242455</c:v>
+                  <c:v>972378.78787878831</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>1077645.4545454548</c:v>
+                  <c:v>1059400.0000000005</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>1162048.4848484851</c:v>
+                  <c:v>1146421.2121212126</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>1246451.5151515154</c:v>
+                  <c:v>1233442.4242424248</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>1330854.5454545456</c:v>
+                  <c:v>1320463.6363636369</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>1234719.6969696973</c:v>
+                  <c:v>1226946.9696969702</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>1358304.5454545459</c:v>
+                  <c:v>1362559.0909090915</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>1481889.3939393945</c:v>
+                  <c:v>1498171.2121212129</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>1605474.2424242431</c:v>
+                  <c:v>1633783.3333333342</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>1729059.0909090918</c:v>
+                  <c:v>1769395.4545454555</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>1852643.9393939404</c:v>
+                  <c:v>1905007.5757575769</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>1976228.787878789</c:v>
+                  <c:v>2040619.6969696982</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>2099813.6363636376</c:v>
+                  <c:v>2176231.8181818193</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>2223398.4848484863</c:v>
+                  <c:v>2311843.9393939404</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>2346983.3333333349</c:v>
+                  <c:v>2447456.0606060615</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>2470568.1818181835</c:v>
+                  <c:v>2583068.1818181826</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>2594153.0303030321</c:v>
+                  <c:v>2718680.3030303037</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>2529200.0000000019</c:v>
+                  <c:v>2665754.5454545463</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>2701457.5757575775</c:v>
+                  <c:v>2854048.4848484858</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>2873715.1515151532</c:v>
+                  <c:v>3042342.4242424252</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>3045972.7272727289</c:v>
+                  <c:v>3230636.3636363647</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>3218230.3030303046</c:v>
+                  <c:v>3418930.3030303041</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>3390487.8787878803</c:v>
+                  <c:v>3607224.2424242436</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>3562745.454545456</c:v>
+                  <c:v>3795518.181818183</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>3735003.0303030317</c:v>
+                  <c:v>3983812.1212121225</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>3907260.6060606074</c:v>
+                  <c:v>4172106.0606060619</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>4079518.181818183</c:v>
+                  <c:v>4360400.0000000019</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>4251775.7575757587</c:v>
+                  <c:v>4548693.9393939413</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>4424033.3333333349</c:v>
+                  <c:v>4736987.8787878808</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>4596290.909090911</c:v>
+                  <c:v>4925281.8181818202</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2184,11 +2192,29 @@
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C16"/>
-      <c r="L16" s="9"/>
-      <c r="M16" s="9"/>
-      <c r="N16" s="9"/>
-      <c r="O16" s="9"/>
-      <c r="P16" s="9"/>
+      <c r="K16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L16" s="21">
+        <f>L7*$D$10*30</f>
+        <v>18000</v>
+      </c>
+      <c r="M16" s="21">
+        <f t="shared" ref="M16:P16" si="1">M7*$D$10*30</f>
+        <v>36000</v>
+      </c>
+      <c r="N16" s="21">
+        <f t="shared" si="1"/>
+        <v>72000</v>
+      </c>
+      <c r="O16" s="21">
+        <f t="shared" si="1"/>
+        <v>108000</v>
+      </c>
+      <c r="P16" s="21">
+        <f t="shared" si="1"/>
+        <v>144000</v>
+      </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C17"/>
@@ -2433,19 +2459,19 @@
         <v>-0.75757575757575746</v>
       </c>
       <c r="M27" s="9">
-        <f t="shared" ref="M27:P27" si="1">-$D$27/$D$19/12</f>
+        <f t="shared" ref="M27:P27" si="2">-$D$27/$D$19/12</f>
         <v>-0.75757575757575746</v>
       </c>
       <c r="N27" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-0.75757575757575746</v>
       </c>
       <c r="O27" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-0.75757575757575746</v>
       </c>
       <c r="P27" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-0.75757575757575746</v>
       </c>
     </row>
@@ -2542,19 +2568,19 @@
         <v>-25</v>
       </c>
       <c r="M33" s="9">
-        <f t="shared" ref="M33:P33" si="2">-$D$33/12</f>
+        <f t="shared" ref="M33:P33" si="3">-$D$33/12</f>
         <v>-25</v>
       </c>
       <c r="N33" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-25</v>
       </c>
       <c r="O33" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-25</v>
       </c>
       <c r="P33" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-25</v>
       </c>
     </row>
@@ -2573,19 +2599,19 @@
         <v>-16.666666666666668</v>
       </c>
       <c r="M34" s="9">
-        <f t="shared" ref="M34:P34" si="3">-$D$34/12</f>
+        <f t="shared" ref="M34:P34" si="4">-$D$34/12</f>
         <v>-16.666666666666668</v>
       </c>
       <c r="N34" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-16.666666666666668</v>
       </c>
       <c r="O34" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-16.666666666666668</v>
       </c>
       <c r="P34" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-16.666666666666668</v>
       </c>
     </row>
@@ -2608,19 +2634,19 @@
         <v>-3.1565656565656561</v>
       </c>
       <c r="M35" s="9">
-        <f t="shared" ref="M35:P35" si="4">-$D$35/12</f>
+        <f t="shared" ref="M35:P35" si="5">-$D$35/12</f>
         <v>-3.1565656565656561</v>
       </c>
       <c r="N35" s="9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-3.1565656565656561</v>
       </c>
       <c r="O35" s="9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-3.1565656565656561</v>
       </c>
       <c r="P35" s="9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-3.1565656565656561</v>
       </c>
     </row>
@@ -2716,19 +2742,19 @@
         <v>-400</v>
       </c>
       <c r="M42" s="9">
-        <f t="shared" ref="M42:P42" si="5">-$D$42*M3</f>
+        <f t="shared" ref="M42:P42" si="6">-$D$42*M3</f>
         <v>-400</v>
       </c>
       <c r="N42" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-800</v>
       </c>
       <c r="O42" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-800</v>
       </c>
       <c r="P42" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-800</v>
       </c>
     </row>
@@ -2784,23 +2810,23 @@
         <v>47</v>
       </c>
       <c r="L47" s="9">
-        <f t="shared" ref="L47:P53" si="6">-$D47*L7</f>
+        <f t="shared" ref="L47:P53" si="7">-$D47*L7</f>
         <v>-16000</v>
       </c>
       <c r="M47" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-32000</v>
       </c>
       <c r="N47" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-64000</v>
       </c>
       <c r="O47" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-96000</v>
       </c>
       <c r="P47" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-128000</v>
       </c>
     </row>
@@ -2813,23 +2839,23 @@
         <v>400</v>
       </c>
       <c r="L48" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-800</v>
       </c>
       <c r="M48" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-1600</v>
       </c>
       <c r="N48" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-3200</v>
       </c>
       <c r="O48" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-3200</v>
       </c>
       <c r="P48" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-3200</v>
       </c>
     </row>
@@ -2842,23 +2868,23 @@
         <v>400</v>
       </c>
       <c r="L49" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-800</v>
       </c>
       <c r="M49" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-800</v>
       </c>
       <c r="N49" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-2400</v>
       </c>
       <c r="O49" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-2400</v>
       </c>
       <c r="P49" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-2400</v>
       </c>
     </row>
@@ -2871,23 +2897,23 @@
         <v>400</v>
       </c>
       <c r="L50" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-800</v>
       </c>
       <c r="M50" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-800</v>
       </c>
       <c r="N50" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-2000</v>
       </c>
       <c r="O50" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-2000</v>
       </c>
       <c r="P50" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-2000</v>
       </c>
     </row>
@@ -2900,23 +2926,23 @@
         <v>600</v>
       </c>
       <c r="L51" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-600</v>
       </c>
       <c r="M51" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-600</v>
       </c>
       <c r="N51" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-600</v>
       </c>
       <c r="O51" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-600</v>
       </c>
       <c r="P51" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-600</v>
       </c>
     </row>
@@ -2929,23 +2955,23 @@
         <v>400</v>
       </c>
       <c r="L52" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-400</v>
       </c>
       <c r="M52" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-800</v>
       </c>
       <c r="N52" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-1600</v>
       </c>
       <c r="O52" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-1600</v>
       </c>
       <c r="P52" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-1600</v>
       </c>
     </row>
@@ -2958,23 +2984,23 @@
         <v>500</v>
       </c>
       <c r="L53" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-500</v>
       </c>
       <c r="M53" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-500</v>
       </c>
       <c r="N53" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-1000</v>
       </c>
       <c r="O53" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-1000</v>
       </c>
       <c r="P53" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-1000</v>
       </c>
     </row>
@@ -2983,27 +3009,27 @@
         <v>46</v>
       </c>
       <c r="D56" s="20">
-        <v>0</v>
-      </c>
-      <c r="L56" s="17">
-        <f>-$D$56*L15</f>
-        <v>0</v>
-      </c>
-      <c r="M56" s="17">
-        <f t="shared" ref="M56:P56" si="7">-$D$56*M15</f>
-        <v>0</v>
-      </c>
-      <c r="N56" s="17">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="O56" s="17">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="P56" s="17">
-        <f t="shared" si="7"/>
-        <v>0</v>
+        <v>0.1</v>
+      </c>
+      <c r="L56" s="9">
+        <f>-L16*$D$8/$B$1*$D$56</f>
+        <v>-2045.4545454545457</v>
+      </c>
+      <c r="M56" s="9">
+        <f t="shared" ref="M56:P56" si="8">-M16*$D$8/$B$1*$D$56</f>
+        <v>-4090.9090909090914</v>
+      </c>
+      <c r="N56" s="9">
+        <f t="shared" si="8"/>
+        <v>-8181.8181818181829</v>
+      </c>
+      <c r="O56" s="9">
+        <f t="shared" si="8"/>
+        <v>-12272.727272727272</v>
+      </c>
+      <c r="P56" s="9">
+        <f t="shared" si="8"/>
+        <v>-16363.636363636366</v>
       </c>
     </row>
     <row r="57" spans="1:16" x14ac:dyDescent="0.25">
@@ -3014,24 +3040,24 @@
         <v>35</v>
       </c>
       <c r="L58" s="9">
-        <f>-L5*L15</f>
+        <f>-L16*L5*$D$8/$B$1</f>
         <v>0</v>
       </c>
       <c r="M58" s="9">
-        <f>-M5*M15</f>
-        <v>-4745.4545454545469</v>
+        <f t="shared" ref="M58:P58" si="9">-M16*M5*$D$8/$B$1</f>
+        <v>-2045.4545454545455</v>
       </c>
       <c r="N58" s="9">
-        <f>-N5*N15</f>
-        <v>-18981.818181818187</v>
+        <f t="shared" si="9"/>
+        <v>-8181.818181818182</v>
       </c>
       <c r="O58" s="9">
-        <f>-O5*O15</f>
-        <v>-42709.090909090912</v>
+        <f t="shared" si="9"/>
+        <v>-18409.090909090908</v>
       </c>
       <c r="P58" s="9">
-        <f>-P5*P15</f>
-        <v>-56945.454545454551</v>
+        <f t="shared" si="9"/>
+        <v>-24545.454545454544</v>
       </c>
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.25">
@@ -3046,23 +3072,23 @@
       </c>
       <c r="L62" s="10">
         <f>SUM(L15:L60)</f>
-        <v>23108.96464646465</v>
+        <v>39063.510101010106</v>
       </c>
       <c r="M62" s="10">
         <f>SUM(M15:M60)</f>
-        <v>47318.055555555591</v>
+        <v>81927.146464646503</v>
       </c>
       <c r="N62" s="10">
         <f>SUM(N15:N60)</f>
-        <v>84624.116161616214</v>
+        <v>159242.29797979805</v>
       </c>
       <c r="O62" s="10">
         <f>SUM(O15:O60)</f>
-        <v>121205.93434343432</v>
+        <v>241233.20707070705</v>
       </c>
       <c r="P62" s="10">
         <f>SUM(P15:P60)</f>
-        <v>167278.66161616161</v>
+        <v>327315.02525252529</v>
       </c>
     </row>
     <row r="64" spans="1:16" x14ac:dyDescent="0.25">
@@ -3213,7 +3239,7 @@
       </c>
       <c r="I10" s="9">
         <f>Main!$L$58+Main!$L$56</f>
-        <v>0</v>
+        <v>-2045.4545454545457</v>
       </c>
       <c r="K10" s="9">
         <f>Main!$L$15</f>
@@ -3221,11 +3247,11 @@
       </c>
       <c r="M10" s="9">
         <f>SUM(C10:K10)</f>
-        <v>16737.878787878795</v>
+        <v>14692.424242424251</v>
       </c>
       <c r="N10" s="9">
         <f>N9+M10</f>
-        <v>22154.545454545463</v>
+        <v>20109.090909090919</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
@@ -3248,7 +3274,7 @@
       </c>
       <c r="I11" s="9">
         <f>Main!$L$58+Main!$L$56</f>
-        <v>0</v>
+        <v>-2045.4545454545457</v>
       </c>
       <c r="K11" s="9">
         <f>Main!$L$15</f>
@@ -3256,11 +3282,11 @@
       </c>
       <c r="M11" s="9">
         <f t="shared" ref="M11:M68" si="0">SUM(C11:K11)</f>
-        <v>16737.878787878795</v>
+        <v>14692.424242424251</v>
       </c>
       <c r="N11" s="9">
         <f t="shared" ref="N11:N68" si="1">N10+M11</f>
-        <v>38892.424242424255</v>
+        <v>34801.515151515167</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
@@ -3283,7 +3309,7 @@
       </c>
       <c r="I12" s="9">
         <f>Main!$L$58+Main!$L$56</f>
-        <v>0</v>
+        <v>-2045.4545454545457</v>
       </c>
       <c r="K12" s="9">
         <f>Main!$L$15</f>
@@ -3291,11 +3317,11 @@
       </c>
       <c r="M12" s="9">
         <f t="shared" si="0"/>
-        <v>16737.878787878795</v>
+        <v>14692.424242424251</v>
       </c>
       <c r="N12" s="9">
         <f t="shared" si="1"/>
-        <v>55630.303030303054</v>
+        <v>49493.939393939421</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
@@ -3318,7 +3344,7 @@
       </c>
       <c r="I13" s="9">
         <f>Main!$L$58+Main!$L$56</f>
-        <v>0</v>
+        <v>-2045.4545454545457</v>
       </c>
       <c r="K13" s="9">
         <f>Main!$L$15</f>
@@ -3326,11 +3352,11 @@
       </c>
       <c r="M13" s="9">
         <f t="shared" si="0"/>
-        <v>16737.878787878795</v>
+        <v>14692.424242424251</v>
       </c>
       <c r="N13" s="9">
         <f t="shared" si="1"/>
-        <v>72368.181818181853</v>
+        <v>64186.363636363676</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
@@ -3353,7 +3379,7 @@
       </c>
       <c r="I14" s="9">
         <f>Main!$L$58+Main!$L$56</f>
-        <v>0</v>
+        <v>-2045.4545454545457</v>
       </c>
       <c r="K14" s="9">
         <f>Main!$L$15</f>
@@ -3361,11 +3387,11 @@
       </c>
       <c r="M14" s="9">
         <f t="shared" si="0"/>
-        <v>16737.878787878795</v>
+        <v>14692.424242424251</v>
       </c>
       <c r="N14" s="9">
         <f t="shared" si="1"/>
-        <v>89106.060606060651</v>
+        <v>78878.787878787931</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
@@ -3388,7 +3414,7 @@
       </c>
       <c r="I15" s="9">
         <f>Main!$L$58+Main!$L$56</f>
-        <v>0</v>
+        <v>-2045.4545454545457</v>
       </c>
       <c r="K15" s="9">
         <f>Main!$L$15</f>
@@ -3396,11 +3422,11 @@
       </c>
       <c r="M15" s="9">
         <f t="shared" si="0"/>
-        <v>16737.878787878795</v>
+        <v>14692.424242424251</v>
       </c>
       <c r="N15" s="9">
         <f t="shared" si="1"/>
-        <v>105843.93939393945</v>
+        <v>93571.212121212186</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
@@ -3423,7 +3449,7 @@
       </c>
       <c r="I16" s="9">
         <f>Main!$L$58+Main!$L$56</f>
-        <v>0</v>
+        <v>-2045.4545454545457</v>
       </c>
       <c r="K16" s="9">
         <f>Main!$L$15</f>
@@ -3431,11 +3457,11 @@
       </c>
       <c r="M16" s="9">
         <f t="shared" si="0"/>
-        <v>16737.878787878795</v>
+        <v>14692.424242424251</v>
       </c>
       <c r="N16" s="9">
         <f t="shared" si="1"/>
-        <v>122581.81818181825</v>
+        <v>108263.63636363644</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
@@ -3458,7 +3484,7 @@
       </c>
       <c r="I17" s="9">
         <f>Main!$L$58+Main!$L$56</f>
-        <v>0</v>
+        <v>-2045.4545454545457</v>
       </c>
       <c r="K17" s="9">
         <f>Main!$L$15</f>
@@ -3466,11 +3492,11 @@
       </c>
       <c r="M17" s="9">
         <f t="shared" si="0"/>
-        <v>16737.878787878795</v>
+        <v>14692.424242424251</v>
       </c>
       <c r="N17" s="9">
         <f t="shared" si="1"/>
-        <v>139319.69696969705</v>
+        <v>122956.0606060607</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
@@ -3493,7 +3519,7 @@
       </c>
       <c r="I18" s="9">
         <f>Main!$L$58+Main!$L$56</f>
-        <v>0</v>
+        <v>-2045.4545454545457</v>
       </c>
       <c r="K18" s="9">
         <f>Main!$L$15</f>
@@ -3501,11 +3527,11 @@
       </c>
       <c r="M18" s="9">
         <f t="shared" si="0"/>
-        <v>16737.878787878795</v>
+        <v>14692.424242424251</v>
       </c>
       <c r="N18" s="9">
         <f t="shared" si="1"/>
-        <v>156057.57575757583</v>
+        <v>137648.48484848495</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
@@ -3528,7 +3554,7 @@
       </c>
       <c r="I19" s="9">
         <f>Main!$L$58+Main!$L$56</f>
-        <v>0</v>
+        <v>-2045.4545454545457</v>
       </c>
       <c r="K19" s="9">
         <f>Main!$L$15</f>
@@ -3536,11 +3562,11 @@
       </c>
       <c r="M19" s="9">
         <f t="shared" si="0"/>
-        <v>16737.878787878795</v>
+        <v>14692.424242424251</v>
       </c>
       <c r="N19" s="9">
         <f t="shared" si="1"/>
-        <v>172795.45454545462</v>
+        <v>152340.9090909092</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
@@ -3571,7 +3597,7 @@
       </c>
       <c r="I20" s="9">
         <f>Main!$L$58+Main!$L$56</f>
-        <v>0</v>
+        <v>-2045.4545454545457</v>
       </c>
       <c r="K20" s="9">
         <f>Main!$L$15</f>
@@ -3579,11 +3605,11 @@
       </c>
       <c r="M20" s="9">
         <f t="shared" si="0"/>
-        <v>-69800.000000000029</v>
+        <v>-71845.454545454559</v>
       </c>
       <c r="N20" s="9">
         <f t="shared" si="1"/>
-        <v>102995.45454545459</v>
+        <v>80495.454545454646</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
@@ -3606,7 +3632,7 @@
       </c>
       <c r="I21" s="9">
         <f>Main!$M$58+Main!$M$56</f>
-        <v>-4745.4545454545469</v>
+        <v>-6136.3636363636369</v>
       </c>
       <c r="K21" s="9">
         <f>Main!$M$15</f>
@@ -3614,11 +3640,11 @@
       </c>
       <c r="M21" s="9">
         <f t="shared" si="0"/>
-        <v>42246.969696969718</v>
+        <v>40856.060606060622</v>
       </c>
       <c r="N21" s="9">
         <f t="shared" si="1"/>
-        <v>145242.42424242431</v>
+        <v>121351.51515151527</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
@@ -3641,7 +3667,7 @@
       </c>
       <c r="I22" s="9">
         <f>Main!$M$58+Main!$M$56</f>
-        <v>-4745.4545454545469</v>
+        <v>-6136.3636363636369</v>
       </c>
       <c r="K22" s="9">
         <f>Main!$M$15</f>
@@ -3649,11 +3675,11 @@
       </c>
       <c r="M22" s="9">
         <f t="shared" si="0"/>
-        <v>42246.969696969718</v>
+        <v>40856.060606060622</v>
       </c>
       <c r="N22" s="9">
         <f t="shared" si="1"/>
-        <v>187489.39393939404</v>
+        <v>162207.57575757589</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
@@ -3676,7 +3702,7 @@
       </c>
       <c r="I23" s="9">
         <f>Main!$M$58+Main!$M$56</f>
-        <v>-4745.4545454545469</v>
+        <v>-6136.3636363636369</v>
       </c>
       <c r="K23" s="9">
         <f>Main!$M$15</f>
@@ -3684,11 +3710,11 @@
       </c>
       <c r="M23" s="9">
         <f t="shared" si="0"/>
-        <v>42246.969696969718</v>
+        <v>40856.060606060622</v>
       </c>
       <c r="N23" s="9">
         <f t="shared" si="1"/>
-        <v>229736.36363636376</v>
+        <v>203063.63636363653</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
@@ -3711,7 +3737,7 @@
       </c>
       <c r="I24" s="9">
         <f>Main!$M$58+Main!$M$56</f>
-        <v>-4745.4545454545469</v>
+        <v>-6136.3636363636369</v>
       </c>
       <c r="K24" s="9">
         <f>Main!$M$15</f>
@@ -3719,11 +3745,11 @@
       </c>
       <c r="M24" s="9">
         <f t="shared" si="0"/>
-        <v>42246.969696969718</v>
+        <v>40856.060606060622</v>
       </c>
       <c r="N24" s="9">
         <f t="shared" si="1"/>
-        <v>271983.33333333349</v>
+        <v>243919.69696969714</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
@@ -3746,7 +3772,7 @@
       </c>
       <c r="I25" s="9">
         <f>Main!$M$58+Main!$M$56</f>
-        <v>-4745.4545454545469</v>
+        <v>-6136.3636363636369</v>
       </c>
       <c r="K25" s="9">
         <f>Main!$M$15</f>
@@ -3754,11 +3780,11 @@
       </c>
       <c r="M25" s="9">
         <f t="shared" si="0"/>
-        <v>42246.969696969718</v>
+        <v>40856.060606060622</v>
       </c>
       <c r="N25" s="9">
         <f t="shared" si="1"/>
-        <v>314230.30303030321</v>
+        <v>284775.75757575774</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
@@ -3781,7 +3807,7 @@
       </c>
       <c r="I26" s="9">
         <f>Main!$M$58+Main!$M$56</f>
-        <v>-4745.4545454545469</v>
+        <v>-6136.3636363636369</v>
       </c>
       <c r="K26" s="9">
         <f>Main!$M$15</f>
@@ -3789,11 +3815,11 @@
       </c>
       <c r="M26" s="9">
         <f t="shared" si="0"/>
-        <v>42246.969696969718</v>
+        <v>40856.060606060622</v>
       </c>
       <c r="N26" s="9">
         <f t="shared" si="1"/>
-        <v>356477.27272727294</v>
+        <v>325631.81818181835</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
@@ -3816,7 +3842,7 @@
       </c>
       <c r="I27" s="9">
         <f>Main!$M$58+Main!$M$56</f>
-        <v>-4745.4545454545469</v>
+        <v>-6136.3636363636369</v>
       </c>
       <c r="K27" s="9">
         <f>Main!$M$15</f>
@@ -3824,11 +3850,11 @@
       </c>
       <c r="M27" s="9">
         <f t="shared" si="0"/>
-        <v>42246.969696969718</v>
+        <v>40856.060606060622</v>
       </c>
       <c r="N27" s="9">
         <f t="shared" si="1"/>
-        <v>398724.24242424266</v>
+        <v>366487.87878787896</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
@@ -3851,7 +3877,7 @@
       </c>
       <c r="I28" s="9">
         <f>Main!$M$58+Main!$M$56</f>
-        <v>-4745.4545454545469</v>
+        <v>-6136.3636363636369</v>
       </c>
       <c r="K28" s="9">
         <f>Main!$M$15</f>
@@ -3859,11 +3885,11 @@
       </c>
       <c r="M28" s="9">
         <f t="shared" si="0"/>
-        <v>42246.969696969718</v>
+        <v>40856.060606060622</v>
       </c>
       <c r="N28" s="9">
         <f t="shared" si="1"/>
-        <v>440971.21212121239</v>
+        <v>407343.93939393957</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
@@ -3886,7 +3912,7 @@
       </c>
       <c r="I29" s="9">
         <f>Main!$M$58+Main!$M$56</f>
-        <v>-4745.4545454545469</v>
+        <v>-6136.3636363636369</v>
       </c>
       <c r="K29" s="9">
         <f>Main!$M$15</f>
@@ -3894,11 +3920,11 @@
       </c>
       <c r="M29" s="9">
         <f t="shared" si="0"/>
-        <v>42246.969696969718</v>
+        <v>40856.060606060622</v>
       </c>
       <c r="N29" s="9">
         <f t="shared" si="1"/>
-        <v>483218.18181818211</v>
+        <v>448200.00000000017</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
@@ -3921,7 +3947,7 @@
       </c>
       <c r="I30" s="9">
         <f>Main!$M$58+Main!$M$56</f>
-        <v>-4745.4545454545469</v>
+        <v>-6136.3636363636369</v>
       </c>
       <c r="K30" s="9">
         <f>Main!$M$15</f>
@@ -3929,11 +3955,11 @@
       </c>
       <c r="M30" s="9">
         <f t="shared" si="0"/>
-        <v>42246.969696969718</v>
+        <v>40856.060606060622</v>
       </c>
       <c r="N30" s="9">
         <f t="shared" si="1"/>
-        <v>525465.15151515184</v>
+        <v>489056.06060606078</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
@@ -3956,7 +3982,7 @@
       </c>
       <c r="I31" s="9">
         <f>Main!$M$58+Main!$M$56</f>
-        <v>-4745.4545454545469</v>
+        <v>-6136.3636363636369</v>
       </c>
       <c r="K31" s="9">
         <f>Main!$M$15</f>
@@ -3964,11 +3990,11 @@
       </c>
       <c r="M31" s="9">
         <f t="shared" si="0"/>
-        <v>42246.969696969718</v>
+        <v>40856.060606060622</v>
       </c>
       <c r="N31" s="9">
         <f t="shared" si="1"/>
-        <v>567712.12121212156</v>
+        <v>529912.12121212145</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
@@ -3999,7 +4025,7 @@
       </c>
       <c r="I32" s="9">
         <f>Main!$M$58+Main!$M$56</f>
-        <v>-4745.4545454545469</v>
+        <v>-6136.3636363636369</v>
       </c>
       <c r="K32" s="9">
         <f>Main!$M$15</f>
@@ -4007,11 +4033,11 @@
       </c>
       <c r="M32" s="9">
         <f t="shared" si="0"/>
-        <v>-165290.90909090906</v>
+        <v>-166681.81818181818</v>
       </c>
       <c r="N32" s="9">
         <f t="shared" si="1"/>
-        <v>402421.21212121251</v>
+        <v>363230.30303030327</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
@@ -4034,7 +4060,7 @@
       </c>
       <c r="I33" s="9">
         <f>Main!$N$58+Main!$N$56</f>
-        <v>-18981.818181818187</v>
+        <v>-16363.636363636364</v>
       </c>
       <c r="K33" s="9">
         <f>Main!$N$15</f>
@@ -4042,11 +4068,11 @@
       </c>
       <c r="M33" s="9">
         <f t="shared" si="0"/>
-        <v>84403.030303030333</v>
+        <v>87021.212121212156</v>
       </c>
       <c r="N33" s="9">
         <f t="shared" si="1"/>
-        <v>486824.24242424284</v>
+        <v>450251.51515151543</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
@@ -4069,7 +4095,7 @@
       </c>
       <c r="I34" s="9">
         <f>Main!$N$58+Main!$N$56</f>
-        <v>-18981.818181818187</v>
+        <v>-16363.636363636364</v>
       </c>
       <c r="K34" s="9">
         <f>Main!$N$15</f>
@@ -4077,11 +4103,11 @@
       </c>
       <c r="M34" s="9">
         <f t="shared" si="0"/>
-        <v>84403.030303030333</v>
+        <v>87021.212121212156</v>
       </c>
       <c r="N34" s="9">
         <f t="shared" si="1"/>
-        <v>571227.27272727317</v>
+        <v>537272.72727272753</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
@@ -4104,7 +4130,7 @@
       </c>
       <c r="I35" s="9">
         <f>Main!$N$58+Main!$N$56</f>
-        <v>-18981.818181818187</v>
+        <v>-16363.636363636364</v>
       </c>
       <c r="K35" s="9">
         <f>Main!$N$15</f>
@@ -4112,11 +4138,11 @@
       </c>
       <c r="M35" s="9">
         <f t="shared" si="0"/>
-        <v>84403.030303030333</v>
+        <v>87021.212121212156</v>
       </c>
       <c r="N35" s="9">
         <f t="shared" si="1"/>
-        <v>655630.30303030345</v>
+        <v>624293.93939393968</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
@@ -4139,7 +4165,7 @@
       </c>
       <c r="I36" s="9">
         <f>Main!$N$58+Main!$N$56</f>
-        <v>-18981.818181818187</v>
+        <v>-16363.636363636364</v>
       </c>
       <c r="K36" s="9">
         <f>Main!$N$15</f>
@@ -4147,11 +4173,11 @@
       </c>
       <c r="M36" s="9">
         <f t="shared" si="0"/>
-        <v>84403.030303030333</v>
+        <v>87021.212121212156</v>
       </c>
       <c r="N36" s="9">
         <f t="shared" si="1"/>
-        <v>740033.33333333372</v>
+        <v>711315.15151515184</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
@@ -4174,7 +4200,7 @@
       </c>
       <c r="I37" s="9">
         <f>Main!$N$58+Main!$N$56</f>
-        <v>-18981.818181818187</v>
+        <v>-16363.636363636364</v>
       </c>
       <c r="K37" s="9">
         <f>Main!$N$15</f>
@@ -4182,11 +4208,11 @@
       </c>
       <c r="M37" s="9">
         <f t="shared" si="0"/>
-        <v>84403.030303030333</v>
+        <v>87021.212121212156</v>
       </c>
       <c r="N37" s="9">
         <f t="shared" si="1"/>
-        <v>824436.363636364</v>
+        <v>798336.363636364</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
@@ -4209,7 +4235,7 @@
       </c>
       <c r="I38" s="9">
         <f>Main!$N$58+Main!$N$56</f>
-        <v>-18981.818181818187</v>
+        <v>-16363.636363636364</v>
       </c>
       <c r="K38" s="9">
         <f>Main!$N$15</f>
@@ -4217,11 +4243,11 @@
       </c>
       <c r="M38" s="9">
         <f t="shared" si="0"/>
-        <v>84403.030303030333</v>
+        <v>87021.212121212156</v>
       </c>
       <c r="N38" s="9">
         <f t="shared" si="1"/>
-        <v>908839.39393939427</v>
+        <v>885357.57575757615</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
@@ -4244,7 +4270,7 @@
       </c>
       <c r="I39" s="9">
         <f>Main!$N$58+Main!$N$56</f>
-        <v>-18981.818181818187</v>
+        <v>-16363.636363636364</v>
       </c>
       <c r="K39" s="9">
         <f>Main!$N$15</f>
@@ -4252,11 +4278,11 @@
       </c>
       <c r="M39" s="9">
         <f t="shared" si="0"/>
-        <v>84403.030303030333</v>
+        <v>87021.212121212156</v>
       </c>
       <c r="N39" s="9">
         <f t="shared" si="1"/>
-        <v>993242.42424242455</v>
+        <v>972378.78787878831</v>
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
@@ -4279,7 +4305,7 @@
       </c>
       <c r="I40" s="9">
         <f>Main!$N$58+Main!$N$56</f>
-        <v>-18981.818181818187</v>
+        <v>-16363.636363636364</v>
       </c>
       <c r="K40" s="9">
         <f>Main!$N$15</f>
@@ -4287,11 +4313,11 @@
       </c>
       <c r="M40" s="9">
         <f t="shared" si="0"/>
-        <v>84403.030303030333</v>
+        <v>87021.212121212156</v>
       </c>
       <c r="N40" s="9">
         <f t="shared" si="1"/>
-        <v>1077645.4545454548</v>
+        <v>1059400.0000000005</v>
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
@@ -4314,7 +4340,7 @@
       </c>
       <c r="I41" s="9">
         <f>Main!$N$58+Main!$N$56</f>
-        <v>-18981.818181818187</v>
+        <v>-16363.636363636364</v>
       </c>
       <c r="K41" s="9">
         <f>Main!$N$15</f>
@@ -4322,11 +4348,11 @@
       </c>
       <c r="M41" s="9">
         <f t="shared" si="0"/>
-        <v>84403.030303030333</v>
+        <v>87021.212121212156</v>
       </c>
       <c r="N41" s="9">
         <f t="shared" si="1"/>
-        <v>1162048.4848484851</v>
+        <v>1146421.2121212126</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
@@ -4349,7 +4375,7 @@
       </c>
       <c r="I42" s="9">
         <f>Main!$N$58+Main!$N$56</f>
-        <v>-18981.818181818187</v>
+        <v>-16363.636363636364</v>
       </c>
       <c r="K42" s="9">
         <f>Main!$N$15</f>
@@ -4357,11 +4383,11 @@
       </c>
       <c r="M42" s="9">
         <f t="shared" si="0"/>
-        <v>84403.030303030333</v>
+        <v>87021.212121212156</v>
       </c>
       <c r="N42" s="9">
         <f t="shared" si="1"/>
-        <v>1246451.5151515154</v>
+        <v>1233442.4242424248</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
@@ -4384,7 +4410,7 @@
       </c>
       <c r="I43" s="9">
         <f>Main!$N$58+Main!$N$56</f>
-        <v>-18981.818181818187</v>
+        <v>-16363.636363636364</v>
       </c>
       <c r="K43" s="9">
         <f>Main!$N$15</f>
@@ -4392,11 +4418,11 @@
       </c>
       <c r="M43" s="9">
         <f t="shared" si="0"/>
-        <v>84403.030303030333</v>
+        <v>87021.212121212156</v>
       </c>
       <c r="N43" s="9">
         <f t="shared" si="1"/>
-        <v>1330854.5454545456</v>
+        <v>1320463.6363636369</v>
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.25">
@@ -4427,7 +4453,7 @@
       </c>
       <c r="I44" s="9">
         <f>Main!$N$58+Main!$N$56</f>
-        <v>-18981.818181818187</v>
+        <v>-16363.636363636364</v>
       </c>
       <c r="K44" s="9">
         <f>Main!$N$15</f>
@@ -4435,11 +4461,11 @@
       </c>
       <c r="M44" s="9">
         <f t="shared" si="0"/>
-        <v>-96134.84848484848</v>
+        <v>-93516.666666666657</v>
       </c>
       <c r="N44" s="9">
         <f t="shared" si="1"/>
-        <v>1234719.6969696973</v>
+        <v>1226946.9696969702</v>
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
@@ -4462,7 +4488,7 @@
       </c>
       <c r="I45" s="9">
         <f>Main!$O$58+Main!$O$56</f>
-        <v>-42709.090909090912</v>
+        <v>-30681.81818181818</v>
       </c>
       <c r="K45" s="9">
         <f>Main!$O$15</f>
@@ -4470,11 +4496,11 @@
       </c>
       <c r="M45" s="9">
         <f t="shared" si="0"/>
-        <v>123584.84848484851</v>
+        <v>135612.12121212124</v>
       </c>
       <c r="N45" s="9">
         <f t="shared" si="1"/>
-        <v>1358304.5454545459</v>
+        <v>1362559.0909090915</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
@@ -4497,7 +4523,7 @@
       </c>
       <c r="I46" s="9">
         <f>Main!$O$58+Main!$O$56</f>
-        <v>-42709.090909090912</v>
+        <v>-30681.81818181818</v>
       </c>
       <c r="K46" s="9">
         <f>Main!$O$15</f>
@@ -4505,11 +4531,11 @@
       </c>
       <c r="M46" s="9">
         <f t="shared" si="0"/>
-        <v>123584.84848484851</v>
+        <v>135612.12121212124</v>
       </c>
       <c r="N46" s="9">
         <f t="shared" si="1"/>
-        <v>1481889.3939393945</v>
+        <v>1498171.2121212129</v>
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.25">
@@ -4532,7 +4558,7 @@
       </c>
       <c r="I47" s="9">
         <f>Main!$O$58+Main!$O$56</f>
-        <v>-42709.090909090912</v>
+        <v>-30681.81818181818</v>
       </c>
       <c r="K47" s="9">
         <f>Main!$O$15</f>
@@ -4540,11 +4566,11 @@
       </c>
       <c r="M47" s="9">
         <f t="shared" si="0"/>
-        <v>123584.84848484851</v>
+        <v>135612.12121212124</v>
       </c>
       <c r="N47" s="9">
         <f t="shared" si="1"/>
-        <v>1605474.2424242431</v>
+        <v>1633783.3333333342</v>
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.25">
@@ -4567,7 +4593,7 @@
       </c>
       <c r="I48" s="9">
         <f>Main!$O$58+Main!$O$56</f>
-        <v>-42709.090909090912</v>
+        <v>-30681.81818181818</v>
       </c>
       <c r="K48" s="9">
         <f>Main!$O$15</f>
@@ -4575,11 +4601,11 @@
       </c>
       <c r="M48" s="9">
         <f t="shared" si="0"/>
-        <v>123584.84848484851</v>
+        <v>135612.12121212124</v>
       </c>
       <c r="N48" s="9">
         <f t="shared" si="1"/>
-        <v>1729059.0909090918</v>
+        <v>1769395.4545454555</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
@@ -4602,7 +4628,7 @@
       </c>
       <c r="I49" s="9">
         <f>Main!$O$58+Main!$O$56</f>
-        <v>-42709.090909090912</v>
+        <v>-30681.81818181818</v>
       </c>
       <c r="K49" s="9">
         <f>Main!$O$15</f>
@@ -4610,11 +4636,11 @@
       </c>
       <c r="M49" s="9">
         <f t="shared" si="0"/>
-        <v>123584.84848484851</v>
+        <v>135612.12121212124</v>
       </c>
       <c r="N49" s="9">
         <f t="shared" si="1"/>
-        <v>1852643.9393939404</v>
+        <v>1905007.5757575769</v>
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
@@ -4637,7 +4663,7 @@
       </c>
       <c r="I50" s="9">
         <f>Main!$O$58+Main!$O$56</f>
-        <v>-42709.090909090912</v>
+        <v>-30681.81818181818</v>
       </c>
       <c r="K50" s="9">
         <f>Main!$O$15</f>
@@ -4645,11 +4671,11 @@
       </c>
       <c r="M50" s="9">
         <f t="shared" si="0"/>
-        <v>123584.84848484851</v>
+        <v>135612.12121212124</v>
       </c>
       <c r="N50" s="9">
         <f t="shared" si="1"/>
-        <v>1976228.787878789</v>
+        <v>2040619.6969696982</v>
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.25">
@@ -4672,7 +4698,7 @@
       </c>
       <c r="I51" s="9">
         <f>Main!$O$58+Main!$O$56</f>
-        <v>-42709.090909090912</v>
+        <v>-30681.81818181818</v>
       </c>
       <c r="K51" s="9">
         <f>Main!$O$15</f>
@@ -4680,11 +4706,11 @@
       </c>
       <c r="M51" s="9">
         <f t="shared" si="0"/>
-        <v>123584.84848484851</v>
+        <v>135612.12121212124</v>
       </c>
       <c r="N51" s="9">
         <f t="shared" si="1"/>
-        <v>2099813.6363636376</v>
+        <v>2176231.8181818193</v>
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.25">
@@ -4707,7 +4733,7 @@
       </c>
       <c r="I52" s="9">
         <f>Main!$O$58+Main!$O$56</f>
-        <v>-42709.090909090912</v>
+        <v>-30681.81818181818</v>
       </c>
       <c r="K52" s="9">
         <f>Main!$O$15</f>
@@ -4715,11 +4741,11 @@
       </c>
       <c r="M52" s="9">
         <f t="shared" si="0"/>
-        <v>123584.84848484851</v>
+        <v>135612.12121212124</v>
       </c>
       <c r="N52" s="9">
         <f t="shared" si="1"/>
-        <v>2223398.4848484863</v>
+        <v>2311843.9393939404</v>
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.25">
@@ -4742,7 +4768,7 @@
       </c>
       <c r="I53" s="9">
         <f>Main!$O$58+Main!$O$56</f>
-        <v>-42709.090909090912</v>
+        <v>-30681.81818181818</v>
       </c>
       <c r="K53" s="9">
         <f>Main!$O$15</f>
@@ -4750,11 +4776,11 @@
       </c>
       <c r="M53" s="9">
         <f t="shared" si="0"/>
-        <v>123584.84848484851</v>
+        <v>135612.12121212124</v>
       </c>
       <c r="N53" s="9">
         <f t="shared" si="1"/>
-        <v>2346983.3333333349</v>
+        <v>2447456.0606060615</v>
       </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.25">
@@ -4777,7 +4803,7 @@
       </c>
       <c r="I54" s="9">
         <f>Main!$O$58+Main!$O$56</f>
-        <v>-42709.090909090912</v>
+        <v>-30681.81818181818</v>
       </c>
       <c r="K54" s="9">
         <f>Main!$O$15</f>
@@ -4785,11 +4811,11 @@
       </c>
       <c r="M54" s="9">
         <f t="shared" si="0"/>
-        <v>123584.84848484851</v>
+        <v>135612.12121212124</v>
       </c>
       <c r="N54" s="9">
         <f t="shared" si="1"/>
-        <v>2470568.1818181835</v>
+        <v>2583068.1818181826</v>
       </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.25">
@@ -4812,7 +4838,7 @@
       </c>
       <c r="I55" s="9">
         <f>Main!$O$58+Main!$O$56</f>
-        <v>-42709.090909090912</v>
+        <v>-30681.81818181818</v>
       </c>
       <c r="K55" s="9">
         <f>Main!$O$15</f>
@@ -4820,11 +4846,11 @@
       </c>
       <c r="M55" s="9">
         <f t="shared" si="0"/>
-        <v>123584.84848484851</v>
+        <v>135612.12121212124</v>
       </c>
       <c r="N55" s="9">
         <f t="shared" si="1"/>
-        <v>2594153.0303030321</v>
+        <v>2718680.3030303037</v>
       </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.25">
@@ -4855,7 +4881,7 @@
       </c>
       <c r="I56" s="9">
         <f>Main!$O$58+Main!$O$56</f>
-        <v>-42709.090909090912</v>
+        <v>-30681.81818181818</v>
       </c>
       <c r="K56" s="9">
         <f>Main!$O$15</f>
@@ -4863,11 +4889,11 @@
       </c>
       <c r="M56" s="9">
         <f t="shared" si="0"/>
-        <v>-64953.030303030217</v>
+        <v>-52925.757575757452</v>
       </c>
       <c r="N56" s="9">
         <f t="shared" si="1"/>
-        <v>2529200.0000000019</v>
+        <v>2665754.5454545463</v>
       </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.25">
@@ -4890,7 +4916,7 @@
       </c>
       <c r="I57" s="9">
         <f>Main!$P$58+Main!$P$56</f>
-        <v>-56945.454545454551</v>
+        <v>-40909.090909090912</v>
       </c>
       <c r="K57" s="9">
         <f>Main!$P$15</f>
@@ -4898,11 +4924,11 @@
       </c>
       <c r="M57" s="9">
         <f t="shared" si="0"/>
-        <v>172257.5757575758</v>
+        <v>188293.93939393945</v>
       </c>
       <c r="N57" s="9">
         <f t="shared" si="1"/>
-        <v>2701457.5757575775</v>
+        <v>2854048.4848484858</v>
       </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.25">
@@ -4925,7 +4951,7 @@
       </c>
       <c r="I58" s="9">
         <f>Main!$P$58+Main!$P$56</f>
-        <v>-56945.454545454551</v>
+        <v>-40909.090909090912</v>
       </c>
       <c r="K58" s="9">
         <f>Main!$P$15</f>
@@ -4933,11 +4959,11 @@
       </c>
       <c r="M58" s="9">
         <f t="shared" si="0"/>
-        <v>172257.5757575758</v>
+        <v>188293.93939393945</v>
       </c>
       <c r="N58" s="9">
         <f t="shared" si="1"/>
-        <v>2873715.1515151532</v>
+        <v>3042342.4242424252</v>
       </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.25">
@@ -4960,7 +4986,7 @@
       </c>
       <c r="I59" s="9">
         <f>Main!$P$58+Main!$P$56</f>
-        <v>-56945.454545454551</v>
+        <v>-40909.090909090912</v>
       </c>
       <c r="K59" s="9">
         <f>Main!$P$15</f>
@@ -4968,11 +4994,11 @@
       </c>
       <c r="M59" s="9">
         <f t="shared" si="0"/>
-        <v>172257.5757575758</v>
+        <v>188293.93939393945</v>
       </c>
       <c r="N59" s="9">
         <f t="shared" si="1"/>
-        <v>3045972.7272727289</v>
+        <v>3230636.3636363647</v>
       </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.25">
@@ -4995,7 +5021,7 @@
       </c>
       <c r="I60" s="9">
         <f>Main!$P$58+Main!$P$56</f>
-        <v>-56945.454545454551</v>
+        <v>-40909.090909090912</v>
       </c>
       <c r="K60" s="9">
         <f>Main!$P$15</f>
@@ -5003,11 +5029,11 @@
       </c>
       <c r="M60" s="9">
         <f t="shared" si="0"/>
-        <v>172257.5757575758</v>
+        <v>188293.93939393945</v>
       </c>
       <c r="N60" s="9">
         <f t="shared" si="1"/>
-        <v>3218230.3030303046</v>
+        <v>3418930.3030303041</v>
       </c>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.25">
@@ -5030,7 +5056,7 @@
       </c>
       <c r="I61" s="9">
         <f>Main!$P$58+Main!$P$56</f>
-        <v>-56945.454545454551</v>
+        <v>-40909.090909090912</v>
       </c>
       <c r="K61" s="9">
         <f>Main!$P$15</f>
@@ -5038,11 +5064,11 @@
       </c>
       <c r="M61" s="9">
         <f t="shared" si="0"/>
-        <v>172257.5757575758</v>
+        <v>188293.93939393945</v>
       </c>
       <c r="N61" s="9">
         <f t="shared" si="1"/>
-        <v>3390487.8787878803</v>
+        <v>3607224.2424242436</v>
       </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.25">
@@ -5065,7 +5091,7 @@
       </c>
       <c r="I62" s="9">
         <f>Main!$P$58+Main!$P$56</f>
-        <v>-56945.454545454551</v>
+        <v>-40909.090909090912</v>
       </c>
       <c r="K62" s="9">
         <f>Main!$P$15</f>
@@ -5073,11 +5099,11 @@
       </c>
       <c r="M62" s="9">
         <f t="shared" si="0"/>
-        <v>172257.5757575758</v>
+        <v>188293.93939393945</v>
       </c>
       <c r="N62" s="9">
         <f t="shared" si="1"/>
-        <v>3562745.454545456</v>
+        <v>3795518.181818183</v>
       </c>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.25">
@@ -5100,7 +5126,7 @@
       </c>
       <c r="I63" s="9">
         <f>Main!$P$58+Main!$P$56</f>
-        <v>-56945.454545454551</v>
+        <v>-40909.090909090912</v>
       </c>
       <c r="K63" s="9">
         <f>Main!$P$15</f>
@@ -5108,11 +5134,11 @@
       </c>
       <c r="M63" s="9">
         <f t="shared" si="0"/>
-        <v>172257.5757575758</v>
+        <v>188293.93939393945</v>
       </c>
       <c r="N63" s="9">
         <f t="shared" si="1"/>
-        <v>3735003.0303030317</v>
+        <v>3983812.1212121225</v>
       </c>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.25">
@@ -5135,7 +5161,7 @@
       </c>
       <c r="I64" s="9">
         <f>Main!$P$58+Main!$P$56</f>
-        <v>-56945.454545454551</v>
+        <v>-40909.090909090912</v>
       </c>
       <c r="K64" s="9">
         <f>Main!$P$15</f>
@@ -5143,11 +5169,11 @@
       </c>
       <c r="M64" s="9">
         <f t="shared" si="0"/>
-        <v>172257.5757575758</v>
+        <v>188293.93939393945</v>
       </c>
       <c r="N64" s="9">
         <f t="shared" si="1"/>
-        <v>3907260.6060606074</v>
+        <v>4172106.0606060619</v>
       </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.25">
@@ -5170,7 +5196,7 @@
       </c>
       <c r="I65" s="9">
         <f>Main!$P$58+Main!$P$56</f>
-        <v>-56945.454545454551</v>
+        <v>-40909.090909090912</v>
       </c>
       <c r="K65" s="9">
         <f>Main!$P$15</f>
@@ -5178,11 +5204,11 @@
       </c>
       <c r="M65" s="9">
         <f t="shared" si="0"/>
-        <v>172257.5757575758</v>
+        <v>188293.93939393945</v>
       </c>
       <c r="N65" s="9">
         <f t="shared" si="1"/>
-        <v>4079518.181818183</v>
+        <v>4360400.0000000019</v>
       </c>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.25">
@@ -5205,7 +5231,7 @@
       </c>
       <c r="I66" s="9">
         <f>Main!$P$58+Main!$P$56</f>
-        <v>-56945.454545454551</v>
+        <v>-40909.090909090912</v>
       </c>
       <c r="K66" s="9">
         <f>Main!$P$15</f>
@@ -5213,11 +5239,11 @@
       </c>
       <c r="M66" s="9">
         <f t="shared" si="0"/>
-        <v>172257.5757575758</v>
+        <v>188293.93939393945</v>
       </c>
       <c r="N66" s="9">
         <f t="shared" si="1"/>
-        <v>4251775.7575757587</v>
+        <v>4548693.9393939413</v>
       </c>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.25">
@@ -5240,7 +5266,7 @@
       </c>
       <c r="I67" s="9">
         <f>Main!$P$58+Main!$P$56</f>
-        <v>-56945.454545454551</v>
+        <v>-40909.090909090912</v>
       </c>
       <c r="K67" s="9">
         <f>Main!$P$15</f>
@@ -5248,11 +5274,11 @@
       </c>
       <c r="M67" s="9">
         <f t="shared" si="0"/>
-        <v>172257.5757575758</v>
+        <v>188293.93939393945</v>
       </c>
       <c r="N67" s="9">
         <f t="shared" si="1"/>
-        <v>4424033.3333333349</v>
+        <v>4736987.8787878808</v>
       </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.25">
@@ -5275,7 +5301,7 @@
       </c>
       <c r="I68" s="9">
         <f>Main!$P$58+Main!$P$56</f>
-        <v>-56945.454545454551</v>
+        <v>-40909.090909090912</v>
       </c>
       <c r="K68" s="9">
         <f>Main!$P$15</f>
@@ -5283,11 +5309,11 @@
       </c>
       <c r="M68" s="9">
         <f t="shared" si="0"/>
-        <v>172257.5757575758</v>
+        <v>188293.93939393945</v>
       </c>
       <c r="N68" s="9">
         <f t="shared" si="1"/>
-        <v>4596290.909090911</v>
+        <v>4925281.8181818202</v>
       </c>
     </row>
   </sheetData>

--- a/data/Delivery.xlsx
+++ b/data/Delivery.xlsx
@@ -2167,62 +2167,57 @@
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="K15" t="s">
+        <v>63</v>
+      </c>
+      <c r="L15" s="21">
+        <f>L7*$D$10*30</f>
+        <v>18000</v>
+      </c>
+      <c r="M15" s="21">
+        <f>M7*$D$10*30</f>
+        <v>36000</v>
+      </c>
+      <c r="N15" s="21">
+        <f>N7*$D$10*30</f>
+        <v>72000</v>
+      </c>
+      <c r="O15" s="21">
+        <f>O7*$D$10*30</f>
+        <v>108000</v>
+      </c>
+      <c r="P15" s="21">
+        <f>P7*$D$10*30</f>
+        <v>144000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C16"/>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C17"/>
+      <c r="K17" t="s">
         <v>9</v>
       </c>
-      <c r="L15" s="9">
+      <c r="L17" s="9">
         <f>L7*30*$D$10*($D$9*$D$7+$D$8/$B$1)</f>
         <v>47454.545454545463</v>
       </c>
-      <c r="M15" s="9">
+      <c r="M17" s="9">
         <f>M7*30*$D$10*($D$9*$D$7+$D$8/$B$1)</f>
         <v>94909.090909090926</v>
       </c>
-      <c r="N15" s="9">
+      <c r="N17" s="9">
         <f>N7*30*$D$10*($D$9*$D$7+$D$8/$B$1)</f>
         <v>189818.18181818185</v>
       </c>
-      <c r="O15" s="9">
+      <c r="O17" s="9">
         <f>O7*30*$D$10*($D$9*$D$7+$D$8/$B$1)</f>
         <v>284727.27272727276</v>
       </c>
-      <c r="P15" s="9">
+      <c r="P17" s="9">
         <f>P7*30*$D$10*($D$9*$D$7+$D$8/$B$1)</f>
         <v>379636.36363636371</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C16"/>
-      <c r="K16" t="s">
-        <v>63</v>
-      </c>
-      <c r="L16" s="21">
-        <f>L7*$D$10*30</f>
-        <v>18000</v>
-      </c>
-      <c r="M16" s="21">
-        <f t="shared" ref="M16:P16" si="1">M7*$D$10*30</f>
-        <v>36000</v>
-      </c>
-      <c r="N16" s="21">
-        <f t="shared" si="1"/>
-        <v>72000</v>
-      </c>
-      <c r="O16" s="21">
-        <f t="shared" si="1"/>
-        <v>108000</v>
-      </c>
-      <c r="P16" s="21">
-        <f t="shared" si="1"/>
-        <v>144000</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C17"/>
-      <c r="L17" s="9"/>
-      <c r="M17" s="9"/>
-      <c r="N17" s="9"/>
-      <c r="O17" s="9"/>
-      <c r="P17" s="9"/>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
@@ -2459,19 +2454,19 @@
         <v>-0.75757575757575746</v>
       </c>
       <c r="M27" s="9">
-        <f t="shared" ref="M27:P27" si="2">-$D$27/$D$19/12</f>
+        <f t="shared" ref="M27:P27" si="1">-$D$27/$D$19/12</f>
         <v>-0.75757575757575746</v>
       </c>
       <c r="N27" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-0.75757575757575746</v>
       </c>
       <c r="O27" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-0.75757575757575746</v>
       </c>
       <c r="P27" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-0.75757575757575746</v>
       </c>
     </row>
@@ -2568,19 +2563,19 @@
         <v>-25</v>
       </c>
       <c r="M33" s="9">
-        <f t="shared" ref="M33:P33" si="3">-$D$33/12</f>
+        <f t="shared" ref="M33:P33" si="2">-$D$33/12</f>
         <v>-25</v>
       </c>
       <c r="N33" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-25</v>
       </c>
       <c r="O33" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-25</v>
       </c>
       <c r="P33" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-25</v>
       </c>
     </row>
@@ -2599,19 +2594,19 @@
         <v>-16.666666666666668</v>
       </c>
       <c r="M34" s="9">
-        <f t="shared" ref="M34:P34" si="4">-$D$34/12</f>
+        <f t="shared" ref="M34:P34" si="3">-$D$34/12</f>
         <v>-16.666666666666668</v>
       </c>
       <c r="N34" s="9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-16.666666666666668</v>
       </c>
       <c r="O34" s="9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-16.666666666666668</v>
       </c>
       <c r="P34" s="9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-16.666666666666668</v>
       </c>
     </row>
@@ -2634,19 +2629,19 @@
         <v>-3.1565656565656561</v>
       </c>
       <c r="M35" s="9">
-        <f t="shared" ref="M35:P35" si="5">-$D$35/12</f>
+        <f t="shared" ref="M35:P35" si="4">-$D$35/12</f>
         <v>-3.1565656565656561</v>
       </c>
       <c r="N35" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>-3.1565656565656561</v>
       </c>
       <c r="O35" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>-3.1565656565656561</v>
       </c>
       <c r="P35" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>-3.1565656565656561</v>
       </c>
     </row>
@@ -2742,19 +2737,19 @@
         <v>-400</v>
       </c>
       <c r="M42" s="9">
-        <f t="shared" ref="M42:P42" si="6">-$D$42*M3</f>
+        <f t="shared" ref="M42:P42" si="5">-$D$42*M3</f>
         <v>-400</v>
       </c>
       <c r="N42" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>-800</v>
       </c>
       <c r="O42" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>-800</v>
       </c>
       <c r="P42" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>-800</v>
       </c>
     </row>
@@ -2810,23 +2805,23 @@
         <v>47</v>
       </c>
       <c r="L47" s="9">
-        <f t="shared" ref="L47:P53" si="7">-$D47*L7</f>
+        <f t="shared" ref="L47:P53" si="6">-$D47*L7</f>
         <v>-16000</v>
       </c>
       <c r="M47" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>-32000</v>
       </c>
       <c r="N47" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>-64000</v>
       </c>
       <c r="O47" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>-96000</v>
       </c>
       <c r="P47" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>-128000</v>
       </c>
     </row>
@@ -2839,23 +2834,23 @@
         <v>400</v>
       </c>
       <c r="L48" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>-800</v>
       </c>
       <c r="M48" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>-1600</v>
       </c>
       <c r="N48" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>-3200</v>
       </c>
       <c r="O48" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>-3200</v>
       </c>
       <c r="P48" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>-3200</v>
       </c>
     </row>
@@ -2868,23 +2863,23 @@
         <v>400</v>
       </c>
       <c r="L49" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>-800</v>
       </c>
       <c r="M49" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>-800</v>
       </c>
       <c r="N49" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>-2400</v>
       </c>
       <c r="O49" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>-2400</v>
       </c>
       <c r="P49" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>-2400</v>
       </c>
     </row>
@@ -2897,23 +2892,23 @@
         <v>400</v>
       </c>
       <c r="L50" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>-800</v>
       </c>
       <c r="M50" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>-800</v>
       </c>
       <c r="N50" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>-2000</v>
       </c>
       <c r="O50" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>-2000</v>
       </c>
       <c r="P50" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>-2000</v>
       </c>
     </row>
@@ -2926,23 +2921,23 @@
         <v>600</v>
       </c>
       <c r="L51" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>-600</v>
       </c>
       <c r="M51" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>-600</v>
       </c>
       <c r="N51" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>-600</v>
       </c>
       <c r="O51" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>-600</v>
       </c>
       <c r="P51" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>-600</v>
       </c>
     </row>
@@ -2955,23 +2950,23 @@
         <v>400</v>
       </c>
       <c r="L52" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>-400</v>
       </c>
       <c r="M52" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>-800</v>
       </c>
       <c r="N52" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>-1600</v>
       </c>
       <c r="O52" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>-1600</v>
       </c>
       <c r="P52" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>-1600</v>
       </c>
     </row>
@@ -2984,23 +2979,23 @@
         <v>500</v>
       </c>
       <c r="L53" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>-500</v>
       </c>
       <c r="M53" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>-500</v>
       </c>
       <c r="N53" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>-1000</v>
       </c>
       <c r="O53" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>-1000</v>
       </c>
       <c r="P53" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>-1000</v>
       </c>
     </row>
@@ -3012,23 +3007,23 @@
         <v>0.1</v>
       </c>
       <c r="L56" s="9">
-        <f>-L16*$D$8/$B$1*$D$56</f>
+        <f>-L15*$D$8/$B$1*$D$56</f>
         <v>-2045.4545454545457</v>
       </c>
       <c r="M56" s="9">
-        <f t="shared" ref="M56:P56" si="8">-M16*$D$8/$B$1*$D$56</f>
+        <f>-M15*$D$8/$B$1*$D$56</f>
         <v>-4090.9090909090914</v>
       </c>
       <c r="N56" s="9">
-        <f t="shared" si="8"/>
+        <f>-N15*$D$8/$B$1*$D$56</f>
         <v>-8181.8181818181829</v>
       </c>
       <c r="O56" s="9">
-        <f t="shared" si="8"/>
+        <f>-O15*$D$8/$B$1*$D$56</f>
         <v>-12272.727272727272</v>
       </c>
       <c r="P56" s="9">
-        <f t="shared" si="8"/>
+        <f>-P15*$D$8/$B$1*$D$56</f>
         <v>-16363.636363636366</v>
       </c>
     </row>
@@ -3040,23 +3035,23 @@
         <v>35</v>
       </c>
       <c r="L58" s="9">
-        <f>-L16*L5*$D$8/$B$1</f>
+        <f>-L15*L5*$D$8/$B$1</f>
         <v>0</v>
       </c>
       <c r="M58" s="9">
-        <f t="shared" ref="M58:P58" si="9">-M16*M5*$D$8/$B$1</f>
+        <f>-M15*M5*$D$8/$B$1</f>
         <v>-2045.4545454545455</v>
       </c>
       <c r="N58" s="9">
-        <f t="shared" si="9"/>
+        <f>-N15*N5*$D$8/$B$1</f>
         <v>-8181.818181818182</v>
       </c>
       <c r="O58" s="9">
-        <f t="shared" si="9"/>
+        <f>-O15*O5*$D$8/$B$1</f>
         <v>-18409.090909090908</v>
       </c>
       <c r="P58" s="9">
-        <f t="shared" si="9"/>
+        <f>-P15*P5*$D$8/$B$1</f>
         <v>-24545.454545454544</v>
       </c>
     </row>
@@ -3071,24 +3066,24 @@
         <v>36</v>
       </c>
       <c r="L62" s="10">
-        <f>SUM(L15:L60)</f>
-        <v>39063.510101010106</v>
+        <f>SUM(L17:L60)</f>
+        <v>21063.510101010106</v>
       </c>
       <c r="M62" s="10">
-        <f>SUM(M15:M60)</f>
-        <v>81927.146464646503</v>
+        <f>SUM(M17:M60)</f>
+        <v>45927.146464646503</v>
       </c>
       <c r="N62" s="10">
-        <f>SUM(N15:N60)</f>
-        <v>159242.29797979805</v>
+        <f>SUM(N17:N60)</f>
+        <v>87242.297979798052</v>
       </c>
       <c r="O62" s="10">
-        <f>SUM(O15:O60)</f>
-        <v>241233.20707070705</v>
+        <f>SUM(O17:O60)</f>
+        <v>133233.20707070705</v>
       </c>
       <c r="P62" s="10">
-        <f>SUM(P15:P60)</f>
-        <v>327315.02525252529</v>
+        <f>SUM(P17:P60)</f>
+        <v>183315.02525252529</v>
       </c>
     </row>
     <row r="64" spans="1:16" x14ac:dyDescent="0.25">
@@ -3242,7 +3237,7 @@
         <v>-2045.4545454545457</v>
       </c>
       <c r="K10" s="9">
-        <f>Main!$L$15</f>
+        <f>Main!$L$17</f>
         <v>47454.545454545463</v>
       </c>
       <c r="M10" s="9">
@@ -3277,7 +3272,7 @@
         <v>-2045.4545454545457</v>
       </c>
       <c r="K11" s="9">
-        <f>Main!$L$15</f>
+        <f>Main!$L$17</f>
         <v>47454.545454545463</v>
       </c>
       <c r="M11" s="9">
@@ -3312,7 +3307,7 @@
         <v>-2045.4545454545457</v>
       </c>
       <c r="K12" s="9">
-        <f>Main!$L$15</f>
+        <f>Main!$L$17</f>
         <v>47454.545454545463</v>
       </c>
       <c r="M12" s="9">
@@ -3347,7 +3342,7 @@
         <v>-2045.4545454545457</v>
       </c>
       <c r="K13" s="9">
-        <f>Main!$L$15</f>
+        <f>Main!$L$17</f>
         <v>47454.545454545463</v>
       </c>
       <c r="M13" s="9">
@@ -3382,7 +3377,7 @@
         <v>-2045.4545454545457</v>
       </c>
       <c r="K14" s="9">
-        <f>Main!$L$15</f>
+        <f>Main!$L$17</f>
         <v>47454.545454545463</v>
       </c>
       <c r="M14" s="9">
@@ -3417,7 +3412,7 @@
         <v>-2045.4545454545457</v>
       </c>
       <c r="K15" s="9">
-        <f>Main!$L$15</f>
+        <f>Main!$L$17</f>
         <v>47454.545454545463</v>
       </c>
       <c r="M15" s="9">
@@ -3452,7 +3447,7 @@
         <v>-2045.4545454545457</v>
       </c>
       <c r="K16" s="9">
-        <f>Main!$L$15</f>
+        <f>Main!$L$17</f>
         <v>47454.545454545463</v>
       </c>
       <c r="M16" s="9">
@@ -3487,7 +3482,7 @@
         <v>-2045.4545454545457</v>
       </c>
       <c r="K17" s="9">
-        <f>Main!$L$15</f>
+        <f>Main!$L$17</f>
         <v>47454.545454545463</v>
       </c>
       <c r="M17" s="9">
@@ -3522,7 +3517,7 @@
         <v>-2045.4545454545457</v>
       </c>
       <c r="K18" s="9">
-        <f>Main!$L$15</f>
+        <f>Main!$L$17</f>
         <v>47454.545454545463</v>
       </c>
       <c r="M18" s="9">
@@ -3557,7 +3552,7 @@
         <v>-2045.4545454545457</v>
       </c>
       <c r="K19" s="9">
-        <f>Main!$L$15</f>
+        <f>Main!$L$17</f>
         <v>47454.545454545463</v>
       </c>
       <c r="M19" s="9">
@@ -3600,7 +3595,7 @@
         <v>-2045.4545454545457</v>
       </c>
       <c r="K20" s="9">
-        <f>Main!$L$15</f>
+        <f>Main!$L$17</f>
         <v>47454.545454545463</v>
       </c>
       <c r="M20" s="9">
@@ -3635,7 +3630,7 @@
         <v>-6136.3636363636369</v>
       </c>
       <c r="K21" s="9">
-        <f>Main!$M$15</f>
+        <f>Main!$M$17</f>
         <v>94909.090909090926</v>
       </c>
       <c r="M21" s="9">
@@ -3670,7 +3665,7 @@
         <v>-6136.3636363636369</v>
       </c>
       <c r="K22" s="9">
-        <f>Main!$M$15</f>
+        <f>Main!$M$17</f>
         <v>94909.090909090926</v>
       </c>
       <c r="M22" s="9">
@@ -3705,7 +3700,7 @@
         <v>-6136.3636363636369</v>
       </c>
       <c r="K23" s="9">
-        <f>Main!$M$15</f>
+        <f>Main!$M$17</f>
         <v>94909.090909090926</v>
       </c>
       <c r="M23" s="9">
@@ -3740,7 +3735,7 @@
         <v>-6136.3636363636369</v>
       </c>
       <c r="K24" s="9">
-        <f>Main!$M$15</f>
+        <f>Main!$M$17</f>
         <v>94909.090909090926</v>
       </c>
       <c r="M24" s="9">
@@ -3775,7 +3770,7 @@
         <v>-6136.3636363636369</v>
       </c>
       <c r="K25" s="9">
-        <f>Main!$M$15</f>
+        <f>Main!$M$17</f>
         <v>94909.090909090926</v>
       </c>
       <c r="M25" s="9">
@@ -3810,7 +3805,7 @@
         <v>-6136.3636363636369</v>
       </c>
       <c r="K26" s="9">
-        <f>Main!$M$15</f>
+        <f>Main!$M$17</f>
         <v>94909.090909090926</v>
       </c>
       <c r="M26" s="9">
@@ -3845,7 +3840,7 @@
         <v>-6136.3636363636369</v>
       </c>
       <c r="K27" s="9">
-        <f>Main!$M$15</f>
+        <f>Main!$M$17</f>
         <v>94909.090909090926</v>
       </c>
       <c r="M27" s="9">
@@ -3880,7 +3875,7 @@
         <v>-6136.3636363636369</v>
       </c>
       <c r="K28" s="9">
-        <f>Main!$M$15</f>
+        <f>Main!$M$17</f>
         <v>94909.090909090926</v>
       </c>
       <c r="M28" s="9">
@@ -3915,7 +3910,7 @@
         <v>-6136.3636363636369</v>
       </c>
       <c r="K29" s="9">
-        <f>Main!$M$15</f>
+        <f>Main!$M$17</f>
         <v>94909.090909090926</v>
       </c>
       <c r="M29" s="9">
@@ -3950,7 +3945,7 @@
         <v>-6136.3636363636369</v>
       </c>
       <c r="K30" s="9">
-        <f>Main!$M$15</f>
+        <f>Main!$M$17</f>
         <v>94909.090909090926</v>
       </c>
       <c r="M30" s="9">
@@ -3985,7 +3980,7 @@
         <v>-6136.3636363636369</v>
       </c>
       <c r="K31" s="9">
-        <f>Main!$M$15</f>
+        <f>Main!$M$17</f>
         <v>94909.090909090926</v>
       </c>
       <c r="M31" s="9">
@@ -4028,7 +4023,7 @@
         <v>-6136.3636363636369</v>
       </c>
       <c r="K32" s="9">
-        <f>Main!$M$15</f>
+        <f>Main!$M$17</f>
         <v>94909.090909090926</v>
       </c>
       <c r="M32" s="9">
@@ -4063,7 +4058,7 @@
         <v>-16363.636363636364</v>
       </c>
       <c r="K33" s="9">
-        <f>Main!$N$15</f>
+        <f>Main!$N$17</f>
         <v>189818.18181818185</v>
       </c>
       <c r="M33" s="9">
@@ -4098,7 +4093,7 @@
         <v>-16363.636363636364</v>
       </c>
       <c r="K34" s="9">
-        <f>Main!$N$15</f>
+        <f>Main!$N$17</f>
         <v>189818.18181818185</v>
       </c>
       <c r="M34" s="9">
@@ -4133,7 +4128,7 @@
         <v>-16363.636363636364</v>
       </c>
       <c r="K35" s="9">
-        <f>Main!$N$15</f>
+        <f>Main!$N$17</f>
         <v>189818.18181818185</v>
       </c>
       <c r="M35" s="9">
@@ -4168,7 +4163,7 @@
         <v>-16363.636363636364</v>
       </c>
       <c r="K36" s="9">
-        <f>Main!$N$15</f>
+        <f>Main!$N$17</f>
         <v>189818.18181818185</v>
       </c>
       <c r="M36" s="9">
@@ -4203,7 +4198,7 @@
         <v>-16363.636363636364</v>
       </c>
       <c r="K37" s="9">
-        <f>Main!$N$15</f>
+        <f>Main!$N$17</f>
         <v>189818.18181818185</v>
       </c>
       <c r="M37" s="9">
@@ -4238,7 +4233,7 @@
         <v>-16363.636363636364</v>
       </c>
       <c r="K38" s="9">
-        <f>Main!$N$15</f>
+        <f>Main!$N$17</f>
         <v>189818.18181818185</v>
       </c>
       <c r="M38" s="9">
@@ -4273,7 +4268,7 @@
         <v>-16363.636363636364</v>
       </c>
       <c r="K39" s="9">
-        <f>Main!$N$15</f>
+        <f>Main!$N$17</f>
         <v>189818.18181818185</v>
       </c>
       <c r="M39" s="9">
@@ -4308,7 +4303,7 @@
         <v>-16363.636363636364</v>
       </c>
       <c r="K40" s="9">
-        <f>Main!$N$15</f>
+        <f>Main!$N$17</f>
         <v>189818.18181818185</v>
       </c>
       <c r="M40" s="9">
@@ -4343,7 +4338,7 @@
         <v>-16363.636363636364</v>
       </c>
       <c r="K41" s="9">
-        <f>Main!$N$15</f>
+        <f>Main!$N$17</f>
         <v>189818.18181818185</v>
       </c>
       <c r="M41" s="9">
@@ -4378,7 +4373,7 @@
         <v>-16363.636363636364</v>
       </c>
       <c r="K42" s="9">
-        <f>Main!$N$15</f>
+        <f>Main!$N$17</f>
         <v>189818.18181818185</v>
       </c>
       <c r="M42" s="9">
@@ -4413,7 +4408,7 @@
         <v>-16363.636363636364</v>
       </c>
       <c r="K43" s="9">
-        <f>Main!$N$15</f>
+        <f>Main!$N$17</f>
         <v>189818.18181818185</v>
       </c>
       <c r="M43" s="9">
@@ -4456,7 +4451,7 @@
         <v>-16363.636363636364</v>
       </c>
       <c r="K44" s="9">
-        <f>Main!$N$15</f>
+        <f>Main!$N$17</f>
         <v>189818.18181818185</v>
       </c>
       <c r="M44" s="9">
@@ -4491,7 +4486,7 @@
         <v>-30681.81818181818</v>
       </c>
       <c r="K45" s="9">
-        <f>Main!$O$15</f>
+        <f>Main!$O$17</f>
         <v>284727.27272727276</v>
       </c>
       <c r="M45" s="9">
@@ -4526,7 +4521,7 @@
         <v>-30681.81818181818</v>
       </c>
       <c r="K46" s="9">
-        <f>Main!$O$15</f>
+        <f>Main!$O$17</f>
         <v>284727.27272727276</v>
       </c>
       <c r="M46" s="9">
@@ -4561,7 +4556,7 @@
         <v>-30681.81818181818</v>
       </c>
       <c r="K47" s="9">
-        <f>Main!$O$15</f>
+        <f>Main!$O$17</f>
         <v>284727.27272727276</v>
       </c>
       <c r="M47" s="9">
@@ -4596,7 +4591,7 @@
         <v>-30681.81818181818</v>
       </c>
       <c r="K48" s="9">
-        <f>Main!$O$15</f>
+        <f>Main!$O$17</f>
         <v>284727.27272727276</v>
       </c>
       <c r="M48" s="9">
@@ -4631,7 +4626,7 @@
         <v>-30681.81818181818</v>
       </c>
       <c r="K49" s="9">
-        <f>Main!$O$15</f>
+        <f>Main!$O$17</f>
         <v>284727.27272727276</v>
       </c>
       <c r="M49" s="9">
@@ -4666,7 +4661,7 @@
         <v>-30681.81818181818</v>
       </c>
       <c r="K50" s="9">
-        <f>Main!$O$15</f>
+        <f>Main!$O$17</f>
         <v>284727.27272727276</v>
       </c>
       <c r="M50" s="9">
@@ -4701,7 +4696,7 @@
         <v>-30681.81818181818</v>
       </c>
       <c r="K51" s="9">
-        <f>Main!$O$15</f>
+        <f>Main!$O$17</f>
         <v>284727.27272727276</v>
       </c>
       <c r="M51" s="9">
@@ -4736,7 +4731,7 @@
         <v>-30681.81818181818</v>
       </c>
       <c r="K52" s="9">
-        <f>Main!$O$15</f>
+        <f>Main!$O$17</f>
         <v>284727.27272727276</v>
       </c>
       <c r="M52" s="9">
@@ -4771,7 +4766,7 @@
         <v>-30681.81818181818</v>
       </c>
       <c r="K53" s="9">
-        <f>Main!$O$15</f>
+        <f>Main!$O$17</f>
         <v>284727.27272727276</v>
       </c>
       <c r="M53" s="9">
@@ -4806,7 +4801,7 @@
         <v>-30681.81818181818</v>
       </c>
       <c r="K54" s="9">
-        <f>Main!$O$15</f>
+        <f>Main!$O$17</f>
         <v>284727.27272727276</v>
       </c>
       <c r="M54" s="9">
@@ -4841,7 +4836,7 @@
         <v>-30681.81818181818</v>
       </c>
       <c r="K55" s="9">
-        <f>Main!$O$15</f>
+        <f>Main!$O$17</f>
         <v>284727.27272727276</v>
       </c>
       <c r="M55" s="9">
@@ -4884,7 +4879,7 @@
         <v>-30681.81818181818</v>
       </c>
       <c r="K56" s="9">
-        <f>Main!$O$15</f>
+        <f>Main!$O$17</f>
         <v>284727.27272727276</v>
       </c>
       <c r="M56" s="9">
@@ -4919,7 +4914,7 @@
         <v>-40909.090909090912</v>
       </c>
       <c r="K57" s="9">
-        <f>Main!$P$15</f>
+        <f>Main!$P$17</f>
         <v>379636.36363636371</v>
       </c>
       <c r="M57" s="9">
@@ -4954,7 +4949,7 @@
         <v>-40909.090909090912</v>
       </c>
       <c r="K58" s="9">
-        <f>Main!$P$15</f>
+        <f>Main!$P$17</f>
         <v>379636.36363636371</v>
       </c>
       <c r="M58" s="9">
@@ -4989,7 +4984,7 @@
         <v>-40909.090909090912</v>
       </c>
       <c r="K59" s="9">
-        <f>Main!$P$15</f>
+        <f>Main!$P$17</f>
         <v>379636.36363636371</v>
       </c>
       <c r="M59" s="9">
@@ -5024,7 +5019,7 @@
         <v>-40909.090909090912</v>
       </c>
       <c r="K60" s="9">
-        <f>Main!$P$15</f>
+        <f>Main!$P$17</f>
         <v>379636.36363636371</v>
       </c>
       <c r="M60" s="9">
@@ -5059,7 +5054,7 @@
         <v>-40909.090909090912</v>
       </c>
       <c r="K61" s="9">
-        <f>Main!$P$15</f>
+        <f>Main!$P$17</f>
         <v>379636.36363636371</v>
       </c>
       <c r="M61" s="9">
@@ -5094,7 +5089,7 @@
         <v>-40909.090909090912</v>
       </c>
       <c r="K62" s="9">
-        <f>Main!$P$15</f>
+        <f>Main!$P$17</f>
         <v>379636.36363636371</v>
       </c>
       <c r="M62" s="9">
@@ -5129,7 +5124,7 @@
         <v>-40909.090909090912</v>
       </c>
       <c r="K63" s="9">
-        <f>Main!$P$15</f>
+        <f>Main!$P$17</f>
         <v>379636.36363636371</v>
       </c>
       <c r="M63" s="9">
@@ -5164,7 +5159,7 @@
         <v>-40909.090909090912</v>
       </c>
       <c r="K64" s="9">
-        <f>Main!$P$15</f>
+        <f>Main!$P$17</f>
         <v>379636.36363636371</v>
       </c>
       <c r="M64" s="9">
@@ -5199,7 +5194,7 @@
         <v>-40909.090909090912</v>
       </c>
       <c r="K65" s="9">
-        <f>Main!$P$15</f>
+        <f>Main!$P$17</f>
         <v>379636.36363636371</v>
       </c>
       <c r="M65" s="9">
@@ -5234,7 +5229,7 @@
         <v>-40909.090909090912</v>
       </c>
       <c r="K66" s="9">
-        <f>Main!$P$15</f>
+        <f>Main!$P$17</f>
         <v>379636.36363636371</v>
       </c>
       <c r="M66" s="9">
@@ -5269,7 +5264,7 @@
         <v>-40909.090909090912</v>
       </c>
       <c r="K67" s="9">
-        <f>Main!$P$15</f>
+        <f>Main!$P$17</f>
         <v>379636.36363636371</v>
       </c>
       <c r="M67" s="9">
@@ -5304,7 +5299,7 @@
         <v>-40909.090909090912</v>
       </c>
       <c r="K68" s="9">
-        <f>Main!$P$15</f>
+        <f>Main!$P$17</f>
         <v>379636.36363636371</v>
       </c>
       <c r="M68" s="9">

--- a/data/Delivery.xlsx
+++ b/data/Delivery.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Delivery Business\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Delivery Business\DeliveryStudy\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="64">
   <si>
     <t>Average order value</t>
   </si>
@@ -214,16 +214,21 @@
   </si>
   <si>
     <t>SyTRA+Tax</t>
+  </si>
+  <si>
+    <t>Number of Orders</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="3">
+  <numFmts count="5">
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="_([$SYP]\ * #,##0_);_([$SYP]\ * \(#,##0\);_([$SYP]\ * &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="171" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -319,14 +324,15 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="5">
+  <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
@@ -360,9 +366,11 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="5">
+  <cellStyles count="6">
     <cellStyle name="Accent3" xfId="4" builtinId="37"/>
+    <cellStyle name="Comma" xfId="5" builtinId="3"/>
     <cellStyle name="Currency" xfId="2" builtinId="4"/>
     <cellStyle name="Input" xfId="3" builtinId="20"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -657,181 +665,181 @@
                   <c:v>5416.6666666666679</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>22154.545454545463</c:v>
+                  <c:v>20109.090909090919</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>38892.424242424255</c:v>
+                  <c:v>34801.515151515167</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>55630.303030303054</c:v>
+                  <c:v>49493.939393939421</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>72368.181818181853</c:v>
+                  <c:v>64186.363636363676</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>89106.060606060651</c:v>
+                  <c:v>78878.787878787931</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>105843.93939393945</c:v>
+                  <c:v>93571.212121212186</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>122581.81818181825</c:v>
+                  <c:v>108263.63636363644</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>139319.69696969705</c:v>
+                  <c:v>122956.0606060607</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>156057.57575757583</c:v>
+                  <c:v>137648.48484848495</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>172795.45454545462</c:v>
+                  <c:v>152340.9090909092</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>102995.45454545459</c:v>
+                  <c:v>80495.454545454646</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>145242.42424242431</c:v>
+                  <c:v>121351.51515151527</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>187489.39393939404</c:v>
+                  <c:v>162207.57575757589</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>229736.36363636376</c:v>
+                  <c:v>203063.63636363653</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>271983.33333333349</c:v>
+                  <c:v>243919.69696969714</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>314230.30303030321</c:v>
+                  <c:v>284775.75757575774</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>356477.27272727294</c:v>
+                  <c:v>325631.81818181835</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>398724.24242424266</c:v>
+                  <c:v>366487.87878787896</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>440971.21212121239</c:v>
+                  <c:v>407343.93939393957</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>483218.18181818211</c:v>
+                  <c:v>448200.00000000017</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>525465.15151515184</c:v>
+                  <c:v>489056.06060606078</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>567712.12121212156</c:v>
+                  <c:v>529912.12121212145</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>402421.21212121251</c:v>
+                  <c:v>363230.30303030327</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>486824.24242424284</c:v>
+                  <c:v>450251.51515151543</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>571227.27272727317</c:v>
+                  <c:v>537272.72727272753</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>655630.30303030345</c:v>
+                  <c:v>624293.93939393968</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>740033.33333333372</c:v>
+                  <c:v>711315.15151515184</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>824436.363636364</c:v>
+                  <c:v>798336.363636364</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>908839.39393939427</c:v>
+                  <c:v>885357.57575757615</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>993242.42424242455</c:v>
+                  <c:v>972378.78787878831</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>1077645.4545454548</c:v>
+                  <c:v>1059400.0000000005</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>1162048.4848484851</c:v>
+                  <c:v>1146421.2121212126</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>1246451.5151515154</c:v>
+                  <c:v>1233442.4242424248</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>1330854.5454545456</c:v>
+                  <c:v>1320463.6363636369</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>1234719.6969696973</c:v>
+                  <c:v>1226946.9696969702</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>1358304.5454545459</c:v>
+                  <c:v>1362559.0909090915</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>1481889.3939393945</c:v>
+                  <c:v>1498171.2121212129</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>1605474.2424242431</c:v>
+                  <c:v>1633783.3333333342</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>1729059.0909090918</c:v>
+                  <c:v>1769395.4545454555</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>1852643.9393939404</c:v>
+                  <c:v>1905007.5757575769</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>1976228.787878789</c:v>
+                  <c:v>2040619.6969696982</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>2099813.6363636376</c:v>
+                  <c:v>2176231.8181818193</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>2223398.4848484863</c:v>
+                  <c:v>2311843.9393939404</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>2346983.3333333349</c:v>
+                  <c:v>2447456.0606060615</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>2470568.1818181835</c:v>
+                  <c:v>2583068.1818181826</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>2594153.0303030321</c:v>
+                  <c:v>2718680.3030303037</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>2529200.0000000019</c:v>
+                  <c:v>2665754.5454545463</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>2701457.5757575775</c:v>
+                  <c:v>2854048.4848484858</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>2873715.1515151532</c:v>
+                  <c:v>3042342.4242424252</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>3045972.7272727289</c:v>
+                  <c:v>3230636.3636363647</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>3218230.3030303046</c:v>
+                  <c:v>3418930.3030303041</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>3390487.8787878803</c:v>
+                  <c:v>3607224.2424242436</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>3562745.454545456</c:v>
+                  <c:v>3795518.181818183</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>3735003.0303030317</c:v>
+                  <c:v>3983812.1212121225</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>3907260.6060606074</c:v>
+                  <c:v>4172106.0606060619</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>4079518.181818183</c:v>
+                  <c:v>4360400.0000000019</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>4251775.7575757587</c:v>
+                  <c:v>4548693.9393939413</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>4424033.3333333349</c:v>
+                  <c:v>4736987.8787878808</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>4596290.909090911</c:v>
+                  <c:v>4925281.8181818202</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2159,44 +2167,57 @@
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="K15" t="s">
+        <v>63</v>
+      </c>
+      <c r="L15" s="21">
+        <f>L7*$D$10*30</f>
+        <v>18000</v>
+      </c>
+      <c r="M15" s="21">
+        <f>M7*$D$10*30</f>
+        <v>36000</v>
+      </c>
+      <c r="N15" s="21">
+        <f>N7*$D$10*30</f>
+        <v>72000</v>
+      </c>
+      <c r="O15" s="21">
+        <f>O7*$D$10*30</f>
+        <v>108000</v>
+      </c>
+      <c r="P15" s="21">
+        <f>P7*$D$10*30</f>
+        <v>144000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C16"/>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C17"/>
+      <c r="K17" t="s">
         <v>9</v>
       </c>
-      <c r="L15" s="9">
+      <c r="L17" s="9">
         <f>L7*30*$D$10*($D$9*$D$7+$D$8/$B$1)</f>
         <v>47454.545454545463</v>
       </c>
-      <c r="M15" s="9">
+      <c r="M17" s="9">
         <f>M7*30*$D$10*($D$9*$D$7+$D$8/$B$1)</f>
         <v>94909.090909090926</v>
       </c>
-      <c r="N15" s="9">
+      <c r="N17" s="9">
         <f>N7*30*$D$10*($D$9*$D$7+$D$8/$B$1)</f>
         <v>189818.18181818185</v>
       </c>
-      <c r="O15" s="9">
+      <c r="O17" s="9">
         <f>O7*30*$D$10*($D$9*$D$7+$D$8/$B$1)</f>
         <v>284727.27272727276</v>
       </c>
-      <c r="P15" s="9">
+      <c r="P17" s="9">
         <f>P7*30*$D$10*($D$9*$D$7+$D$8/$B$1)</f>
         <v>379636.36363636371</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C16"/>
-      <c r="L16" s="9"/>
-      <c r="M16" s="9"/>
-      <c r="N16" s="9"/>
-      <c r="O16" s="9"/>
-      <c r="P16" s="9"/>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C17"/>
-      <c r="L17" s="9"/>
-      <c r="M17" s="9"/>
-      <c r="N17" s="9"/>
-      <c r="O17" s="9"/>
-      <c r="P17" s="9"/>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
@@ -2983,27 +3004,27 @@
         <v>46</v>
       </c>
       <c r="D56" s="20">
-        <v>0</v>
-      </c>
-      <c r="L56" s="17">
-        <f>-$D$56*L15</f>
-        <v>0</v>
-      </c>
-      <c r="M56" s="17">
-        <f t="shared" ref="M56:P56" si="7">-$D$56*M15</f>
-        <v>0</v>
-      </c>
-      <c r="N56" s="17">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="O56" s="17">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="P56" s="17">
-        <f t="shared" si="7"/>
-        <v>0</v>
+        <v>0.1</v>
+      </c>
+      <c r="L56" s="9">
+        <f>-L15*$D$8/$B$1*$D$56</f>
+        <v>-2045.4545454545457</v>
+      </c>
+      <c r="M56" s="9">
+        <f>-M15*$D$8/$B$1*$D$56</f>
+        <v>-4090.9090909090914</v>
+      </c>
+      <c r="N56" s="9">
+        <f>-N15*$D$8/$B$1*$D$56</f>
+        <v>-8181.8181818181829</v>
+      </c>
+      <c r="O56" s="9">
+        <f>-O15*$D$8/$B$1*$D$56</f>
+        <v>-12272.727272727272</v>
+      </c>
+      <c r="P56" s="9">
+        <f>-P15*$D$8/$B$1*$D$56</f>
+        <v>-16363.636363636366</v>
       </c>
     </row>
     <row r="57" spans="1:16" x14ac:dyDescent="0.25">
@@ -3014,24 +3035,24 @@
         <v>35</v>
       </c>
       <c r="L58" s="9">
-        <f>-L5*L15</f>
+        <f>-L15*L5*$D$8/$B$1</f>
         <v>0</v>
       </c>
       <c r="M58" s="9">
-        <f>-M5*M15</f>
-        <v>-4745.4545454545469</v>
+        <f>-M15*M5*$D$8/$B$1</f>
+        <v>-2045.4545454545455</v>
       </c>
       <c r="N58" s="9">
-        <f>-N5*N15</f>
-        <v>-18981.818181818187</v>
+        <f>-N15*N5*$D$8/$B$1</f>
+        <v>-8181.818181818182</v>
       </c>
       <c r="O58" s="9">
-        <f>-O5*O15</f>
-        <v>-42709.090909090912</v>
+        <f>-O15*O5*$D$8/$B$1</f>
+        <v>-18409.090909090908</v>
       </c>
       <c r="P58" s="9">
-        <f>-P5*P15</f>
-        <v>-56945.454545454551</v>
+        <f>-P15*P5*$D$8/$B$1</f>
+        <v>-24545.454545454544</v>
       </c>
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.25">
@@ -3045,24 +3066,24 @@
         <v>36</v>
       </c>
       <c r="L62" s="10">
-        <f>SUM(L15:L60)</f>
-        <v>23108.96464646465</v>
+        <f>SUM(L17:L60)</f>
+        <v>21063.510101010106</v>
       </c>
       <c r="M62" s="10">
-        <f>SUM(M15:M60)</f>
-        <v>47318.055555555591</v>
+        <f>SUM(M17:M60)</f>
+        <v>45927.146464646503</v>
       </c>
       <c r="N62" s="10">
-        <f>SUM(N15:N60)</f>
-        <v>84624.116161616214</v>
+        <f>SUM(N17:N60)</f>
+        <v>87242.297979798052</v>
       </c>
       <c r="O62" s="10">
-        <f>SUM(O15:O60)</f>
-        <v>121205.93434343432</v>
+        <f>SUM(O17:O60)</f>
+        <v>133233.20707070705</v>
       </c>
       <c r="P62" s="10">
-        <f>SUM(P15:P60)</f>
-        <v>167278.66161616161</v>
+        <f>SUM(P17:P60)</f>
+        <v>183315.02525252529</v>
       </c>
     </row>
     <row r="64" spans="1:16" x14ac:dyDescent="0.25">
@@ -3213,19 +3234,19 @@
       </c>
       <c r="I10" s="9">
         <f>Main!$L$58+Main!$L$56</f>
-        <v>0</v>
+        <v>-2045.4545454545457</v>
       </c>
       <c r="K10" s="9">
-        <f>Main!$L$15</f>
+        <f>Main!$L$17</f>
         <v>47454.545454545463</v>
       </c>
       <c r="M10" s="9">
         <f>SUM(C10:K10)</f>
-        <v>16737.878787878795</v>
+        <v>14692.424242424251</v>
       </c>
       <c r="N10" s="9">
         <f>N9+M10</f>
-        <v>22154.545454545463</v>
+        <v>20109.090909090919</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
@@ -3248,19 +3269,19 @@
       </c>
       <c r="I11" s="9">
         <f>Main!$L$58+Main!$L$56</f>
-        <v>0</v>
+        <v>-2045.4545454545457</v>
       </c>
       <c r="K11" s="9">
-        <f>Main!$L$15</f>
+        <f>Main!$L$17</f>
         <v>47454.545454545463</v>
       </c>
       <c r="M11" s="9">
         <f t="shared" ref="M11:M68" si="0">SUM(C11:K11)</f>
-        <v>16737.878787878795</v>
+        <v>14692.424242424251</v>
       </c>
       <c r="N11" s="9">
         <f t="shared" ref="N11:N68" si="1">N10+M11</f>
-        <v>38892.424242424255</v>
+        <v>34801.515151515167</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
@@ -3283,19 +3304,19 @@
       </c>
       <c r="I12" s="9">
         <f>Main!$L$58+Main!$L$56</f>
-        <v>0</v>
+        <v>-2045.4545454545457</v>
       </c>
       <c r="K12" s="9">
-        <f>Main!$L$15</f>
+        <f>Main!$L$17</f>
         <v>47454.545454545463</v>
       </c>
       <c r="M12" s="9">
         <f t="shared" si="0"/>
-        <v>16737.878787878795</v>
+        <v>14692.424242424251</v>
       </c>
       <c r="N12" s="9">
         <f t="shared" si="1"/>
-        <v>55630.303030303054</v>
+        <v>49493.939393939421</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
@@ -3318,19 +3339,19 @@
       </c>
       <c r="I13" s="9">
         <f>Main!$L$58+Main!$L$56</f>
-        <v>0</v>
+        <v>-2045.4545454545457</v>
       </c>
       <c r="K13" s="9">
-        <f>Main!$L$15</f>
+        <f>Main!$L$17</f>
         <v>47454.545454545463</v>
       </c>
       <c r="M13" s="9">
         <f t="shared" si="0"/>
-        <v>16737.878787878795</v>
+        <v>14692.424242424251</v>
       </c>
       <c r="N13" s="9">
         <f t="shared" si="1"/>
-        <v>72368.181818181853</v>
+        <v>64186.363636363676</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
@@ -3353,19 +3374,19 @@
       </c>
       <c r="I14" s="9">
         <f>Main!$L$58+Main!$L$56</f>
-        <v>0</v>
+        <v>-2045.4545454545457</v>
       </c>
       <c r="K14" s="9">
-        <f>Main!$L$15</f>
+        <f>Main!$L$17</f>
         <v>47454.545454545463</v>
       </c>
       <c r="M14" s="9">
         <f t="shared" si="0"/>
-        <v>16737.878787878795</v>
+        <v>14692.424242424251</v>
       </c>
       <c r="N14" s="9">
         <f t="shared" si="1"/>
-        <v>89106.060606060651</v>
+        <v>78878.787878787931</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
@@ -3388,19 +3409,19 @@
       </c>
       <c r="I15" s="9">
         <f>Main!$L$58+Main!$L$56</f>
-        <v>0</v>
+        <v>-2045.4545454545457</v>
       </c>
       <c r="K15" s="9">
-        <f>Main!$L$15</f>
+        <f>Main!$L$17</f>
         <v>47454.545454545463</v>
       </c>
       <c r="M15" s="9">
         <f t="shared" si="0"/>
-        <v>16737.878787878795</v>
+        <v>14692.424242424251</v>
       </c>
       <c r="N15" s="9">
         <f t="shared" si="1"/>
-        <v>105843.93939393945</v>
+        <v>93571.212121212186</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
@@ -3423,19 +3444,19 @@
       </c>
       <c r="I16" s="9">
         <f>Main!$L$58+Main!$L$56</f>
-        <v>0</v>
+        <v>-2045.4545454545457</v>
       </c>
       <c r="K16" s="9">
-        <f>Main!$L$15</f>
+        <f>Main!$L$17</f>
         <v>47454.545454545463</v>
       </c>
       <c r="M16" s="9">
         <f t="shared" si="0"/>
-        <v>16737.878787878795</v>
+        <v>14692.424242424251</v>
       </c>
       <c r="N16" s="9">
         <f t="shared" si="1"/>
-        <v>122581.81818181825</v>
+        <v>108263.63636363644</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
@@ -3458,19 +3479,19 @@
       </c>
       <c r="I17" s="9">
         <f>Main!$L$58+Main!$L$56</f>
-        <v>0</v>
+        <v>-2045.4545454545457</v>
       </c>
       <c r="K17" s="9">
-        <f>Main!$L$15</f>
+        <f>Main!$L$17</f>
         <v>47454.545454545463</v>
       </c>
       <c r="M17" s="9">
         <f t="shared" si="0"/>
-        <v>16737.878787878795</v>
+        <v>14692.424242424251</v>
       </c>
       <c r="N17" s="9">
         <f t="shared" si="1"/>
-        <v>139319.69696969705</v>
+        <v>122956.0606060607</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
@@ -3493,19 +3514,19 @@
       </c>
       <c r="I18" s="9">
         <f>Main!$L$58+Main!$L$56</f>
-        <v>0</v>
+        <v>-2045.4545454545457</v>
       </c>
       <c r="K18" s="9">
-        <f>Main!$L$15</f>
+        <f>Main!$L$17</f>
         <v>47454.545454545463</v>
       </c>
       <c r="M18" s="9">
         <f t="shared" si="0"/>
-        <v>16737.878787878795</v>
+        <v>14692.424242424251</v>
       </c>
       <c r="N18" s="9">
         <f t="shared" si="1"/>
-        <v>156057.57575757583</v>
+        <v>137648.48484848495</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
@@ -3528,19 +3549,19 @@
       </c>
       <c r="I19" s="9">
         <f>Main!$L$58+Main!$L$56</f>
-        <v>0</v>
+        <v>-2045.4545454545457</v>
       </c>
       <c r="K19" s="9">
-        <f>Main!$L$15</f>
+        <f>Main!$L$17</f>
         <v>47454.545454545463</v>
       </c>
       <c r="M19" s="9">
         <f t="shared" si="0"/>
-        <v>16737.878787878795</v>
+        <v>14692.424242424251</v>
       </c>
       <c r="N19" s="9">
         <f t="shared" si="1"/>
-        <v>172795.45454545462</v>
+        <v>152340.9090909092</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
@@ -3571,19 +3592,19 @@
       </c>
       <c r="I20" s="9">
         <f>Main!$L$58+Main!$L$56</f>
-        <v>0</v>
+        <v>-2045.4545454545457</v>
       </c>
       <c r="K20" s="9">
-        <f>Main!$L$15</f>
+        <f>Main!$L$17</f>
         <v>47454.545454545463</v>
       </c>
       <c r="M20" s="9">
         <f t="shared" si="0"/>
-        <v>-69800.000000000029</v>
+        <v>-71845.454545454559</v>
       </c>
       <c r="N20" s="9">
         <f t="shared" si="1"/>
-        <v>102995.45454545459</v>
+        <v>80495.454545454646</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
@@ -3606,19 +3627,19 @@
       </c>
       <c r="I21" s="9">
         <f>Main!$M$58+Main!$M$56</f>
-        <v>-4745.4545454545469</v>
+        <v>-6136.3636363636369</v>
       </c>
       <c r="K21" s="9">
-        <f>Main!$M$15</f>
+        <f>Main!$M$17</f>
         <v>94909.090909090926</v>
       </c>
       <c r="M21" s="9">
         <f t="shared" si="0"/>
-        <v>42246.969696969718</v>
+        <v>40856.060606060622</v>
       </c>
       <c r="N21" s="9">
         <f t="shared" si="1"/>
-        <v>145242.42424242431</v>
+        <v>121351.51515151527</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
@@ -3641,19 +3662,19 @@
       </c>
       <c r="I22" s="9">
         <f>Main!$M$58+Main!$M$56</f>
-        <v>-4745.4545454545469</v>
+        <v>-6136.3636363636369</v>
       </c>
       <c r="K22" s="9">
-        <f>Main!$M$15</f>
+        <f>Main!$M$17</f>
         <v>94909.090909090926</v>
       </c>
       <c r="M22" s="9">
         <f t="shared" si="0"/>
-        <v>42246.969696969718</v>
+        <v>40856.060606060622</v>
       </c>
       <c r="N22" s="9">
         <f t="shared" si="1"/>
-        <v>187489.39393939404</v>
+        <v>162207.57575757589</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
@@ -3676,19 +3697,19 @@
       </c>
       <c r="I23" s="9">
         <f>Main!$M$58+Main!$M$56</f>
-        <v>-4745.4545454545469</v>
+        <v>-6136.3636363636369</v>
       </c>
       <c r="K23" s="9">
-        <f>Main!$M$15</f>
+        <f>Main!$M$17</f>
         <v>94909.090909090926</v>
       </c>
       <c r="M23" s="9">
         <f t="shared" si="0"/>
-        <v>42246.969696969718</v>
+        <v>40856.060606060622</v>
       </c>
       <c r="N23" s="9">
         <f t="shared" si="1"/>
-        <v>229736.36363636376</v>
+        <v>203063.63636363653</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
@@ -3711,19 +3732,19 @@
       </c>
       <c r="I24" s="9">
         <f>Main!$M$58+Main!$M$56</f>
-        <v>-4745.4545454545469</v>
+        <v>-6136.3636363636369</v>
       </c>
       <c r="K24" s="9">
-        <f>Main!$M$15</f>
+        <f>Main!$M$17</f>
         <v>94909.090909090926</v>
       </c>
       <c r="M24" s="9">
         <f t="shared" si="0"/>
-        <v>42246.969696969718</v>
+        <v>40856.060606060622</v>
       </c>
       <c r="N24" s="9">
         <f t="shared" si="1"/>
-        <v>271983.33333333349</v>
+        <v>243919.69696969714</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
@@ -3746,19 +3767,19 @@
       </c>
       <c r="I25" s="9">
         <f>Main!$M$58+Main!$M$56</f>
-        <v>-4745.4545454545469</v>
+        <v>-6136.3636363636369</v>
       </c>
       <c r="K25" s="9">
-        <f>Main!$M$15</f>
+        <f>Main!$M$17</f>
         <v>94909.090909090926</v>
       </c>
       <c r="M25" s="9">
         <f t="shared" si="0"/>
-        <v>42246.969696969718</v>
+        <v>40856.060606060622</v>
       </c>
       <c r="N25" s="9">
         <f t="shared" si="1"/>
-        <v>314230.30303030321</v>
+        <v>284775.75757575774</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
@@ -3781,19 +3802,19 @@
       </c>
       <c r="I26" s="9">
         <f>Main!$M$58+Main!$M$56</f>
-        <v>-4745.4545454545469</v>
+        <v>-6136.3636363636369</v>
       </c>
       <c r="K26" s="9">
-        <f>Main!$M$15</f>
+        <f>Main!$M$17</f>
         <v>94909.090909090926</v>
       </c>
       <c r="M26" s="9">
         <f t="shared" si="0"/>
-        <v>42246.969696969718</v>
+        <v>40856.060606060622</v>
       </c>
       <c r="N26" s="9">
         <f t="shared" si="1"/>
-        <v>356477.27272727294</v>
+        <v>325631.81818181835</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
@@ -3816,19 +3837,19 @@
       </c>
       <c r="I27" s="9">
         <f>Main!$M$58+Main!$M$56</f>
-        <v>-4745.4545454545469</v>
+        <v>-6136.3636363636369</v>
       </c>
       <c r="K27" s="9">
-        <f>Main!$M$15</f>
+        <f>Main!$M$17</f>
         <v>94909.090909090926</v>
       </c>
       <c r="M27" s="9">
         <f t="shared" si="0"/>
-        <v>42246.969696969718</v>
+        <v>40856.060606060622</v>
       </c>
       <c r="N27" s="9">
         <f t="shared" si="1"/>
-        <v>398724.24242424266</v>
+        <v>366487.87878787896</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
@@ -3851,19 +3872,19 @@
       </c>
       <c r="I28" s="9">
         <f>Main!$M$58+Main!$M$56</f>
-        <v>-4745.4545454545469</v>
+        <v>-6136.3636363636369</v>
       </c>
       <c r="K28" s="9">
-        <f>Main!$M$15</f>
+        <f>Main!$M$17</f>
         <v>94909.090909090926</v>
       </c>
       <c r="M28" s="9">
         <f t="shared" si="0"/>
-        <v>42246.969696969718</v>
+        <v>40856.060606060622</v>
       </c>
       <c r="N28" s="9">
         <f t="shared" si="1"/>
-        <v>440971.21212121239</v>
+        <v>407343.93939393957</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
@@ -3886,19 +3907,19 @@
       </c>
       <c r="I29" s="9">
         <f>Main!$M$58+Main!$M$56</f>
-        <v>-4745.4545454545469</v>
+        <v>-6136.3636363636369</v>
       </c>
       <c r="K29" s="9">
-        <f>Main!$M$15</f>
+        <f>Main!$M$17</f>
         <v>94909.090909090926</v>
       </c>
       <c r="M29" s="9">
         <f t="shared" si="0"/>
-        <v>42246.969696969718</v>
+        <v>40856.060606060622</v>
       </c>
       <c r="N29" s="9">
         <f t="shared" si="1"/>
-        <v>483218.18181818211</v>
+        <v>448200.00000000017</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
@@ -3921,19 +3942,19 @@
       </c>
       <c r="I30" s="9">
         <f>Main!$M$58+Main!$M$56</f>
-        <v>-4745.4545454545469</v>
+        <v>-6136.3636363636369</v>
       </c>
       <c r="K30" s="9">
-        <f>Main!$M$15</f>
+        <f>Main!$M$17</f>
         <v>94909.090909090926</v>
       </c>
       <c r="M30" s="9">
         <f t="shared" si="0"/>
-        <v>42246.969696969718</v>
+        <v>40856.060606060622</v>
       </c>
       <c r="N30" s="9">
         <f t="shared" si="1"/>
-        <v>525465.15151515184</v>
+        <v>489056.06060606078</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
@@ -3956,19 +3977,19 @@
       </c>
       <c r="I31" s="9">
         <f>Main!$M$58+Main!$M$56</f>
-        <v>-4745.4545454545469</v>
+        <v>-6136.3636363636369</v>
       </c>
       <c r="K31" s="9">
-        <f>Main!$M$15</f>
+        <f>Main!$M$17</f>
         <v>94909.090909090926</v>
       </c>
       <c r="M31" s="9">
         <f t="shared" si="0"/>
-        <v>42246.969696969718</v>
+        <v>40856.060606060622</v>
       </c>
       <c r="N31" s="9">
         <f t="shared" si="1"/>
-        <v>567712.12121212156</v>
+        <v>529912.12121212145</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
@@ -3999,19 +4020,19 @@
       </c>
       <c r="I32" s="9">
         <f>Main!$M$58+Main!$M$56</f>
-        <v>-4745.4545454545469</v>
+        <v>-6136.3636363636369</v>
       </c>
       <c r="K32" s="9">
-        <f>Main!$M$15</f>
+        <f>Main!$M$17</f>
         <v>94909.090909090926</v>
       </c>
       <c r="M32" s="9">
         <f t="shared" si="0"/>
-        <v>-165290.90909090906</v>
+        <v>-166681.81818181818</v>
       </c>
       <c r="N32" s="9">
         <f t="shared" si="1"/>
-        <v>402421.21212121251</v>
+        <v>363230.30303030327</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
@@ -4034,19 +4055,19 @@
       </c>
       <c r="I33" s="9">
         <f>Main!$N$58+Main!$N$56</f>
-        <v>-18981.818181818187</v>
+        <v>-16363.636363636364</v>
       </c>
       <c r="K33" s="9">
-        <f>Main!$N$15</f>
+        <f>Main!$N$17</f>
         <v>189818.18181818185</v>
       </c>
       <c r="M33" s="9">
         <f t="shared" si="0"/>
-        <v>84403.030303030333</v>
+        <v>87021.212121212156</v>
       </c>
       <c r="N33" s="9">
         <f t="shared" si="1"/>
-        <v>486824.24242424284</v>
+        <v>450251.51515151543</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
@@ -4069,19 +4090,19 @@
       </c>
       <c r="I34" s="9">
         <f>Main!$N$58+Main!$N$56</f>
-        <v>-18981.818181818187</v>
+        <v>-16363.636363636364</v>
       </c>
       <c r="K34" s="9">
-        <f>Main!$N$15</f>
+        <f>Main!$N$17</f>
         <v>189818.18181818185</v>
       </c>
       <c r="M34" s="9">
         <f t="shared" si="0"/>
-        <v>84403.030303030333</v>
+        <v>87021.212121212156</v>
       </c>
       <c r="N34" s="9">
         <f t="shared" si="1"/>
-        <v>571227.27272727317</v>
+        <v>537272.72727272753</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
@@ -4104,19 +4125,19 @@
       </c>
       <c r="I35" s="9">
         <f>Main!$N$58+Main!$N$56</f>
-        <v>-18981.818181818187</v>
+        <v>-16363.636363636364</v>
       </c>
       <c r="K35" s="9">
-        <f>Main!$N$15</f>
+        <f>Main!$N$17</f>
         <v>189818.18181818185</v>
       </c>
       <c r="M35" s="9">
         <f t="shared" si="0"/>
-        <v>84403.030303030333</v>
+        <v>87021.212121212156</v>
       </c>
       <c r="N35" s="9">
         <f t="shared" si="1"/>
-        <v>655630.30303030345</v>
+        <v>624293.93939393968</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
@@ -4139,19 +4160,19 @@
       </c>
       <c r="I36" s="9">
         <f>Main!$N$58+Main!$N$56</f>
-        <v>-18981.818181818187</v>
+        <v>-16363.636363636364</v>
       </c>
       <c r="K36" s="9">
-        <f>Main!$N$15</f>
+        <f>Main!$N$17</f>
         <v>189818.18181818185</v>
       </c>
       <c r="M36" s="9">
         <f t="shared" si="0"/>
-        <v>84403.030303030333</v>
+        <v>87021.212121212156</v>
       </c>
       <c r="N36" s="9">
         <f t="shared" si="1"/>
-        <v>740033.33333333372</v>
+        <v>711315.15151515184</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
@@ -4174,19 +4195,19 @@
       </c>
       <c r="I37" s="9">
         <f>Main!$N$58+Main!$N$56</f>
-        <v>-18981.818181818187</v>
+        <v>-16363.636363636364</v>
       </c>
       <c r="K37" s="9">
-        <f>Main!$N$15</f>
+        <f>Main!$N$17</f>
         <v>189818.18181818185</v>
       </c>
       <c r="M37" s="9">
         <f t="shared" si="0"/>
-        <v>84403.030303030333</v>
+        <v>87021.212121212156</v>
       </c>
       <c r="N37" s="9">
         <f t="shared" si="1"/>
-        <v>824436.363636364</v>
+        <v>798336.363636364</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
@@ -4209,19 +4230,19 @@
       </c>
       <c r="I38" s="9">
         <f>Main!$N$58+Main!$N$56</f>
-        <v>-18981.818181818187</v>
+        <v>-16363.636363636364</v>
       </c>
       <c r="K38" s="9">
-        <f>Main!$N$15</f>
+        <f>Main!$N$17</f>
         <v>189818.18181818185</v>
       </c>
       <c r="M38" s="9">
         <f t="shared" si="0"/>
-        <v>84403.030303030333</v>
+        <v>87021.212121212156</v>
       </c>
       <c r="N38" s="9">
         <f t="shared" si="1"/>
-        <v>908839.39393939427</v>
+        <v>885357.57575757615</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
@@ -4244,19 +4265,19 @@
       </c>
       <c r="I39" s="9">
         <f>Main!$N$58+Main!$N$56</f>
-        <v>-18981.818181818187</v>
+        <v>-16363.636363636364</v>
       </c>
       <c r="K39" s="9">
-        <f>Main!$N$15</f>
+        <f>Main!$N$17</f>
         <v>189818.18181818185</v>
       </c>
       <c r="M39" s="9">
         <f t="shared" si="0"/>
-        <v>84403.030303030333</v>
+        <v>87021.212121212156</v>
       </c>
       <c r="N39" s="9">
         <f t="shared" si="1"/>
-        <v>993242.42424242455</v>
+        <v>972378.78787878831</v>
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
@@ -4279,19 +4300,19 @@
       </c>
       <c r="I40" s="9">
         <f>Main!$N$58+Main!$N$56</f>
-        <v>-18981.818181818187</v>
+        <v>-16363.636363636364</v>
       </c>
       <c r="K40" s="9">
-        <f>Main!$N$15</f>
+        <f>Main!$N$17</f>
         <v>189818.18181818185</v>
       </c>
       <c r="M40" s="9">
         <f t="shared" si="0"/>
-        <v>84403.030303030333</v>
+        <v>87021.212121212156</v>
       </c>
       <c r="N40" s="9">
         <f t="shared" si="1"/>
-        <v>1077645.4545454548</v>
+        <v>1059400.0000000005</v>
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
@@ -4314,19 +4335,19 @@
       </c>
       <c r="I41" s="9">
         <f>Main!$N$58+Main!$N$56</f>
-        <v>-18981.818181818187</v>
+        <v>-16363.636363636364</v>
       </c>
       <c r="K41" s="9">
-        <f>Main!$N$15</f>
+        <f>Main!$N$17</f>
         <v>189818.18181818185</v>
       </c>
       <c r="M41" s="9">
         <f t="shared" si="0"/>
-        <v>84403.030303030333</v>
+        <v>87021.212121212156</v>
       </c>
       <c r="N41" s="9">
         <f t="shared" si="1"/>
-        <v>1162048.4848484851</v>
+        <v>1146421.2121212126</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
@@ -4349,19 +4370,19 @@
       </c>
       <c r="I42" s="9">
         <f>Main!$N$58+Main!$N$56</f>
-        <v>-18981.818181818187</v>
+        <v>-16363.636363636364</v>
       </c>
       <c r="K42" s="9">
-        <f>Main!$N$15</f>
+        <f>Main!$N$17</f>
         <v>189818.18181818185</v>
       </c>
       <c r="M42" s="9">
         <f t="shared" si="0"/>
-        <v>84403.030303030333</v>
+        <v>87021.212121212156</v>
       </c>
       <c r="N42" s="9">
         <f t="shared" si="1"/>
-        <v>1246451.5151515154</v>
+        <v>1233442.4242424248</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
@@ -4384,19 +4405,19 @@
       </c>
       <c r="I43" s="9">
         <f>Main!$N$58+Main!$N$56</f>
-        <v>-18981.818181818187</v>
+        <v>-16363.636363636364</v>
       </c>
       <c r="K43" s="9">
-        <f>Main!$N$15</f>
+        <f>Main!$N$17</f>
         <v>189818.18181818185</v>
       </c>
       <c r="M43" s="9">
         <f t="shared" si="0"/>
-        <v>84403.030303030333</v>
+        <v>87021.212121212156</v>
       </c>
       <c r="N43" s="9">
         <f t="shared" si="1"/>
-        <v>1330854.5454545456</v>
+        <v>1320463.6363636369</v>
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.25">
@@ -4427,19 +4448,19 @@
       </c>
       <c r="I44" s="9">
         <f>Main!$N$58+Main!$N$56</f>
-        <v>-18981.818181818187</v>
+        <v>-16363.636363636364</v>
       </c>
       <c r="K44" s="9">
-        <f>Main!$N$15</f>
+        <f>Main!$N$17</f>
         <v>189818.18181818185</v>
       </c>
       <c r="M44" s="9">
         <f t="shared" si="0"/>
-        <v>-96134.84848484848</v>
+        <v>-93516.666666666657</v>
       </c>
       <c r="N44" s="9">
         <f t="shared" si="1"/>
-        <v>1234719.6969696973</v>
+        <v>1226946.9696969702</v>
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
@@ -4462,19 +4483,19 @@
       </c>
       <c r="I45" s="9">
         <f>Main!$O$58+Main!$O$56</f>
-        <v>-42709.090909090912</v>
+        <v>-30681.81818181818</v>
       </c>
       <c r="K45" s="9">
-        <f>Main!$O$15</f>
+        <f>Main!$O$17</f>
         <v>284727.27272727276</v>
       </c>
       <c r="M45" s="9">
         <f t="shared" si="0"/>
-        <v>123584.84848484851</v>
+        <v>135612.12121212124</v>
       </c>
       <c r="N45" s="9">
         <f t="shared" si="1"/>
-        <v>1358304.5454545459</v>
+        <v>1362559.0909090915</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
@@ -4497,19 +4518,19 @@
       </c>
       <c r="I46" s="9">
         <f>Main!$O$58+Main!$O$56</f>
-        <v>-42709.090909090912</v>
+        <v>-30681.81818181818</v>
       </c>
       <c r="K46" s="9">
-        <f>Main!$O$15</f>
+        <f>Main!$O$17</f>
         <v>284727.27272727276</v>
       </c>
       <c r="M46" s="9">
         <f t="shared" si="0"/>
-        <v>123584.84848484851</v>
+        <v>135612.12121212124</v>
       </c>
       <c r="N46" s="9">
         <f t="shared" si="1"/>
-        <v>1481889.3939393945</v>
+        <v>1498171.2121212129</v>
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.25">
@@ -4532,19 +4553,19 @@
       </c>
       <c r="I47" s="9">
         <f>Main!$O$58+Main!$O$56</f>
-        <v>-42709.090909090912</v>
+        <v>-30681.81818181818</v>
       </c>
       <c r="K47" s="9">
-        <f>Main!$O$15</f>
+        <f>Main!$O$17</f>
         <v>284727.27272727276</v>
       </c>
       <c r="M47" s="9">
         <f t="shared" si="0"/>
-        <v>123584.84848484851</v>
+        <v>135612.12121212124</v>
       </c>
       <c r="N47" s="9">
         <f t="shared" si="1"/>
-        <v>1605474.2424242431</v>
+        <v>1633783.3333333342</v>
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.25">
@@ -4567,19 +4588,19 @@
       </c>
       <c r="I48" s="9">
         <f>Main!$O$58+Main!$O$56</f>
-        <v>-42709.090909090912</v>
+        <v>-30681.81818181818</v>
       </c>
       <c r="K48" s="9">
-        <f>Main!$O$15</f>
+        <f>Main!$O$17</f>
         <v>284727.27272727276</v>
       </c>
       <c r="M48" s="9">
         <f t="shared" si="0"/>
-        <v>123584.84848484851</v>
+        <v>135612.12121212124</v>
       </c>
       <c r="N48" s="9">
         <f t="shared" si="1"/>
-        <v>1729059.0909090918</v>
+        <v>1769395.4545454555</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
@@ -4602,19 +4623,19 @@
       </c>
       <c r="I49" s="9">
         <f>Main!$O$58+Main!$O$56</f>
-        <v>-42709.090909090912</v>
+        <v>-30681.81818181818</v>
       </c>
       <c r="K49" s="9">
-        <f>Main!$O$15</f>
+        <f>Main!$O$17</f>
         <v>284727.27272727276</v>
       </c>
       <c r="M49" s="9">
         <f t="shared" si="0"/>
-        <v>123584.84848484851</v>
+        <v>135612.12121212124</v>
       </c>
       <c r="N49" s="9">
         <f t="shared" si="1"/>
-        <v>1852643.9393939404</v>
+        <v>1905007.5757575769</v>
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
@@ -4637,19 +4658,19 @@
       </c>
       <c r="I50" s="9">
         <f>Main!$O$58+Main!$O$56</f>
-        <v>-42709.090909090912</v>
+        <v>-30681.81818181818</v>
       </c>
       <c r="K50" s="9">
-        <f>Main!$O$15</f>
+        <f>Main!$O$17</f>
         <v>284727.27272727276</v>
       </c>
       <c r="M50" s="9">
         <f t="shared" si="0"/>
-        <v>123584.84848484851</v>
+        <v>135612.12121212124</v>
       </c>
       <c r="N50" s="9">
         <f t="shared" si="1"/>
-        <v>1976228.787878789</v>
+        <v>2040619.6969696982</v>
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.25">
@@ -4672,19 +4693,19 @@
       </c>
       <c r="I51" s="9">
         <f>Main!$O$58+Main!$O$56</f>
-        <v>-42709.090909090912</v>
+        <v>-30681.81818181818</v>
       </c>
       <c r="K51" s="9">
-        <f>Main!$O$15</f>
+        <f>Main!$O$17</f>
         <v>284727.27272727276</v>
       </c>
       <c r="M51" s="9">
         <f t="shared" si="0"/>
-        <v>123584.84848484851</v>
+        <v>135612.12121212124</v>
       </c>
       <c r="N51" s="9">
         <f t="shared" si="1"/>
-        <v>2099813.6363636376</v>
+        <v>2176231.8181818193</v>
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.25">
@@ -4707,19 +4728,19 @@
       </c>
       <c r="I52" s="9">
         <f>Main!$O$58+Main!$O$56</f>
-        <v>-42709.090909090912</v>
+        <v>-30681.81818181818</v>
       </c>
       <c r="K52" s="9">
-        <f>Main!$O$15</f>
+        <f>Main!$O$17</f>
         <v>284727.27272727276</v>
       </c>
       <c r="M52" s="9">
         <f t="shared" si="0"/>
-        <v>123584.84848484851</v>
+        <v>135612.12121212124</v>
       </c>
       <c r="N52" s="9">
         <f t="shared" si="1"/>
-        <v>2223398.4848484863</v>
+        <v>2311843.9393939404</v>
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.25">
@@ -4742,19 +4763,19 @@
       </c>
       <c r="I53" s="9">
         <f>Main!$O$58+Main!$O$56</f>
-        <v>-42709.090909090912</v>
+        <v>-30681.81818181818</v>
       </c>
       <c r="K53" s="9">
-        <f>Main!$O$15</f>
+        <f>Main!$O$17</f>
         <v>284727.27272727276</v>
       </c>
       <c r="M53" s="9">
         <f t="shared" si="0"/>
-        <v>123584.84848484851</v>
+        <v>135612.12121212124</v>
       </c>
       <c r="N53" s="9">
         <f t="shared" si="1"/>
-        <v>2346983.3333333349</v>
+        <v>2447456.0606060615</v>
       </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.25">
@@ -4777,19 +4798,19 @@
       </c>
       <c r="I54" s="9">
         <f>Main!$O$58+Main!$O$56</f>
-        <v>-42709.090909090912</v>
+        <v>-30681.81818181818</v>
       </c>
       <c r="K54" s="9">
-        <f>Main!$O$15</f>
+        <f>Main!$O$17</f>
         <v>284727.27272727276</v>
       </c>
       <c r="M54" s="9">
         <f t="shared" si="0"/>
-        <v>123584.84848484851</v>
+        <v>135612.12121212124</v>
       </c>
       <c r="N54" s="9">
         <f t="shared" si="1"/>
-        <v>2470568.1818181835</v>
+        <v>2583068.1818181826</v>
       </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.25">
@@ -4812,19 +4833,19 @@
       </c>
       <c r="I55" s="9">
         <f>Main!$O$58+Main!$O$56</f>
-        <v>-42709.090909090912</v>
+        <v>-30681.81818181818</v>
       </c>
       <c r="K55" s="9">
-        <f>Main!$O$15</f>
+        <f>Main!$O$17</f>
         <v>284727.27272727276</v>
       </c>
       <c r="M55" s="9">
         <f t="shared" si="0"/>
-        <v>123584.84848484851</v>
+        <v>135612.12121212124</v>
       </c>
       <c r="N55" s="9">
         <f t="shared" si="1"/>
-        <v>2594153.0303030321</v>
+        <v>2718680.3030303037</v>
       </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.25">
@@ -4855,19 +4876,19 @@
       </c>
       <c r="I56" s="9">
         <f>Main!$O$58+Main!$O$56</f>
-        <v>-42709.090909090912</v>
+        <v>-30681.81818181818</v>
       </c>
       <c r="K56" s="9">
-        <f>Main!$O$15</f>
+        <f>Main!$O$17</f>
         <v>284727.27272727276</v>
       </c>
       <c r="M56" s="9">
         <f t="shared" si="0"/>
-        <v>-64953.030303030217</v>
+        <v>-52925.757575757452</v>
       </c>
       <c r="N56" s="9">
         <f t="shared" si="1"/>
-        <v>2529200.0000000019</v>
+        <v>2665754.5454545463</v>
       </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.25">
@@ -4890,19 +4911,19 @@
       </c>
       <c r="I57" s="9">
         <f>Main!$P$58+Main!$P$56</f>
-        <v>-56945.454545454551</v>
+        <v>-40909.090909090912</v>
       </c>
       <c r="K57" s="9">
-        <f>Main!$P$15</f>
+        <f>Main!$P$17</f>
         <v>379636.36363636371</v>
       </c>
       <c r="M57" s="9">
         <f t="shared" si="0"/>
-        <v>172257.5757575758</v>
+        <v>188293.93939393945</v>
       </c>
       <c r="N57" s="9">
         <f t="shared" si="1"/>
-        <v>2701457.5757575775</v>
+        <v>2854048.4848484858</v>
       </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.25">
@@ -4925,19 +4946,19 @@
       </c>
       <c r="I58" s="9">
         <f>Main!$P$58+Main!$P$56</f>
-        <v>-56945.454545454551</v>
+        <v>-40909.090909090912</v>
       </c>
       <c r="K58" s="9">
-        <f>Main!$P$15</f>
+        <f>Main!$P$17</f>
         <v>379636.36363636371</v>
       </c>
       <c r="M58" s="9">
         <f t="shared" si="0"/>
-        <v>172257.5757575758</v>
+        <v>188293.93939393945</v>
       </c>
       <c r="N58" s="9">
         <f t="shared" si="1"/>
-        <v>2873715.1515151532</v>
+        <v>3042342.4242424252</v>
       </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.25">
@@ -4960,19 +4981,19 @@
       </c>
       <c r="I59" s="9">
         <f>Main!$P$58+Main!$P$56</f>
-        <v>-56945.454545454551</v>
+        <v>-40909.090909090912</v>
       </c>
       <c r="K59" s="9">
-        <f>Main!$P$15</f>
+        <f>Main!$P$17</f>
         <v>379636.36363636371</v>
       </c>
       <c r="M59" s="9">
         <f t="shared" si="0"/>
-        <v>172257.5757575758</v>
+        <v>188293.93939393945</v>
       </c>
       <c r="N59" s="9">
         <f t="shared" si="1"/>
-        <v>3045972.7272727289</v>
+        <v>3230636.3636363647</v>
       </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.25">
@@ -4995,19 +5016,19 @@
       </c>
       <c r="I60" s="9">
         <f>Main!$P$58+Main!$P$56</f>
-        <v>-56945.454545454551</v>
+        <v>-40909.090909090912</v>
       </c>
       <c r="K60" s="9">
-        <f>Main!$P$15</f>
+        <f>Main!$P$17</f>
         <v>379636.36363636371</v>
       </c>
       <c r="M60" s="9">
         <f t="shared" si="0"/>
-        <v>172257.5757575758</v>
+        <v>188293.93939393945</v>
       </c>
       <c r="N60" s="9">
         <f t="shared" si="1"/>
-        <v>3218230.3030303046</v>
+        <v>3418930.3030303041</v>
       </c>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.25">
@@ -5030,19 +5051,19 @@
       </c>
       <c r="I61" s="9">
         <f>Main!$P$58+Main!$P$56</f>
-        <v>-56945.454545454551</v>
+        <v>-40909.090909090912</v>
       </c>
       <c r="K61" s="9">
-        <f>Main!$P$15</f>
+        <f>Main!$P$17</f>
         <v>379636.36363636371</v>
       </c>
       <c r="M61" s="9">
         <f t="shared" si="0"/>
-        <v>172257.5757575758</v>
+        <v>188293.93939393945</v>
       </c>
       <c r="N61" s="9">
         <f t="shared" si="1"/>
-        <v>3390487.8787878803</v>
+        <v>3607224.2424242436</v>
       </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.25">
@@ -5065,19 +5086,19 @@
       </c>
       <c r="I62" s="9">
         <f>Main!$P$58+Main!$P$56</f>
-        <v>-56945.454545454551</v>
+        <v>-40909.090909090912</v>
       </c>
       <c r="K62" s="9">
-        <f>Main!$P$15</f>
+        <f>Main!$P$17</f>
         <v>379636.36363636371</v>
       </c>
       <c r="M62" s="9">
         <f t="shared" si="0"/>
-        <v>172257.5757575758</v>
+        <v>188293.93939393945</v>
       </c>
       <c r="N62" s="9">
         <f t="shared" si="1"/>
-        <v>3562745.454545456</v>
+        <v>3795518.181818183</v>
       </c>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.25">
@@ -5100,19 +5121,19 @@
       </c>
       <c r="I63" s="9">
         <f>Main!$P$58+Main!$P$56</f>
-        <v>-56945.454545454551</v>
+        <v>-40909.090909090912</v>
       </c>
       <c r="K63" s="9">
-        <f>Main!$P$15</f>
+        <f>Main!$P$17</f>
         <v>379636.36363636371</v>
       </c>
       <c r="M63" s="9">
         <f t="shared" si="0"/>
-        <v>172257.5757575758</v>
+        <v>188293.93939393945</v>
       </c>
       <c r="N63" s="9">
         <f t="shared" si="1"/>
-        <v>3735003.0303030317</v>
+        <v>3983812.1212121225</v>
       </c>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.25">
@@ -5135,19 +5156,19 @@
       </c>
       <c r="I64" s="9">
         <f>Main!$P$58+Main!$P$56</f>
-        <v>-56945.454545454551</v>
+        <v>-40909.090909090912</v>
       </c>
       <c r="K64" s="9">
-        <f>Main!$P$15</f>
+        <f>Main!$P$17</f>
         <v>379636.36363636371</v>
       </c>
       <c r="M64" s="9">
         <f t="shared" si="0"/>
-        <v>172257.5757575758</v>
+        <v>188293.93939393945</v>
       </c>
       <c r="N64" s="9">
         <f t="shared" si="1"/>
-        <v>3907260.6060606074</v>
+        <v>4172106.0606060619</v>
       </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.25">
@@ -5170,19 +5191,19 @@
       </c>
       <c r="I65" s="9">
         <f>Main!$P$58+Main!$P$56</f>
-        <v>-56945.454545454551</v>
+        <v>-40909.090909090912</v>
       </c>
       <c r="K65" s="9">
-        <f>Main!$P$15</f>
+        <f>Main!$P$17</f>
         <v>379636.36363636371</v>
       </c>
       <c r="M65" s="9">
         <f t="shared" si="0"/>
-        <v>172257.5757575758</v>
+        <v>188293.93939393945</v>
       </c>
       <c r="N65" s="9">
         <f t="shared" si="1"/>
-        <v>4079518.181818183</v>
+        <v>4360400.0000000019</v>
       </c>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.25">
@@ -5205,19 +5226,19 @@
       </c>
       <c r="I66" s="9">
         <f>Main!$P$58+Main!$P$56</f>
-        <v>-56945.454545454551</v>
+        <v>-40909.090909090912</v>
       </c>
       <c r="K66" s="9">
-        <f>Main!$P$15</f>
+        <f>Main!$P$17</f>
         <v>379636.36363636371</v>
       </c>
       <c r="M66" s="9">
         <f t="shared" si="0"/>
-        <v>172257.5757575758</v>
+        <v>188293.93939393945</v>
       </c>
       <c r="N66" s="9">
         <f t="shared" si="1"/>
-        <v>4251775.7575757587</v>
+        <v>4548693.9393939413</v>
       </c>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.25">
@@ -5240,19 +5261,19 @@
       </c>
       <c r="I67" s="9">
         <f>Main!$P$58+Main!$P$56</f>
-        <v>-56945.454545454551</v>
+        <v>-40909.090909090912</v>
       </c>
       <c r="K67" s="9">
-        <f>Main!$P$15</f>
+        <f>Main!$P$17</f>
         <v>379636.36363636371</v>
       </c>
       <c r="M67" s="9">
         <f t="shared" si="0"/>
-        <v>172257.5757575758</v>
+        <v>188293.93939393945</v>
       </c>
       <c r="N67" s="9">
         <f t="shared" si="1"/>
-        <v>4424033.3333333349</v>
+        <v>4736987.8787878808</v>
       </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.25">
@@ -5275,19 +5296,19 @@
       </c>
       <c r="I68" s="9">
         <f>Main!$P$58+Main!$P$56</f>
-        <v>-56945.454545454551</v>
+        <v>-40909.090909090912</v>
       </c>
       <c r="K68" s="9">
-        <f>Main!$P$15</f>
+        <f>Main!$P$17</f>
         <v>379636.36363636371</v>
       </c>
       <c r="M68" s="9">
         <f t="shared" si="0"/>
-        <v>172257.5757575758</v>
+        <v>188293.93939393945</v>
       </c>
       <c r="N68" s="9">
         <f t="shared" si="1"/>
-        <v>4596290.909090911</v>
+        <v>4925281.8181818202</v>
       </c>
     </row>
   </sheetData>

--- a/data/Delivery.xlsx
+++ b/data/Delivery.xlsx
@@ -14,6 +14,7 @@
   <sheets>
     <sheet name="Main" sheetId="3" r:id="rId1"/>
     <sheet name="Cash FLow" sheetId="6" r:id="rId2"/>
+    <sheet name="Rider Salary Calculation" sheetId="7" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="69">
   <si>
     <t>Average order value</t>
   </si>
@@ -168,9 +169,6 @@
     <t>Tax</t>
   </si>
   <si>
-    <t>bonus of delivery fees after $400</t>
-  </si>
-  <si>
     <t>Registration and Fees</t>
   </si>
   <si>
@@ -217,6 +215,24 @@
   </si>
   <si>
     <t>Number of Orders</t>
+  </si>
+  <si>
+    <t>Base</t>
+  </si>
+  <si>
+    <t>%</t>
+  </si>
+  <si>
+    <t>USD Rate</t>
+  </si>
+  <si>
+    <t>bonus of delivery fees after Base Salary</t>
+  </si>
+  <si>
+    <t># Orders</t>
+  </si>
+  <si>
+    <t>Salary + Bonus</t>
   </si>
 </sst>
 </file>
@@ -228,9 +244,9 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="_([$SYP]\ * #,##0_);_([$SYP]\ * \(#,##0\);_([$SYP]\ * &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="171" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -275,8 +291,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -297,6 +320,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -324,15 +352,16 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="6">
+  <cellStyleXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
@@ -366,12 +395,17 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" xfId="6" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="6" fillId="5" borderId="0" xfId="6" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="7">
     <cellStyle name="Accent3" xfId="4" builtinId="37"/>
     <cellStyle name="Comma" xfId="5" builtinId="3"/>
     <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Good" xfId="6" builtinId="26"/>
     <cellStyle name="Input" xfId="3" builtinId="20"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
@@ -662,184 +696,184 @@
                 <c:formatCode>_("$"* #,##0_);_("$"* \(#,##0\);_("$"* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="60"/>
                 <c:pt idx="0">
-                  <c:v>5416.6666666666679</c:v>
+                  <c:v>5116.6666666666679</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>20109.090909090919</c:v>
+                  <c:v>19481.818181818187</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>34801.515151515167</c:v>
+                  <c:v>33846.969696969711</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>49493.939393939421</c:v>
+                  <c:v>48212.12121212123</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>64186.363636363676</c:v>
+                  <c:v>62577.27272727275</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>78878.787878787931</c:v>
+                  <c:v>76942.424242424269</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>93571.212121212186</c:v>
+                  <c:v>91307.575757575789</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>108263.63636363644</c:v>
+                  <c:v>105672.72727272731</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>122956.0606060607</c:v>
+                  <c:v>120037.87878787883</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>137648.48484848495</c:v>
+                  <c:v>134403.03030303033</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>152340.9090909092</c:v>
+                  <c:v>148768.18181818185</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>80495.454545454646</c:v>
+                  <c:v>76295.454545454559</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>121351.51515151527</c:v>
+                  <c:v>116596.96969696973</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>162207.57575757589</c:v>
+                  <c:v>156898.48484848489</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>203063.63636363653</c:v>
+                  <c:v>197200.00000000006</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>243919.69696969714</c:v>
+                  <c:v>237501.51515151522</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>284775.75757575774</c:v>
+                  <c:v>277803.03030303039</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>325631.81818181835</c:v>
+                  <c:v>318104.54545454553</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>366487.87878787896</c:v>
+                  <c:v>358406.06060606067</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>407343.93939393957</c:v>
+                  <c:v>398707.5757575758</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>448200.00000000017</c:v>
+                  <c:v>439009.09090909094</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>489056.06060606078</c:v>
+                  <c:v>479310.60606060608</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>529912.12121212145</c:v>
+                  <c:v>519612.12121212122</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>363230.30303030327</c:v>
+                  <c:v>352075.75757575763</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>450251.51515151543</c:v>
+                  <c:v>437987.8787878789</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>537272.72727272753</c:v>
+                  <c:v>523900.00000000012</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>624293.93939393968</c:v>
+                  <c:v>609812.12121212133</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>711315.15151515184</c:v>
+                  <c:v>695724.24242424255</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>798336.363636364</c:v>
+                  <c:v>781636.36363636376</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>885357.57575757615</c:v>
+                  <c:v>867548.48484848498</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>972378.78787878831</c:v>
+                  <c:v>953460.60606060619</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>1059400.0000000005</c:v>
+                  <c:v>1039372.7272727274</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>1146421.2121212126</c:v>
+                  <c:v>1125284.8484848486</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>1233442.4242424248</c:v>
+                  <c:v>1211196.96969697</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>1320463.6363636369</c:v>
+                  <c:v>1297109.0909090913</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>1226946.9696969702</c:v>
+                  <c:v>1202183.3333333337</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>1362559.0909090915</c:v>
+                  <c:v>1336231.8181818186</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>1498171.2121212129</c:v>
+                  <c:v>1470280.3030303034</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>1633783.3333333342</c:v>
+                  <c:v>1604328.7878787883</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>1769395.4545454555</c:v>
+                  <c:v>1738377.2727272732</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>1905007.5757575769</c:v>
+                  <c:v>1872425.757575758</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>2040619.6969696982</c:v>
+                  <c:v>2006474.2424242429</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>2176231.8181818193</c:v>
+                  <c:v>2140522.727272728</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>2311843.9393939404</c:v>
+                  <c:v>2274571.2121212129</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>2447456.0606060615</c:v>
+                  <c:v>2408619.6969696977</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>2583068.1818181826</c:v>
+                  <c:v>2542668.1818181826</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>2718680.3030303037</c:v>
+                  <c:v>2676716.6666666674</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>2665754.5454545463</c:v>
+                  <c:v>2621927.2727272734</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>2854048.4848484858</c:v>
+                  <c:v>2808203.0303030312</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>3042342.4242424252</c:v>
+                  <c:v>2994478.787878789</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>3230636.3636363647</c:v>
+                  <c:v>3180754.5454545468</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>3418930.3030303041</c:v>
+                  <c:v>3367030.3030303046</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>3607224.2424242436</c:v>
+                  <c:v>3553306.0606060624</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>3795518.181818183</c:v>
+                  <c:v>3739581.8181818202</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>3983812.1212121225</c:v>
+                  <c:v>3925857.575757578</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>4172106.0606060619</c:v>
+                  <c:v>4112133.3333333358</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>4360400.0000000019</c:v>
+                  <c:v>4298409.0909090936</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>4548693.9393939413</c:v>
+                  <c:v>4484684.8484848514</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>4736987.8787878808</c:v>
+                  <c:v>4670960.6060606092</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>4925281.8181818202</c:v>
+                  <c:v>4857236.363636367</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1901,6 +1935,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF92D050"/>
+  </sheetPr>
   <dimension ref="A1:P76"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2167,7 +2204,7 @@
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="K15" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="L15" s="21">
         <f>L7*$D$10*30</f>
@@ -2221,7 +2258,7 @@
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L18" s="9"/>
       <c r="M18" s="9"/>
@@ -2439,7 +2476,7 @@
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C27" s="14">
         <f>1000+5000</f>
@@ -2477,12 +2514,12 @@
       </c>
       <c r="E28" s="10">
         <f>D28-SUM(L31:L37)*12</f>
-        <v>119583.33333333333</v>
+        <v>119883.33333333333</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.25">
@@ -2584,30 +2621,30 @@
         <v>30</v>
       </c>
       <c r="D34" s="5">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="E34" t="s">
         <v>33</v>
       </c>
       <c r="L34" s="9">
         <f>-$D$34/12</f>
-        <v>-16.666666666666668</v>
+        <v>-41.666666666666664</v>
       </c>
       <c r="M34" s="9">
         <f t="shared" ref="M34:P34" si="3">-$D$34/12</f>
-        <v>-16.666666666666668</v>
+        <v>-41.666666666666664</v>
       </c>
       <c r="N34" s="9">
         <f t="shared" si="3"/>
-        <v>-16.666666666666668</v>
+        <v>-41.666666666666664</v>
       </c>
       <c r="O34" s="9">
         <f t="shared" si="3"/>
-        <v>-16.666666666666668</v>
+        <v>-41.666666666666664</v>
       </c>
       <c r="P34" s="9">
         <f t="shared" si="3"/>
-        <v>-16.666666666666668</v>
+        <v>-41.666666666666664</v>
       </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.25">
@@ -2710,7 +2747,7 @@
     <row r="39" spans="1:16" x14ac:dyDescent="0.25">
       <c r="D39" s="10">
         <f>SUM(D31:D35)</f>
-        <v>20537.878787878788</v>
+        <v>20837.878787878788</v>
       </c>
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.25">
@@ -2718,39 +2755,39 @@
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D41" s="10"/>
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D42" s="8">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="E42" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="L42" s="9">
         <f>-$D$42*L3</f>
-        <v>-400</v>
+        <v>-500</v>
       </c>
       <c r="M42" s="9">
         <f t="shared" ref="M42:P42" si="5">-$D$42*M3</f>
-        <v>-400</v>
+        <v>-500</v>
       </c>
       <c r="N42" s="9">
         <f t="shared" si="5"/>
-        <v>-800</v>
+        <v>-1000</v>
       </c>
       <c r="O42" s="9">
         <f t="shared" si="5"/>
-        <v>-800</v>
+        <v>-1000</v>
       </c>
       <c r="P42" s="9">
         <f t="shared" si="5"/>
-        <v>-800</v>
+        <v>-1000</v>
       </c>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.25">
@@ -2795,34 +2832,35 @@
       </c>
       <c r="C47"/>
       <c r="D47" s="8">
-        <f>IF(D10*30*D8/B1*E47&gt;400, D10*30*D8/B1*E47, 400)</f>
-        <v>400</v>
+        <f>'Rider Salary Calculation'!B11+D10*30*D8*E47/B1</f>
+        <v>405.68181818181819</v>
       </c>
       <c r="E47" s="2">
-        <v>0.75</v>
+        <f>'Rider Salary Calculation'!B13</f>
+        <v>0.5</v>
       </c>
       <c r="F47" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="L47" s="9">
         <f t="shared" ref="L47:P53" si="6">-$D47*L7</f>
-        <v>-16000</v>
+        <v>-16227.272727272728</v>
       </c>
       <c r="M47" s="9">
         <f t="shared" si="6"/>
-        <v>-32000</v>
+        <v>-32454.545454545456</v>
       </c>
       <c r="N47" s="9">
         <f t="shared" si="6"/>
-        <v>-64000</v>
+        <v>-64909.090909090912</v>
       </c>
       <c r="O47" s="9">
         <f t="shared" si="6"/>
-        <v>-96000</v>
+        <v>-97363.636363636368</v>
       </c>
       <c r="P47" s="9">
         <f t="shared" si="6"/>
-        <v>-128000</v>
+        <v>-129818.18181818182</v>
       </c>
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.25">
@@ -3067,23 +3105,23 @@
       </c>
       <c r="L62" s="10">
         <f>SUM(L17:L60)</f>
-        <v>21063.510101010106</v>
+        <v>20711.237373737378</v>
       </c>
       <c r="M62" s="10">
         <f>SUM(M17:M60)</f>
-        <v>45927.146464646503</v>
+        <v>45347.601010101047</v>
       </c>
       <c r="N62" s="10">
         <f>SUM(N17:N60)</f>
-        <v>87242.297979798052</v>
+        <v>86108.20707070714</v>
       </c>
       <c r="O62" s="10">
         <f>SUM(O17:O60)</f>
-        <v>133233.20707070705</v>
+        <v>131644.5707070707</v>
       </c>
       <c r="P62" s="10">
         <f>SUM(P17:P60)</f>
-        <v>183315.02525252529</v>
+        <v>181271.84343434346</v>
       </c>
     </row>
     <row r="64" spans="1:16" x14ac:dyDescent="0.25">
@@ -3130,6 +3168,9 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF00B0F0"/>
+  </sheetPr>
   <dimension ref="A8:N68"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3149,42 +3190,42 @@
   <sheetData>
     <row r="8" spans="1:14" s="18" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="19" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B8" s="19" t="s">
         <v>42</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D8" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E8" s="19" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F8" s="19" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G8" s="19" t="s">
         <v>22</v>
       </c>
       <c r="H8" s="19" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I8" s="19" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J8" s="19"/>
       <c r="K8" s="19" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L8" s="19"/>
       <c r="M8" s="19" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="N8" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
@@ -3203,15 +3244,15 @@
       </c>
       <c r="E9" s="9">
         <f>SUM(Main!L31:L37)*12</f>
-        <v>-24537.878787878788</v>
+        <v>-24837.878787878788</v>
       </c>
       <c r="M9" s="9">
         <f>SUM(C9:K9)</f>
-        <v>5416.6666666666679</v>
+        <v>5116.6666666666679</v>
       </c>
       <c r="N9" s="9">
         <f>M9</f>
-        <v>5416.6666666666679</v>
+        <v>5116.6666666666679</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
@@ -3223,11 +3264,11 @@
       </c>
       <c r="F10" s="9">
         <f>SUM(Main!$L$42:$L$43)</f>
-        <v>-816.66666666666674</v>
+        <v>-916.66666666666674</v>
       </c>
       <c r="G10" s="9">
         <f>SUM(Main!$L$47:$L$53)</f>
-        <v>-19900</v>
+        <v>-20127.272727272728</v>
       </c>
       <c r="H10" s="9">
         <v>-10000</v>
@@ -3242,11 +3283,11 @@
       </c>
       <c r="M10" s="9">
         <f>SUM(C10:K10)</f>
-        <v>14692.424242424251</v>
+        <v>14365.15151515152</v>
       </c>
       <c r="N10" s="9">
         <f>N9+M10</f>
-        <v>20109.090909090919</v>
+        <v>19481.818181818187</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
@@ -3258,11 +3299,11 @@
       </c>
       <c r="F11" s="9">
         <f>SUM(Main!$L$42:$L$43)</f>
-        <v>-816.66666666666674</v>
+        <v>-916.66666666666674</v>
       </c>
       <c r="G11" s="9">
         <f>SUM(Main!$L$47:$L$53)</f>
-        <v>-19900</v>
+        <v>-20127.272727272728</v>
       </c>
       <c r="H11" s="9">
         <v>-10000</v>
@@ -3277,11 +3318,11 @@
       </c>
       <c r="M11" s="9">
         <f t="shared" ref="M11:M68" si="0">SUM(C11:K11)</f>
-        <v>14692.424242424251</v>
+        <v>14365.15151515152</v>
       </c>
       <c r="N11" s="9">
         <f t="shared" ref="N11:N68" si="1">N10+M11</f>
-        <v>34801.515151515167</v>
+        <v>33846.969696969711</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
@@ -3293,11 +3334,11 @@
       </c>
       <c r="F12" s="9">
         <f>SUM(Main!$L$42:$L$43)</f>
-        <v>-816.66666666666674</v>
+        <v>-916.66666666666674</v>
       </c>
       <c r="G12" s="9">
         <f>SUM(Main!$L$47:$L$53)</f>
-        <v>-19900</v>
+        <v>-20127.272727272728</v>
       </c>
       <c r="H12" s="9">
         <v>-10000</v>
@@ -3312,11 +3353,11 @@
       </c>
       <c r="M12" s="9">
         <f t="shared" si="0"/>
-        <v>14692.424242424251</v>
+        <v>14365.15151515152</v>
       </c>
       <c r="N12" s="9">
         <f t="shared" si="1"/>
-        <v>49493.939393939421</v>
+        <v>48212.12121212123</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
@@ -3328,11 +3369,11 @@
       </c>
       <c r="F13" s="9">
         <f>SUM(Main!$L$42:$L$43)</f>
-        <v>-816.66666666666674</v>
+        <v>-916.66666666666674</v>
       </c>
       <c r="G13" s="9">
         <f>SUM(Main!$L$47:$L$53)</f>
-        <v>-19900</v>
+        <v>-20127.272727272728</v>
       </c>
       <c r="H13" s="9">
         <v>-10000</v>
@@ -3347,11 +3388,11 @@
       </c>
       <c r="M13" s="9">
         <f t="shared" si="0"/>
-        <v>14692.424242424251</v>
+        <v>14365.15151515152</v>
       </c>
       <c r="N13" s="9">
         <f t="shared" si="1"/>
-        <v>64186.363636363676</v>
+        <v>62577.27272727275</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
@@ -3363,11 +3404,11 @@
       </c>
       <c r="F14" s="9">
         <f>SUM(Main!$L$42:$L$43)</f>
-        <v>-816.66666666666674</v>
+        <v>-916.66666666666674</v>
       </c>
       <c r="G14" s="9">
         <f>SUM(Main!$L$47:$L$53)</f>
-        <v>-19900</v>
+        <v>-20127.272727272728</v>
       </c>
       <c r="H14" s="9">
         <v>-10000</v>
@@ -3382,11 +3423,11 @@
       </c>
       <c r="M14" s="9">
         <f t="shared" si="0"/>
-        <v>14692.424242424251</v>
+        <v>14365.15151515152</v>
       </c>
       <c r="N14" s="9">
         <f t="shared" si="1"/>
-        <v>78878.787878787931</v>
+        <v>76942.424242424269</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
@@ -3398,11 +3439,11 @@
       </c>
       <c r="F15" s="9">
         <f>SUM(Main!$L$42:$L$43)</f>
-        <v>-816.66666666666674</v>
+        <v>-916.66666666666674</v>
       </c>
       <c r="G15" s="9">
         <f>SUM(Main!$L$47:$L$53)</f>
-        <v>-19900</v>
+        <v>-20127.272727272728</v>
       </c>
       <c r="H15" s="9">
         <v>-10000</v>
@@ -3417,11 +3458,11 @@
       </c>
       <c r="M15" s="9">
         <f t="shared" si="0"/>
-        <v>14692.424242424251</v>
+        <v>14365.15151515152</v>
       </c>
       <c r="N15" s="9">
         <f t="shared" si="1"/>
-        <v>93571.212121212186</v>
+        <v>91307.575757575789</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
@@ -3433,11 +3474,11 @@
       </c>
       <c r="F16" s="9">
         <f>SUM(Main!$L$42:$L$43)</f>
-        <v>-816.66666666666674</v>
+        <v>-916.66666666666674</v>
       </c>
       <c r="G16" s="9">
         <f>SUM(Main!$L$47:$L$53)</f>
-        <v>-19900</v>
+        <v>-20127.272727272728</v>
       </c>
       <c r="H16" s="9">
         <v>-10000</v>
@@ -3452,11 +3493,11 @@
       </c>
       <c r="M16" s="9">
         <f t="shared" si="0"/>
-        <v>14692.424242424251</v>
+        <v>14365.15151515152</v>
       </c>
       <c r="N16" s="9">
         <f t="shared" si="1"/>
-        <v>108263.63636363644</v>
+        <v>105672.72727272731</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
@@ -3468,11 +3509,11 @@
       </c>
       <c r="F17" s="9">
         <f>SUM(Main!$L$42:$L$43)</f>
-        <v>-816.66666666666674</v>
+        <v>-916.66666666666674</v>
       </c>
       <c r="G17" s="9">
         <f>SUM(Main!$L$47:$L$53)</f>
-        <v>-19900</v>
+        <v>-20127.272727272728</v>
       </c>
       <c r="H17" s="9">
         <v>-10000</v>
@@ -3487,11 +3528,11 @@
       </c>
       <c r="M17" s="9">
         <f t="shared" si="0"/>
-        <v>14692.424242424251</v>
+        <v>14365.15151515152</v>
       </c>
       <c r="N17" s="9">
         <f t="shared" si="1"/>
-        <v>122956.0606060607</v>
+        <v>120037.87878787883</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
@@ -3503,11 +3544,11 @@
       </c>
       <c r="F18" s="9">
         <f>SUM(Main!$L$42:$L$43)</f>
-        <v>-816.66666666666674</v>
+        <v>-916.66666666666674</v>
       </c>
       <c r="G18" s="9">
         <f>SUM(Main!$L$47:$L$53)</f>
-        <v>-19900</v>
+        <v>-20127.272727272728</v>
       </c>
       <c r="H18" s="9">
         <v>-10000</v>
@@ -3522,11 +3563,11 @@
       </c>
       <c r="M18" s="9">
         <f t="shared" si="0"/>
-        <v>14692.424242424251</v>
+        <v>14365.15151515152</v>
       </c>
       <c r="N18" s="9">
         <f t="shared" si="1"/>
-        <v>137648.48484848495</v>
+        <v>134403.03030303033</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
@@ -3538,11 +3579,11 @@
       </c>
       <c r="F19" s="9">
         <f>SUM(Main!$L$42:$L$43)</f>
-        <v>-816.66666666666674</v>
+        <v>-916.66666666666674</v>
       </c>
       <c r="G19" s="9">
         <f>SUM(Main!$L$47:$L$53)</f>
-        <v>-19900</v>
+        <v>-20127.272727272728</v>
       </c>
       <c r="H19" s="9">
         <v>-10000</v>
@@ -3557,11 +3598,11 @@
       </c>
       <c r="M19" s="9">
         <f t="shared" si="0"/>
-        <v>14692.424242424251</v>
+        <v>14365.15151515152</v>
       </c>
       <c r="N19" s="9">
         <f t="shared" si="1"/>
-        <v>152340.9090909092</v>
+        <v>148768.18181818185</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
@@ -3577,15 +3618,15 @@
       </c>
       <c r="E20" s="9">
         <f>SUM(Main!M31:M37)*12</f>
-        <v>-28537.878787878792</v>
+        <v>-28837.878787878792</v>
       </c>
       <c r="F20" s="9">
         <f>SUM(Main!$L$42:$L$43)</f>
-        <v>-816.66666666666674</v>
+        <v>-916.66666666666674</v>
       </c>
       <c r="G20" s="9">
         <f>SUM(Main!$L$47:$L$53)</f>
-        <v>-19900</v>
+        <v>-20127.272727272728</v>
       </c>
       <c r="H20" s="9">
         <v>-10000</v>
@@ -3600,11 +3641,11 @@
       </c>
       <c r="M20" s="9">
         <f t="shared" si="0"/>
-        <v>-71845.454545454559</v>
+        <v>-72472.727272727294</v>
       </c>
       <c r="N20" s="9">
         <f t="shared" si="1"/>
-        <v>80495.454545454646</v>
+        <v>76295.454545454559</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
@@ -3616,11 +3657,11 @@
       </c>
       <c r="F21" s="9">
         <f>SUM(Main!$M$42:$M$43)</f>
-        <v>-816.66666666666674</v>
+        <v>-916.66666666666674</v>
       </c>
       <c r="G21" s="9">
         <f>SUM(Main!$M$47:$M$53)</f>
-        <v>-37100</v>
+        <v>-37554.545454545456</v>
       </c>
       <c r="H21" s="9">
         <v>-10000</v>
@@ -3635,11 +3676,11 @@
       </c>
       <c r="M21" s="9">
         <f t="shared" si="0"/>
-        <v>40856.060606060622</v>
+        <v>40301.515151515167</v>
       </c>
       <c r="N21" s="9">
         <f t="shared" si="1"/>
-        <v>121351.51515151527</v>
+        <v>116596.96969696973</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
@@ -3651,11 +3692,11 @@
       </c>
       <c r="F22" s="9">
         <f>SUM(Main!$M$42:$M$43)</f>
-        <v>-816.66666666666674</v>
+        <v>-916.66666666666674</v>
       </c>
       <c r="G22" s="9">
         <f>SUM(Main!$M$47:$M$53)</f>
-        <v>-37100</v>
+        <v>-37554.545454545456</v>
       </c>
       <c r="H22" s="9">
         <v>-10000</v>
@@ -3670,11 +3711,11 @@
       </c>
       <c r="M22" s="9">
         <f t="shared" si="0"/>
-        <v>40856.060606060622</v>
+        <v>40301.515151515167</v>
       </c>
       <c r="N22" s="9">
         <f t="shared" si="1"/>
-        <v>162207.57575757589</v>
+        <v>156898.48484848489</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
@@ -3686,11 +3727,11 @@
       </c>
       <c r="F23" s="9">
         <f>SUM(Main!$M$42:$M$43)</f>
-        <v>-816.66666666666674</v>
+        <v>-916.66666666666674</v>
       </c>
       <c r="G23" s="9">
         <f>SUM(Main!$M$47:$M$53)</f>
-        <v>-37100</v>
+        <v>-37554.545454545456</v>
       </c>
       <c r="H23" s="9">
         <v>-10000</v>
@@ -3705,11 +3746,11 @@
       </c>
       <c r="M23" s="9">
         <f t="shared" si="0"/>
-        <v>40856.060606060622</v>
+        <v>40301.515151515167</v>
       </c>
       <c r="N23" s="9">
         <f t="shared" si="1"/>
-        <v>203063.63636363653</v>
+        <v>197200.00000000006</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
@@ -3721,11 +3762,11 @@
       </c>
       <c r="F24" s="9">
         <f>SUM(Main!$M$42:$M$43)</f>
-        <v>-816.66666666666674</v>
+        <v>-916.66666666666674</v>
       </c>
       <c r="G24" s="9">
         <f>SUM(Main!$M$47:$M$53)</f>
-        <v>-37100</v>
+        <v>-37554.545454545456</v>
       </c>
       <c r="H24" s="9">
         <v>-10000</v>
@@ -3740,11 +3781,11 @@
       </c>
       <c r="M24" s="9">
         <f t="shared" si="0"/>
-        <v>40856.060606060622</v>
+        <v>40301.515151515167</v>
       </c>
       <c r="N24" s="9">
         <f t="shared" si="1"/>
-        <v>243919.69696969714</v>
+        <v>237501.51515151522</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
@@ -3756,11 +3797,11 @@
       </c>
       <c r="F25" s="9">
         <f>SUM(Main!$M$42:$M$43)</f>
-        <v>-816.66666666666674</v>
+        <v>-916.66666666666674</v>
       </c>
       <c r="G25" s="9">
         <f>SUM(Main!$M$47:$M$53)</f>
-        <v>-37100</v>
+        <v>-37554.545454545456</v>
       </c>
       <c r="H25" s="9">
         <v>-10000</v>
@@ -3775,11 +3816,11 @@
       </c>
       <c r="M25" s="9">
         <f t="shared" si="0"/>
-        <v>40856.060606060622</v>
+        <v>40301.515151515167</v>
       </c>
       <c r="N25" s="9">
         <f t="shared" si="1"/>
-        <v>284775.75757575774</v>
+        <v>277803.03030303039</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
@@ -3791,11 +3832,11 @@
       </c>
       <c r="F26" s="9">
         <f>SUM(Main!$M$42:$M$43)</f>
-        <v>-816.66666666666674</v>
+        <v>-916.66666666666674</v>
       </c>
       <c r="G26" s="9">
         <f>SUM(Main!$M$47:$M$53)</f>
-        <v>-37100</v>
+        <v>-37554.545454545456</v>
       </c>
       <c r="H26" s="9">
         <v>-10000</v>
@@ -3810,11 +3851,11 @@
       </c>
       <c r="M26" s="9">
         <f t="shared" si="0"/>
-        <v>40856.060606060622</v>
+        <v>40301.515151515167</v>
       </c>
       <c r="N26" s="9">
         <f t="shared" si="1"/>
-        <v>325631.81818181835</v>
+        <v>318104.54545454553</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
@@ -3826,11 +3867,11 @@
       </c>
       <c r="F27" s="9">
         <f>SUM(Main!$M$42:$M$43)</f>
-        <v>-816.66666666666674</v>
+        <v>-916.66666666666674</v>
       </c>
       <c r="G27" s="9">
         <f>SUM(Main!$M$47:$M$53)</f>
-        <v>-37100</v>
+        <v>-37554.545454545456</v>
       </c>
       <c r="H27" s="9">
         <v>-10000</v>
@@ -3845,11 +3886,11 @@
       </c>
       <c r="M27" s="9">
         <f t="shared" si="0"/>
-        <v>40856.060606060622</v>
+        <v>40301.515151515167</v>
       </c>
       <c r="N27" s="9">
         <f t="shared" si="1"/>
-        <v>366487.87878787896</v>
+        <v>358406.06060606067</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
@@ -3861,11 +3902,11 @@
       </c>
       <c r="F28" s="9">
         <f>SUM(Main!$M$42:$M$43)</f>
-        <v>-816.66666666666674</v>
+        <v>-916.66666666666674</v>
       </c>
       <c r="G28" s="9">
         <f>SUM(Main!$M$47:$M$53)</f>
-        <v>-37100</v>
+        <v>-37554.545454545456</v>
       </c>
       <c r="H28" s="9">
         <v>-10000</v>
@@ -3880,11 +3921,11 @@
       </c>
       <c r="M28" s="9">
         <f t="shared" si="0"/>
-        <v>40856.060606060622</v>
+        <v>40301.515151515167</v>
       </c>
       <c r="N28" s="9">
         <f t="shared" si="1"/>
-        <v>407343.93939393957</v>
+        <v>398707.5757575758</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
@@ -3896,11 +3937,11 @@
       </c>
       <c r="F29" s="9">
         <f>SUM(Main!$M$42:$M$43)</f>
-        <v>-816.66666666666674</v>
+        <v>-916.66666666666674</v>
       </c>
       <c r="G29" s="9">
         <f>SUM(Main!$M$47:$M$53)</f>
-        <v>-37100</v>
+        <v>-37554.545454545456</v>
       </c>
       <c r="H29" s="9">
         <v>-10000</v>
@@ -3915,11 +3956,11 @@
       </c>
       <c r="M29" s="9">
         <f t="shared" si="0"/>
-        <v>40856.060606060622</v>
+        <v>40301.515151515167</v>
       </c>
       <c r="N29" s="9">
         <f t="shared" si="1"/>
-        <v>448200.00000000017</v>
+        <v>439009.09090909094</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
@@ -3931,11 +3972,11 @@
       </c>
       <c r="F30" s="9">
         <f>SUM(Main!$M$42:$M$43)</f>
-        <v>-816.66666666666674</v>
+        <v>-916.66666666666674</v>
       </c>
       <c r="G30" s="9">
         <f>SUM(Main!$M$47:$M$53)</f>
-        <v>-37100</v>
+        <v>-37554.545454545456</v>
       </c>
       <c r="H30" s="9">
         <v>-10000</v>
@@ -3950,11 +3991,11 @@
       </c>
       <c r="M30" s="9">
         <f t="shared" si="0"/>
-        <v>40856.060606060622</v>
+        <v>40301.515151515167</v>
       </c>
       <c r="N30" s="9">
         <f t="shared" si="1"/>
-        <v>489056.06060606078</v>
+        <v>479310.60606060608</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
@@ -3966,11 +4007,11 @@
       </c>
       <c r="F31" s="9">
         <f>SUM(Main!$M$42:$M$43)</f>
-        <v>-816.66666666666674</v>
+        <v>-916.66666666666674</v>
       </c>
       <c r="G31" s="9">
         <f>SUM(Main!$M$47:$M$53)</f>
-        <v>-37100</v>
+        <v>-37554.545454545456</v>
       </c>
       <c r="H31" s="9">
         <v>-10000</v>
@@ -3985,11 +4026,11 @@
       </c>
       <c r="M31" s="9">
         <f t="shared" si="0"/>
-        <v>40856.060606060622</v>
+        <v>40301.515151515167</v>
       </c>
       <c r="N31" s="9">
         <f t="shared" si="1"/>
-        <v>529912.12121212145</v>
+        <v>519612.12121212122</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
@@ -4005,15 +4046,15 @@
       </c>
       <c r="E32" s="9">
         <f>SUM(Main!N31:N37)*12</f>
-        <v>-56537.878787878792</v>
+        <v>-56837.878787878792</v>
       </c>
       <c r="F32" s="9">
         <f>SUM(Main!$M$42:$M$43)</f>
-        <v>-816.66666666666674</v>
+        <v>-916.66666666666674</v>
       </c>
       <c r="G32" s="9">
         <f>SUM(Main!$M$47:$M$53)</f>
-        <v>-37100</v>
+        <v>-37554.545454545456</v>
       </c>
       <c r="H32" s="9">
         <v>-10000</v>
@@ -4028,11 +4069,11 @@
       </c>
       <c r="M32" s="9">
         <f t="shared" si="0"/>
-        <v>-166681.81818181818</v>
+        <v>-167536.36363636359</v>
       </c>
       <c r="N32" s="9">
         <f t="shared" si="1"/>
-        <v>363230.30303030327</v>
+        <v>352075.75757575763</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
@@ -4044,11 +4085,11 @@
       </c>
       <c r="F33" s="9">
         <f>SUM(Main!$N$42:$N$43)</f>
-        <v>-1633.3333333333335</v>
+        <v>-1833.3333333333335</v>
       </c>
       <c r="G33" s="9">
         <f>SUM(Main!$N$47:$N$53)</f>
-        <v>-74800</v>
+        <v>-75709.090909090912</v>
       </c>
       <c r="H33" s="9">
         <v>-10000</v>
@@ -4063,11 +4104,11 @@
       </c>
       <c r="M33" s="9">
         <f t="shared" si="0"/>
-        <v>87021.212121212156</v>
+        <v>85912.121212121245</v>
       </c>
       <c r="N33" s="9">
         <f t="shared" si="1"/>
-        <v>450251.51515151543</v>
+        <v>437987.8787878789</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
@@ -4079,11 +4120,11 @@
       </c>
       <c r="F34" s="9">
         <f>SUM(Main!$N$42:$N$43)</f>
-        <v>-1633.3333333333335</v>
+        <v>-1833.3333333333335</v>
       </c>
       <c r="G34" s="9">
         <f>SUM(Main!$N$47:$N$53)</f>
-        <v>-74800</v>
+        <v>-75709.090909090912</v>
       </c>
       <c r="H34" s="9">
         <v>-10000</v>
@@ -4098,11 +4139,11 @@
       </c>
       <c r="M34" s="9">
         <f t="shared" si="0"/>
-        <v>87021.212121212156</v>
+        <v>85912.121212121245</v>
       </c>
       <c r="N34" s="9">
         <f t="shared" si="1"/>
-        <v>537272.72727272753</v>
+        <v>523900.00000000012</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
@@ -4114,11 +4155,11 @@
       </c>
       <c r="F35" s="9">
         <f>SUM(Main!$N$42:$N$43)</f>
-        <v>-1633.3333333333335</v>
+        <v>-1833.3333333333335</v>
       </c>
       <c r="G35" s="9">
         <f>SUM(Main!$N$47:$N$53)</f>
-        <v>-74800</v>
+        <v>-75709.090909090912</v>
       </c>
       <c r="H35" s="9">
         <v>-10000</v>
@@ -4133,11 +4174,11 @@
       </c>
       <c r="M35" s="9">
         <f t="shared" si="0"/>
-        <v>87021.212121212156</v>
+        <v>85912.121212121245</v>
       </c>
       <c r="N35" s="9">
         <f t="shared" si="1"/>
-        <v>624293.93939393968</v>
+        <v>609812.12121212133</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
@@ -4149,11 +4190,11 @@
       </c>
       <c r="F36" s="9">
         <f>SUM(Main!$N$42:$N$43)</f>
-        <v>-1633.3333333333335</v>
+        <v>-1833.3333333333335</v>
       </c>
       <c r="G36" s="9">
         <f>SUM(Main!$N$47:$N$53)</f>
-        <v>-74800</v>
+        <v>-75709.090909090912</v>
       </c>
       <c r="H36" s="9">
         <v>-10000</v>
@@ -4168,11 +4209,11 @@
       </c>
       <c r="M36" s="9">
         <f t="shared" si="0"/>
-        <v>87021.212121212156</v>
+        <v>85912.121212121245</v>
       </c>
       <c r="N36" s="9">
         <f t="shared" si="1"/>
-        <v>711315.15151515184</v>
+        <v>695724.24242424255</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
@@ -4184,11 +4225,11 @@
       </c>
       <c r="F37" s="9">
         <f>SUM(Main!$N$42:$N$43)</f>
-        <v>-1633.3333333333335</v>
+        <v>-1833.3333333333335</v>
       </c>
       <c r="G37" s="9">
         <f>SUM(Main!$N$47:$N$53)</f>
-        <v>-74800</v>
+        <v>-75709.090909090912</v>
       </c>
       <c r="H37" s="9">
         <v>-10000</v>
@@ -4203,11 +4244,11 @@
       </c>
       <c r="M37" s="9">
         <f t="shared" si="0"/>
-        <v>87021.212121212156</v>
+        <v>85912.121212121245</v>
       </c>
       <c r="N37" s="9">
         <f t="shared" si="1"/>
-        <v>798336.363636364</v>
+        <v>781636.36363636376</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
@@ -4219,11 +4260,11 @@
       </c>
       <c r="F38" s="9">
         <f>SUM(Main!$N$42:$N$43)</f>
-        <v>-1633.3333333333335</v>
+        <v>-1833.3333333333335</v>
       </c>
       <c r="G38" s="9">
         <f>SUM(Main!$N$47:$N$53)</f>
-        <v>-74800</v>
+        <v>-75709.090909090912</v>
       </c>
       <c r="H38" s="9">
         <v>-10000</v>
@@ -4238,11 +4279,11 @@
       </c>
       <c r="M38" s="9">
         <f t="shared" si="0"/>
-        <v>87021.212121212156</v>
+        <v>85912.121212121245</v>
       </c>
       <c r="N38" s="9">
         <f t="shared" si="1"/>
-        <v>885357.57575757615</v>
+        <v>867548.48484848498</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
@@ -4254,11 +4295,11 @@
       </c>
       <c r="F39" s="9">
         <f>SUM(Main!$N$42:$N$43)</f>
-        <v>-1633.3333333333335</v>
+        <v>-1833.3333333333335</v>
       </c>
       <c r="G39" s="9">
         <f>SUM(Main!$N$47:$N$53)</f>
-        <v>-74800</v>
+        <v>-75709.090909090912</v>
       </c>
       <c r="H39" s="9">
         <v>-10000</v>
@@ -4273,11 +4314,11 @@
       </c>
       <c r="M39" s="9">
         <f t="shared" si="0"/>
-        <v>87021.212121212156</v>
+        <v>85912.121212121245</v>
       </c>
       <c r="N39" s="9">
         <f t="shared" si="1"/>
-        <v>972378.78787878831</v>
+        <v>953460.60606060619</v>
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
@@ -4289,11 +4330,11 @@
       </c>
       <c r="F40" s="9">
         <f>SUM(Main!$N$42:$N$43)</f>
-        <v>-1633.3333333333335</v>
+        <v>-1833.3333333333335</v>
       </c>
       <c r="G40" s="9">
         <f>SUM(Main!$N$47:$N$53)</f>
-        <v>-74800</v>
+        <v>-75709.090909090912</v>
       </c>
       <c r="H40" s="9">
         <v>-10000</v>
@@ -4308,11 +4349,11 @@
       </c>
       <c r="M40" s="9">
         <f t="shared" si="0"/>
-        <v>87021.212121212156</v>
+        <v>85912.121212121245</v>
       </c>
       <c r="N40" s="9">
         <f t="shared" si="1"/>
-        <v>1059400.0000000005</v>
+        <v>1039372.7272727274</v>
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
@@ -4324,11 +4365,11 @@
       </c>
       <c r="F41" s="9">
         <f>SUM(Main!$N$42:$N$43)</f>
-        <v>-1633.3333333333335</v>
+        <v>-1833.3333333333335</v>
       </c>
       <c r="G41" s="9">
         <f>SUM(Main!$N$47:$N$53)</f>
-        <v>-74800</v>
+        <v>-75709.090909090912</v>
       </c>
       <c r="H41" s="9">
         <v>-10000</v>
@@ -4343,11 +4384,11 @@
       </c>
       <c r="M41" s="9">
         <f t="shared" si="0"/>
-        <v>87021.212121212156</v>
+        <v>85912.121212121245</v>
       </c>
       <c r="N41" s="9">
         <f t="shared" si="1"/>
-        <v>1146421.2121212126</v>
+        <v>1125284.8484848486</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
@@ -4359,11 +4400,11 @@
       </c>
       <c r="F42" s="9">
         <f>SUM(Main!$N$42:$N$43)</f>
-        <v>-1633.3333333333335</v>
+        <v>-1833.3333333333335</v>
       </c>
       <c r="G42" s="9">
         <f>SUM(Main!$N$47:$N$53)</f>
-        <v>-74800</v>
+        <v>-75709.090909090912</v>
       </c>
       <c r="H42" s="9">
         <v>-10000</v>
@@ -4378,11 +4419,11 @@
       </c>
       <c r="M42" s="9">
         <f t="shared" si="0"/>
-        <v>87021.212121212156</v>
+        <v>85912.121212121245</v>
       </c>
       <c r="N42" s="9">
         <f t="shared" si="1"/>
-        <v>1233442.4242424248</v>
+        <v>1211196.96969697</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
@@ -4394,11 +4435,11 @@
       </c>
       <c r="F43" s="9">
         <f>SUM(Main!$N$42:$N$43)</f>
-        <v>-1633.3333333333335</v>
+        <v>-1833.3333333333335</v>
       </c>
       <c r="G43" s="9">
         <f>SUM(Main!$N$47:$N$53)</f>
-        <v>-74800</v>
+        <v>-75709.090909090912</v>
       </c>
       <c r="H43" s="9">
         <v>-10000</v>
@@ -4413,11 +4454,11 @@
       </c>
       <c r="M43" s="9">
         <f t="shared" si="0"/>
-        <v>87021.212121212156</v>
+        <v>85912.121212121245</v>
       </c>
       <c r="N43" s="9">
         <f t="shared" si="1"/>
-        <v>1320463.6363636369</v>
+        <v>1297109.0909090913</v>
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.25">
@@ -4433,15 +4474,15 @@
       </c>
       <c r="E44" s="9">
         <f>SUM(Main!O31:O37)*12</f>
-        <v>-64537.878787878799</v>
+        <v>-64837.878787878799</v>
       </c>
       <c r="F44" s="9">
         <f>SUM(Main!$N$42:$N$43)</f>
-        <v>-1633.3333333333335</v>
+        <v>-1833.3333333333335</v>
       </c>
       <c r="G44" s="9">
         <f>SUM(Main!$N$47:$N$53)</f>
-        <v>-74800</v>
+        <v>-75709.090909090912</v>
       </c>
       <c r="H44" s="9">
         <v>-10000</v>
@@ -4456,11 +4497,11 @@
       </c>
       <c r="M44" s="9">
         <f t="shared" si="0"/>
-        <v>-93516.666666666657</v>
+        <v>-94925.757575757598</v>
       </c>
       <c r="N44" s="9">
         <f t="shared" si="1"/>
-        <v>1226946.9696969702</v>
+        <v>1202183.3333333337</v>
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
@@ -4472,11 +4513,11 @@
       </c>
       <c r="F45" s="9">
         <f>SUM(Main!$O$42:$O$43)</f>
-        <v>-1633.3333333333335</v>
+        <v>-1833.3333333333335</v>
       </c>
       <c r="G45" s="9">
         <f>SUM(Main!$O$47:$O$53)</f>
-        <v>-106800</v>
+        <v>-108163.63636363637</v>
       </c>
       <c r="H45" s="9">
         <v>-10000</v>
@@ -4491,11 +4532,11 @@
       </c>
       <c r="M45" s="9">
         <f t="shared" si="0"/>
-        <v>135612.12121212124</v>
+        <v>134048.48484848489</v>
       </c>
       <c r="N45" s="9">
         <f t="shared" si="1"/>
-        <v>1362559.0909090915</v>
+        <v>1336231.8181818186</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
@@ -4507,11 +4548,11 @@
       </c>
       <c r="F46" s="9">
         <f>SUM(Main!$O$42:$O$43)</f>
-        <v>-1633.3333333333335</v>
+        <v>-1833.3333333333335</v>
       </c>
       <c r="G46" s="9">
         <f>SUM(Main!$O$47:$O$53)</f>
-        <v>-106800</v>
+        <v>-108163.63636363637</v>
       </c>
       <c r="H46" s="9">
         <v>-10000</v>
@@ -4526,11 +4567,11 @@
       </c>
       <c r="M46" s="9">
         <f t="shared" si="0"/>
-        <v>135612.12121212124</v>
+        <v>134048.48484848489</v>
       </c>
       <c r="N46" s="9">
         <f t="shared" si="1"/>
-        <v>1498171.2121212129</v>
+        <v>1470280.3030303034</v>
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.25">
@@ -4542,11 +4583,11 @@
       </c>
       <c r="F47" s="9">
         <f>SUM(Main!$O$42:$O$43)</f>
-        <v>-1633.3333333333335</v>
+        <v>-1833.3333333333335</v>
       </c>
       <c r="G47" s="9">
         <f>SUM(Main!$O$47:$O$53)</f>
-        <v>-106800</v>
+        <v>-108163.63636363637</v>
       </c>
       <c r="H47" s="9">
         <v>-10000</v>
@@ -4561,11 +4602,11 @@
       </c>
       <c r="M47" s="9">
         <f t="shared" si="0"/>
-        <v>135612.12121212124</v>
+        <v>134048.48484848489</v>
       </c>
       <c r="N47" s="9">
         <f t="shared" si="1"/>
-        <v>1633783.3333333342</v>
+        <v>1604328.7878787883</v>
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.25">
@@ -4577,11 +4618,11 @@
       </c>
       <c r="F48" s="9">
         <f>SUM(Main!$O$42:$O$43)</f>
-        <v>-1633.3333333333335</v>
+        <v>-1833.3333333333335</v>
       </c>
       <c r="G48" s="9">
         <f>SUM(Main!$O$47:$O$53)</f>
-        <v>-106800</v>
+        <v>-108163.63636363637</v>
       </c>
       <c r="H48" s="9">
         <v>-10000</v>
@@ -4596,11 +4637,11 @@
       </c>
       <c r="M48" s="9">
         <f t="shared" si="0"/>
-        <v>135612.12121212124</v>
+        <v>134048.48484848489</v>
       </c>
       <c r="N48" s="9">
         <f t="shared" si="1"/>
-        <v>1769395.4545454555</v>
+        <v>1738377.2727272732</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
@@ -4612,11 +4653,11 @@
       </c>
       <c r="F49" s="9">
         <f>SUM(Main!$O$42:$O$43)</f>
-        <v>-1633.3333333333335</v>
+        <v>-1833.3333333333335</v>
       </c>
       <c r="G49" s="9">
         <f>SUM(Main!$O$47:$O$53)</f>
-        <v>-106800</v>
+        <v>-108163.63636363637</v>
       </c>
       <c r="H49" s="9">
         <v>-10000</v>
@@ -4631,11 +4672,11 @@
       </c>
       <c r="M49" s="9">
         <f t="shared" si="0"/>
-        <v>135612.12121212124</v>
+        <v>134048.48484848489</v>
       </c>
       <c r="N49" s="9">
         <f t="shared" si="1"/>
-        <v>1905007.5757575769</v>
+        <v>1872425.757575758</v>
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
@@ -4647,11 +4688,11 @@
       </c>
       <c r="F50" s="9">
         <f>SUM(Main!$O$42:$O$43)</f>
-        <v>-1633.3333333333335</v>
+        <v>-1833.3333333333335</v>
       </c>
       <c r="G50" s="9">
         <f>SUM(Main!$O$47:$O$53)</f>
-        <v>-106800</v>
+        <v>-108163.63636363637</v>
       </c>
       <c r="H50" s="9">
         <v>-10000</v>
@@ -4666,11 +4707,11 @@
       </c>
       <c r="M50" s="9">
         <f t="shared" si="0"/>
-        <v>135612.12121212124</v>
+        <v>134048.48484848489</v>
       </c>
       <c r="N50" s="9">
         <f t="shared" si="1"/>
-        <v>2040619.6969696982</v>
+        <v>2006474.2424242429</v>
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.25">
@@ -4682,11 +4723,11 @@
       </c>
       <c r="F51" s="9">
         <f>SUM(Main!$O$42:$O$43)</f>
-        <v>-1633.3333333333335</v>
+        <v>-1833.3333333333335</v>
       </c>
       <c r="G51" s="9">
         <f>SUM(Main!$O$47:$O$53)</f>
-        <v>-106800</v>
+        <v>-108163.63636363637</v>
       </c>
       <c r="H51" s="9">
         <v>-10000</v>
@@ -4701,11 +4742,11 @@
       </c>
       <c r="M51" s="9">
         <f t="shared" si="0"/>
-        <v>135612.12121212124</v>
+        <v>134048.48484848489</v>
       </c>
       <c r="N51" s="9">
         <f t="shared" si="1"/>
-        <v>2176231.8181818193</v>
+        <v>2140522.727272728</v>
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.25">
@@ -4717,11 +4758,11 @@
       </c>
       <c r="F52" s="9">
         <f>SUM(Main!$O$42:$O$43)</f>
-        <v>-1633.3333333333335</v>
+        <v>-1833.3333333333335</v>
       </c>
       <c r="G52" s="9">
         <f>SUM(Main!$O$47:$O$53)</f>
-        <v>-106800</v>
+        <v>-108163.63636363637</v>
       </c>
       <c r="H52" s="9">
         <v>-10000</v>
@@ -4736,11 +4777,11 @@
       </c>
       <c r="M52" s="9">
         <f t="shared" si="0"/>
-        <v>135612.12121212124</v>
+        <v>134048.48484848489</v>
       </c>
       <c r="N52" s="9">
         <f t="shared" si="1"/>
-        <v>2311843.9393939404</v>
+        <v>2274571.2121212129</v>
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.25">
@@ -4752,11 +4793,11 @@
       </c>
       <c r="F53" s="9">
         <f>SUM(Main!$O$42:$O$43)</f>
-        <v>-1633.3333333333335</v>
+        <v>-1833.3333333333335</v>
       </c>
       <c r="G53" s="9">
         <f>SUM(Main!$O$47:$O$53)</f>
-        <v>-106800</v>
+        <v>-108163.63636363637</v>
       </c>
       <c r="H53" s="9">
         <v>-10000</v>
@@ -4771,11 +4812,11 @@
       </c>
       <c r="M53" s="9">
         <f t="shared" si="0"/>
-        <v>135612.12121212124</v>
+        <v>134048.48484848489</v>
       </c>
       <c r="N53" s="9">
         <f t="shared" si="1"/>
-        <v>2447456.0606060615</v>
+        <v>2408619.6969696977</v>
       </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.25">
@@ -4787,11 +4828,11 @@
       </c>
       <c r="F54" s="9">
         <f>SUM(Main!$O$42:$O$43)</f>
-        <v>-1633.3333333333335</v>
+        <v>-1833.3333333333335</v>
       </c>
       <c r="G54" s="9">
         <f>SUM(Main!$O$47:$O$53)</f>
-        <v>-106800</v>
+        <v>-108163.63636363637</v>
       </c>
       <c r="H54" s="9">
         <v>-10000</v>
@@ -4806,11 +4847,11 @@
       </c>
       <c r="M54" s="9">
         <f t="shared" si="0"/>
-        <v>135612.12121212124</v>
+        <v>134048.48484848489</v>
       </c>
       <c r="N54" s="9">
         <f t="shared" si="1"/>
-        <v>2583068.1818181826</v>
+        <v>2542668.1818181826</v>
       </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.25">
@@ -4822,11 +4863,11 @@
       </c>
       <c r="F55" s="9">
         <f>SUM(Main!$O$42:$O$43)</f>
-        <v>-1633.3333333333335</v>
+        <v>-1833.3333333333335</v>
       </c>
       <c r="G55" s="9">
         <f>SUM(Main!$O$47:$O$53)</f>
-        <v>-106800</v>
+        <v>-108163.63636363637</v>
       </c>
       <c r="H55" s="9">
         <v>-10000</v>
@@ -4841,11 +4882,11 @@
       </c>
       <c r="M55" s="9">
         <f t="shared" si="0"/>
-        <v>135612.12121212124</v>
+        <v>134048.48484848489</v>
       </c>
       <c r="N55" s="9">
         <f t="shared" si="1"/>
-        <v>2718680.3030303037</v>
+        <v>2676716.6666666674</v>
       </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.25">
@@ -4861,15 +4902,15 @@
       </c>
       <c r="E56" s="9">
         <f>SUM(Main!P31:P37)*12</f>
-        <v>-72537.878787878799</v>
+        <v>-72837.878787878799</v>
       </c>
       <c r="F56" s="9">
         <f>SUM(Main!$O$42:$O$43)</f>
-        <v>-1633.3333333333335</v>
+        <v>-1833.3333333333335</v>
       </c>
       <c r="G56" s="9">
         <f>SUM(Main!$O$47:$O$53)</f>
-        <v>-106800</v>
+        <v>-108163.63636363637</v>
       </c>
       <c r="H56" s="9">
         <v>-10000</v>
@@ -4884,11 +4925,11 @@
       </c>
       <c r="M56" s="9">
         <f t="shared" si="0"/>
-        <v>-52925.757575757452</v>
+        <v>-54789.393939393805</v>
       </c>
       <c r="N56" s="9">
         <f t="shared" si="1"/>
-        <v>2665754.5454545463</v>
+        <v>2621927.2727272734</v>
       </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.25">
@@ -4900,11 +4941,11 @@
       </c>
       <c r="F57" s="9">
         <f>SUM(Main!$P$42:$P$43)</f>
-        <v>-1633.3333333333335</v>
+        <v>-1833.3333333333335</v>
       </c>
       <c r="G57" s="9">
         <f>SUM(Main!$P$47:$P$53)</f>
-        <v>-138800</v>
+        <v>-140618.18181818182</v>
       </c>
       <c r="H57" s="9">
         <v>-10000</v>
@@ -4919,11 +4960,11 @@
       </c>
       <c r="M57" s="9">
         <f t="shared" si="0"/>
-        <v>188293.93939393945</v>
+        <v>186275.75757575763</v>
       </c>
       <c r="N57" s="9">
         <f t="shared" si="1"/>
-        <v>2854048.4848484858</v>
+        <v>2808203.0303030312</v>
       </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.25">
@@ -4935,11 +4976,11 @@
       </c>
       <c r="F58" s="9">
         <f>SUM(Main!$P$42:$P$43)</f>
-        <v>-1633.3333333333335</v>
+        <v>-1833.3333333333335</v>
       </c>
       <c r="G58" s="9">
         <f>SUM(Main!$P$47:$P$53)</f>
-        <v>-138800</v>
+        <v>-140618.18181818182</v>
       </c>
       <c r="H58" s="9">
         <v>-10000</v>
@@ -4954,11 +4995,11 @@
       </c>
       <c r="M58" s="9">
         <f t="shared" si="0"/>
-        <v>188293.93939393945</v>
+        <v>186275.75757575763</v>
       </c>
       <c r="N58" s="9">
         <f t="shared" si="1"/>
-        <v>3042342.4242424252</v>
+        <v>2994478.787878789</v>
       </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.25">
@@ -4970,11 +5011,11 @@
       </c>
       <c r="F59" s="9">
         <f>SUM(Main!$P$42:$P$43)</f>
-        <v>-1633.3333333333335</v>
+        <v>-1833.3333333333335</v>
       </c>
       <c r="G59" s="9">
         <f>SUM(Main!$P$47:$P$53)</f>
-        <v>-138800</v>
+        <v>-140618.18181818182</v>
       </c>
       <c r="H59" s="9">
         <v>-10000</v>
@@ -4989,11 +5030,11 @@
       </c>
       <c r="M59" s="9">
         <f t="shared" si="0"/>
-        <v>188293.93939393945</v>
+        <v>186275.75757575763</v>
       </c>
       <c r="N59" s="9">
         <f t="shared" si="1"/>
-        <v>3230636.3636363647</v>
+        <v>3180754.5454545468</v>
       </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.25">
@@ -5005,11 +5046,11 @@
       </c>
       <c r="F60" s="9">
         <f>SUM(Main!$P$42:$P$43)</f>
-        <v>-1633.3333333333335</v>
+        <v>-1833.3333333333335</v>
       </c>
       <c r="G60" s="9">
         <f>SUM(Main!$P$47:$P$53)</f>
-        <v>-138800</v>
+        <v>-140618.18181818182</v>
       </c>
       <c r="H60" s="9">
         <v>-10000</v>
@@ -5024,11 +5065,11 @@
       </c>
       <c r="M60" s="9">
         <f t="shared" si="0"/>
-        <v>188293.93939393945</v>
+        <v>186275.75757575763</v>
       </c>
       <c r="N60" s="9">
         <f t="shared" si="1"/>
-        <v>3418930.3030303041</v>
+        <v>3367030.3030303046</v>
       </c>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.25">
@@ -5040,11 +5081,11 @@
       </c>
       <c r="F61" s="9">
         <f>SUM(Main!$P$42:$P$43)</f>
-        <v>-1633.3333333333335</v>
+        <v>-1833.3333333333335</v>
       </c>
       <c r="G61" s="9">
         <f>SUM(Main!$P$47:$P$53)</f>
-        <v>-138800</v>
+        <v>-140618.18181818182</v>
       </c>
       <c r="H61" s="9">
         <v>-10000</v>
@@ -5059,11 +5100,11 @@
       </c>
       <c r="M61" s="9">
         <f t="shared" si="0"/>
-        <v>188293.93939393945</v>
+        <v>186275.75757575763</v>
       </c>
       <c r="N61" s="9">
         <f t="shared" si="1"/>
-        <v>3607224.2424242436</v>
+        <v>3553306.0606060624</v>
       </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.25">
@@ -5075,11 +5116,11 @@
       </c>
       <c r="F62" s="9">
         <f>SUM(Main!$P$42:$P$43)</f>
-        <v>-1633.3333333333335</v>
+        <v>-1833.3333333333335</v>
       </c>
       <c r="G62" s="9">
         <f>SUM(Main!$P$47:$P$53)</f>
-        <v>-138800</v>
+        <v>-140618.18181818182</v>
       </c>
       <c r="H62" s="9">
         <v>-10000</v>
@@ -5094,11 +5135,11 @@
       </c>
       <c r="M62" s="9">
         <f t="shared" si="0"/>
-        <v>188293.93939393945</v>
+        <v>186275.75757575763</v>
       </c>
       <c r="N62" s="9">
         <f t="shared" si="1"/>
-        <v>3795518.181818183</v>
+        <v>3739581.8181818202</v>
       </c>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.25">
@@ -5110,11 +5151,11 @@
       </c>
       <c r="F63" s="9">
         <f>SUM(Main!$P$42:$P$43)</f>
-        <v>-1633.3333333333335</v>
+        <v>-1833.3333333333335</v>
       </c>
       <c r="G63" s="9">
         <f>SUM(Main!$P$47:$P$53)</f>
-        <v>-138800</v>
+        <v>-140618.18181818182</v>
       </c>
       <c r="H63" s="9">
         <v>-10000</v>
@@ -5129,11 +5170,11 @@
       </c>
       <c r="M63" s="9">
         <f t="shared" si="0"/>
-        <v>188293.93939393945</v>
+        <v>186275.75757575763</v>
       </c>
       <c r="N63" s="9">
         <f t="shared" si="1"/>
-        <v>3983812.1212121225</v>
+        <v>3925857.575757578</v>
       </c>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.25">
@@ -5145,11 +5186,11 @@
       </c>
       <c r="F64" s="9">
         <f>SUM(Main!$P$42:$P$43)</f>
-        <v>-1633.3333333333335</v>
+        <v>-1833.3333333333335</v>
       </c>
       <c r="G64" s="9">
         <f>SUM(Main!$P$47:$P$53)</f>
-        <v>-138800</v>
+        <v>-140618.18181818182</v>
       </c>
       <c r="H64" s="9">
         <v>-10000</v>
@@ -5164,11 +5205,11 @@
       </c>
       <c r="M64" s="9">
         <f t="shared" si="0"/>
-        <v>188293.93939393945</v>
+        <v>186275.75757575763</v>
       </c>
       <c r="N64" s="9">
         <f t="shared" si="1"/>
-        <v>4172106.0606060619</v>
+        <v>4112133.3333333358</v>
       </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.25">
@@ -5180,11 +5221,11 @@
       </c>
       <c r="F65" s="9">
         <f>SUM(Main!$P$42:$P$43)</f>
-        <v>-1633.3333333333335</v>
+        <v>-1833.3333333333335</v>
       </c>
       <c r="G65" s="9">
         <f>SUM(Main!$P$47:$P$53)</f>
-        <v>-138800</v>
+        <v>-140618.18181818182</v>
       </c>
       <c r="H65" s="9">
         <v>-10000</v>
@@ -5199,11 +5240,11 @@
       </c>
       <c r="M65" s="9">
         <f t="shared" si="0"/>
-        <v>188293.93939393945</v>
+        <v>186275.75757575763</v>
       </c>
       <c r="N65" s="9">
         <f t="shared" si="1"/>
-        <v>4360400.0000000019</v>
+        <v>4298409.0909090936</v>
       </c>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.25">
@@ -5215,11 +5256,11 @@
       </c>
       <c r="F66" s="9">
         <f>SUM(Main!$P$42:$P$43)</f>
-        <v>-1633.3333333333335</v>
+        <v>-1833.3333333333335</v>
       </c>
       <c r="G66" s="9">
         <f>SUM(Main!$P$47:$P$53)</f>
-        <v>-138800</v>
+        <v>-140618.18181818182</v>
       </c>
       <c r="H66" s="9">
         <v>-10000</v>
@@ -5234,11 +5275,11 @@
       </c>
       <c r="M66" s="9">
         <f t="shared" si="0"/>
-        <v>188293.93939393945</v>
+        <v>186275.75757575763</v>
       </c>
       <c r="N66" s="9">
         <f t="shared" si="1"/>
-        <v>4548693.9393939413</v>
+        <v>4484684.8484848514</v>
       </c>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.25">
@@ -5250,11 +5291,11 @@
       </c>
       <c r="F67" s="9">
         <f>SUM(Main!$P$42:$P$43)</f>
-        <v>-1633.3333333333335</v>
+        <v>-1833.3333333333335</v>
       </c>
       <c r="G67" s="9">
         <f>SUM(Main!$P$47:$P$53)</f>
-        <v>-138800</v>
+        <v>-140618.18181818182</v>
       </c>
       <c r="H67" s="9">
         <v>-10000</v>
@@ -5269,11 +5310,11 @@
       </c>
       <c r="M67" s="9">
         <f t="shared" si="0"/>
-        <v>188293.93939393945</v>
+        <v>186275.75757575763</v>
       </c>
       <c r="N67" s="9">
         <f t="shared" si="1"/>
-        <v>4736987.8787878808</v>
+        <v>4670960.6060606092</v>
       </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.25">
@@ -5285,11 +5326,11 @@
       </c>
       <c r="F68" s="9">
         <f>SUM(Main!$P$42:$P$43)</f>
-        <v>-1633.3333333333335</v>
+        <v>-1833.3333333333335</v>
       </c>
       <c r="G68" s="9">
         <f>SUM(Main!$P$47:$P$53)</f>
-        <v>-138800</v>
+        <v>-140618.18181818182</v>
       </c>
       <c r="H68" s="9">
         <v>-10000</v>
@@ -5304,15 +5345,94 @@
       </c>
       <c r="M68" s="9">
         <f t="shared" si="0"/>
-        <v>188293.93939393945</v>
+        <v>186275.75757575763</v>
       </c>
       <c r="N68" s="9">
         <f t="shared" si="1"/>
-        <v>4925281.8181818202</v>
+        <v>4857236.363636367</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FFFFC000"/>
+  </sheetPr>
+  <dimension ref="A10:G13"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>65</v>
+      </c>
+      <c r="B10" s="22">
+        <f>Main!B1</f>
+        <v>132</v>
+      </c>
+      <c r="D10" t="s">
+        <v>67</v>
+      </c>
+      <c r="E10" s="6">
+        <v>10</v>
+      </c>
+      <c r="F10" s="6">
+        <v>15</v>
+      </c>
+      <c r="G10" s="6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="22">
+        <f>Main!D8</f>
+        <v>150</v>
+      </c>
+      <c r="D11" t="s">
+        <v>68</v>
+      </c>
+      <c r="E11" s="23">
+        <f>E10*30*$B$11/$B$10*$B$13+$B$12</f>
+        <v>320.4545454545455</v>
+      </c>
+      <c r="F11" s="23">
+        <f>F10*30*$B$11/$B$10*$B$13+$B$12</f>
+        <v>405.68181818181819</v>
+      </c>
+      <c r="G11" s="23">
+        <f>G10*30*$B$11/$B$10*$B$13+$B$12</f>
+        <v>490.90909090909093</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>63</v>
+      </c>
+      <c r="B12" s="24">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>64</v>
+      </c>
+      <c r="B13" s="25">
+        <v>0.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="256" orientation="portrait" horizontalDpi="203" verticalDpi="203" r:id="rId1"/>
+</worksheet>
 </file>
--- a/data/Delivery.xlsx
+++ b/data/Delivery.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="67">
   <si>
     <t>Average order value</t>
   </si>
@@ -124,9 +124,6 @@
     <t>USD =</t>
   </si>
   <si>
-    <t>Revenue share with SyTRA</t>
-  </si>
-  <si>
     <t>domain, firebase, …</t>
   </si>
   <si>
@@ -209,9 +206,6 @@
   </si>
   <si>
     <t>Bills</t>
-  </si>
-  <si>
-    <t>SyTRA+Tax</t>
   </si>
   <si>
     <t>Number of Orders</t>
@@ -387,7 +381,6 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="3" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -400,6 +393,7 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="6" fillId="5" borderId="0" xfId="6" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="6" fillId="5" borderId="0" xfId="6" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="3" fillId="2" borderId="1" xfId="3" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="Accent3" xfId="4" builtinId="37"/>
@@ -696,184 +690,184 @@
                 <c:formatCode>_("$"* #,##0_);_("$"* \(#,##0\);_("$"* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="60"/>
                 <c:pt idx="0">
-                  <c:v>5116.6666666666679</c:v>
+                  <c:v>10874.242424242424</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>19481.818181818187</c:v>
+                  <c:v>21284.848484848488</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>33846.969696969711</c:v>
+                  <c:v>31695.454545454551</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>48212.12121212123</c:v>
+                  <c:v>42106.060606060615</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>62577.27272727275</c:v>
+                  <c:v>52516.666666666679</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>76942.424242424269</c:v>
+                  <c:v>62927.272727272742</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>91307.575757575789</c:v>
+                  <c:v>73337.878787878813</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>105672.72727272731</c:v>
+                  <c:v>83748.484848484877</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>120037.87878787883</c:v>
+                  <c:v>94159.090909090941</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>134403.03030303033</c:v>
+                  <c:v>104569.696969697</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>148768.18181818185</c:v>
+                  <c:v>114980.30303030307</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>76295.454545454559</c:v>
+                  <c:v>14477.272727272793</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>116596.96969696973</c:v>
+                  <c:v>48915.151515151592</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>156898.48484848489</c:v>
+                  <c:v>83353.030303030391</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>197200.00000000006</c:v>
+                  <c:v>117790.90909090919</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>237501.51515151522</c:v>
+                  <c:v>152228.78787878799</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>277803.03030303039</c:v>
+                  <c:v>186666.6666666668</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>318104.54545454553</c:v>
+                  <c:v>221104.54545454559</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>358406.06060606067</c:v>
+                  <c:v>255542.42424242437</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>398707.5757575758</c:v>
+                  <c:v>289980.30303030316</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>439009.09090909094</c:v>
+                  <c:v>324418.18181818194</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>479310.60606060608</c:v>
+                  <c:v>358856.06060606072</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>519612.12121212122</c:v>
+                  <c:v>393293.93939393951</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>352075.75757575763</c:v>
+                  <c:v>98030.303030303156</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>437987.8787878789</c:v>
+                  <c:v>201033.33333333349</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>523900.00000000012</c:v>
+                  <c:v>304036.36363636382</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>609812.12121212133</c:v>
+                  <c:v>407039.39393939415</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>695724.24242424255</c:v>
+                  <c:v>510042.42424242449</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>781636.36363636376</c:v>
+                  <c:v>613045.45454545482</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>867548.48484848498</c:v>
+                  <c:v>716048.4848484851</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>953460.60606060619</c:v>
+                  <c:v>819051.51515151537</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>1039372.7272727274</c:v>
+                  <c:v>922054.54545454565</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>1125284.8484848486</c:v>
+                  <c:v>1025057.5757575759</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>1211196.96969697</c:v>
+                  <c:v>1128060.6060606062</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>1297109.0909090913</c:v>
+                  <c:v>1231063.6363636365</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>1202183.3333333337</c:v>
+                  <c:v>1098077.2727272729</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>1336231.8181818186</c:v>
+                  <c:v>1251534.8484848486</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>1470280.3030303034</c:v>
+                  <c:v>1404992.4242424243</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>1604328.7878787883</c:v>
+                  <c:v>1558450</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>1738377.2727272732</c:v>
+                  <c:v>1711907.5757575757</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>1872425.757575758</c:v>
+                  <c:v>1865365.1515151514</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>2006474.2424242429</c:v>
+                  <c:v>2018822.7272727271</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>2140522.727272728</c:v>
+                  <c:v>2172280.3030303027</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>2274571.2121212129</c:v>
+                  <c:v>2325737.8787878784</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>2408619.6969696977</c:v>
+                  <c:v>2479195.4545454541</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>2542668.1818181826</c:v>
+                  <c:v>2632653.0303030298</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>2676716.6666666674</c:v>
+                  <c:v>2786110.6060606055</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>2621927.2727272734</c:v>
+                  <c:v>2852366.666666666</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>2808203.0303030312</c:v>
+                  <c:v>3005824.2424242417</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>2994478.787878789</c:v>
+                  <c:v>3159281.8181818174</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>3180754.5454545468</c:v>
+                  <c:v>3312739.3939393931</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>3367030.3030303046</c:v>
+                  <c:v>3466196.9696969688</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>3553306.0606060624</c:v>
+                  <c:v>3619654.5454545445</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>3739581.8181818202</c:v>
+                  <c:v>3773112.1212121202</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>3925857.575757578</c:v>
+                  <c:v>3926569.6969696959</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>4112133.3333333358</c:v>
+                  <c:v>4080027.2727272715</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>4298409.0909090936</c:v>
+                  <c:v>4233484.8484848477</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>4484684.8484848514</c:v>
+                  <c:v>4386942.4242424238</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>4670960.6060606092</c:v>
+                  <c:v>4540400</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>4857236.363636367</c:v>
+                  <c:v>4693857.5757575762</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1958,18 +1952,18 @@
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="K2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L2" t="s">
+        <v>42</v>
+      </c>
+      <c r="N2" t="s">
         <v>43</v>
-      </c>
-      <c r="N2" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="K3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L3" s="16">
         <v>1</v>
@@ -1989,7 +1983,7 @@
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="K4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L4" s="7">
         <v>1</v>
@@ -2008,24 +2002,11 @@
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="K5" t="s">
-        <v>32</v>
-      </c>
-      <c r="L5" s="15">
-        <v>0</v>
-      </c>
-      <c r="M5" s="15">
-        <v>0.05</v>
-      </c>
-      <c r="N5" s="15">
-        <v>0.1</v>
-      </c>
-      <c r="O5" s="15">
-        <v>0.15</v>
-      </c>
-      <c r="P5" s="15">
-        <v>0.15</v>
-      </c>
+      <c r="L5" s="15"/>
+      <c r="M5" s="15"/>
+      <c r="N5" s="15"/>
+      <c r="O5" s="15"/>
+      <c r="P5" s="15"/>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
@@ -2043,19 +2024,19 @@
         <v>18</v>
       </c>
       <c r="L7" s="13">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="M7" s="13">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="N7" s="13">
-        <v>160</v>
+        <v>250</v>
       </c>
       <c r="O7" s="13">
-        <v>240</v>
+        <v>350</v>
       </c>
       <c r="P7" s="13">
-        <v>320</v>
+        <v>350</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
@@ -2066,7 +2047,7 @@
         <v>150</v>
       </c>
       <c r="K8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L8" s="3">
         <v>2</v>
@@ -2089,7 +2070,7 @@
         <v>0</v>
       </c>
       <c r="D9" s="8">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="K9" t="s">
         <v>4</v>
@@ -2118,7 +2099,7 @@
         <v>15</v>
       </c>
       <c r="K10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L10" s="3">
         <v>2</v>
@@ -2138,7 +2119,7 @@
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="K11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L11" s="3">
         <v>1</v>
@@ -2190,45 +2171,60 @@
         <v>1</v>
       </c>
       <c r="N13" s="3">
-        <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O13" s="3">
-        <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P13" s="3">
-        <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="K15" t="s">
-        <v>62</v>
-      </c>
-      <c r="L15" s="21">
-        <f>L7*$D$10*30</f>
-        <v>18000</v>
-      </c>
-      <c r="M15" s="21">
-        <f>M7*$D$10*30</f>
-        <v>36000</v>
-      </c>
-      <c r="N15" s="21">
-        <f>N7*$D$10*30</f>
-        <v>72000</v>
-      </c>
-      <c r="O15" s="21">
-        <f>O7*$D$10*30</f>
-        <v>108000</v>
-      </c>
-      <c r="P15" s="21">
-        <f>P7*$D$10*30</f>
-        <v>144000</v>
+        <v>34</v>
+      </c>
+      <c r="L15" s="25">
+        <v>0</v>
+      </c>
+      <c r="M15" s="25">
+        <v>500000</v>
+      </c>
+      <c r="N15" s="25">
+        <v>1000000</v>
+      </c>
+      <c r="O15" s="25">
+        <v>1500000</v>
+      </c>
+      <c r="P15" s="25">
+        <v>1500000</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C16"/>
+      <c r="K16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L16" s="20">
+        <f>L7*$D$10*30</f>
+        <v>22500</v>
+      </c>
+      <c r="M16" s="20">
+        <f>M7*$D$10*30</f>
+        <v>45000</v>
+      </c>
+      <c r="N16" s="20">
+        <f>N7*$D$10*30</f>
+        <v>112500</v>
+      </c>
+      <c r="O16" s="20">
+        <f>O7*$D$10*30</f>
+        <v>157500</v>
+      </c>
+      <c r="P16" s="20">
+        <f>P7*$D$10*30</f>
+        <v>157500</v>
+      </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C17"/>
@@ -2237,28 +2233,28 @@
       </c>
       <c r="L17" s="9">
         <f>L7*30*$D$10*($D$9*$D$7+$D$8/$B$1)</f>
-        <v>47454.545454545463</v>
+        <v>48068.181818181823</v>
       </c>
       <c r="M17" s="9">
         <f>M7*30*$D$10*($D$9*$D$7+$D$8/$B$1)</f>
-        <v>94909.090909090926</v>
+        <v>96136.363636363647</v>
       </c>
       <c r="N17" s="9">
         <f>N7*30*$D$10*($D$9*$D$7+$D$8/$B$1)</f>
-        <v>189818.18181818185</v>
+        <v>240340.90909090912</v>
       </c>
       <c r="O17" s="9">
         <f>O7*30*$D$10*($D$9*$D$7+$D$8/$B$1)</f>
-        <v>284727.27272727276</v>
+        <v>336477.27272727276</v>
       </c>
       <c r="P17" s="9">
         <f>P7*30*$D$10*($D$9*$D$7+$D$8/$B$1)</f>
-        <v>379636.36363636371</v>
+        <v>336477.27272727276</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="L18" s="9"/>
       <c r="M18" s="9"/>
@@ -2280,30 +2276,30 @@
       </c>
       <c r="C20" s="7">
         <f>L7</f>
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="D20" s="5">
         <v>1300</v>
       </c>
       <c r="L20" s="9">
         <f>-$D$20*L7/$D$19/12</f>
-        <v>-866.66666666666663</v>
+        <v>-1083.3333333333333</v>
       </c>
       <c r="M20" s="9">
         <f>-$D$20*M7/$D$19/12</f>
-        <v>-1733.3333333333333</v>
+        <v>-2166.6666666666665</v>
       </c>
       <c r="N20" s="9">
         <f>-$D$20*N7/$D$19/12</f>
-        <v>-3466.6666666666665</v>
+        <v>-5416.666666666667</v>
       </c>
       <c r="O20" s="9">
         <f>-$D$20*O7/$D$19/12</f>
-        <v>-5200</v>
+        <v>-7583.333333333333</v>
       </c>
       <c r="P20" s="9">
         <f>-$D$20*P7/$D$19/12</f>
-        <v>-6933.333333333333</v>
+        <v>-7583.333333333333</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
@@ -2455,71 +2451,70 @@
       </c>
       <c r="L26" s="9">
         <f>-$D$26*L7/$D$19/12</f>
-        <v>-100</v>
+        <v>-125</v>
       </c>
       <c r="M26" s="9">
         <f>-$D$26*M7/$D$19/12</f>
-        <v>-200</v>
+        <v>-250</v>
       </c>
       <c r="N26" s="9">
         <f>-$D$26*N7/$D$19/12</f>
-        <v>-400</v>
+        <v>-625</v>
       </c>
       <c r="O26" s="9">
         <f>-$D$26*O7/$D$19/12</f>
-        <v>-600</v>
+        <v>-875</v>
       </c>
       <c r="P26" s="9">
         <f>-$D$26*P7/$D$19/12</f>
-        <v>-800</v>
+        <v>-875</v>
       </c>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C27" s="14">
-        <f>1000+5000</f>
-        <v>6000</v>
+        <v>500000</v>
       </c>
       <c r="D27" s="11">
         <f>C27/B1</f>
-        <v>45.454545454545453</v>
+        <v>3787.878787878788</v>
       </c>
       <c r="L27" s="9">
         <f>-$D$27/$D$19/12</f>
-        <v>-0.75757575757575746</v>
+        <v>-63.131313131313135</v>
       </c>
       <c r="M27" s="9">
         <f t="shared" ref="M27:P27" si="1">-$D$27/$D$19/12</f>
-        <v>-0.75757575757575746</v>
+        <v>-63.131313131313135</v>
       </c>
       <c r="N27" s="9">
         <f t="shared" si="1"/>
-        <v>-0.75757575757575746</v>
+        <v>-63.131313131313135</v>
       </c>
       <c r="O27" s="9">
         <f t="shared" si="1"/>
-        <v>-0.75757575757575746</v>
+        <v>-63.131313131313135</v>
       </c>
       <c r="P27" s="9">
         <f t="shared" si="1"/>
-        <v>-0.75757575757575746</v>
+        <v>-63.131313131313135</v>
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="D28" s="10">
         <f>SUM(D21:D25)+D27+D20*C20+C20*D26</f>
-        <v>95045.454545454544</v>
+        <v>113287.87878787878</v>
       </c>
       <c r="E28" s="10">
         <f>D28-SUM(L31:L37)*12</f>
-        <v>119883.33333333333</v>
+        <v>139125.75757575757</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.25">
@@ -2624,7 +2619,7 @@
         <v>500</v>
       </c>
       <c r="E34" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L34" s="9">
         <f>-$D$34/12</f>
@@ -2649,7 +2644,7 @@
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C35" s="14">
         <v>5000</v>
@@ -2694,23 +2689,23 @@
       </c>
       <c r="L36" s="9">
         <f>-$D$36/12*L7</f>
-        <v>-333.33333333333337</v>
+        <v>-416.66666666666669</v>
       </c>
       <c r="M36" s="9">
         <f>-$D$36/12*M7</f>
-        <v>-666.66666666666674</v>
+        <v>-833.33333333333337</v>
       </c>
       <c r="N36" s="9">
         <f>-$D$36/12*N7</f>
-        <v>-1333.3333333333335</v>
+        <v>-2083.3333333333335</v>
       </c>
       <c r="O36" s="9">
         <f>-$D$36/12*O7</f>
-        <v>-2000.0000000000002</v>
+        <v>-2916.666666666667</v>
       </c>
       <c r="P36" s="9">
         <f>-$D$36/12*P7</f>
-        <v>-2666.666666666667</v>
+        <v>-2916.666666666667</v>
       </c>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.25">
@@ -2742,6 +2737,31 @@
       <c r="P37" s="9">
         <f>-$D$37/12*P7</f>
         <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>34</v>
+      </c>
+      <c r="L38" s="9">
+        <f>-L15/$B$1/12</f>
+        <v>0</v>
+      </c>
+      <c r="M38" s="9">
+        <f>-M15/$B$1/12</f>
+        <v>-315.65656565656565</v>
+      </c>
+      <c r="N38" s="9">
+        <f t="shared" ref="N38:P38" si="5">-N15/$B$1/12</f>
+        <v>-631.31313131313129</v>
+      </c>
+      <c r="O38" s="9">
+        <f t="shared" si="5"/>
+        <v>-946.969696969697</v>
+      </c>
+      <c r="P38" s="9">
+        <f t="shared" si="5"/>
+        <v>-946.969696969697</v>
       </c>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.25">
@@ -2755,38 +2775,38 @@
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D41" s="10"/>
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D42" s="8">
         <v>500</v>
       </c>
       <c r="E42" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L42" s="9">
         <f>-$D$42*L3</f>
         <v>-500</v>
       </c>
       <c r="M42" s="9">
-        <f t="shared" ref="M42:P42" si="5">-$D$42*M3</f>
+        <f t="shared" ref="M42:P42" si="6">-$D$42*M3</f>
         <v>-500</v>
       </c>
       <c r="N42" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-1000</v>
       </c>
       <c r="O42" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-1000</v>
       </c>
       <c r="P42" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-1000</v>
       </c>
     </row>
@@ -2840,27 +2860,27 @@
         <v>0.5</v>
       </c>
       <c r="F47" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="L47" s="9">
-        <f t="shared" ref="L47:P53" si="6">-$D47*L7</f>
-        <v>-16227.272727272728</v>
+        <f t="shared" ref="L47:P53" si="7">-$D47*L7</f>
+        <v>-20284.090909090908</v>
       </c>
       <c r="M47" s="9">
-        <f t="shared" si="6"/>
-        <v>-32454.545454545456</v>
+        <f t="shared" si="7"/>
+        <v>-40568.181818181816</v>
       </c>
       <c r="N47" s="9">
-        <f t="shared" si="6"/>
-        <v>-64909.090909090912</v>
+        <f t="shared" si="7"/>
+        <v>-101420.45454545454</v>
       </c>
       <c r="O47" s="9">
-        <f t="shared" si="6"/>
-        <v>-97363.636363636368</v>
+        <f t="shared" si="7"/>
+        <v>-141988.63636363635</v>
       </c>
       <c r="P47" s="9">
-        <f t="shared" si="6"/>
-        <v>-129818.18181818182</v>
+        <f t="shared" si="7"/>
+        <v>-141988.63636363635</v>
       </c>
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.25">
@@ -2872,23 +2892,23 @@
         <v>400</v>
       </c>
       <c r="L48" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-800</v>
       </c>
       <c r="M48" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-1600</v>
       </c>
       <c r="N48" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-3200</v>
       </c>
       <c r="O48" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-3200</v>
       </c>
       <c r="P48" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-3200</v>
       </c>
     </row>
@@ -2901,23 +2921,23 @@
         <v>400</v>
       </c>
       <c r="L49" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-800</v>
       </c>
       <c r="M49" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-800</v>
       </c>
       <c r="N49" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-2400</v>
       </c>
       <c r="O49" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-2400</v>
       </c>
       <c r="P49" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-2400</v>
       </c>
     </row>
@@ -2930,52 +2950,52 @@
         <v>400</v>
       </c>
       <c r="L50" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-800</v>
       </c>
       <c r="M50" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-800</v>
       </c>
       <c r="N50" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-2000</v>
       </c>
       <c r="O50" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-2000</v>
       </c>
       <c r="P50" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-2000</v>
       </c>
     </row>
     <row r="51" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C51"/>
       <c r="D51" s="8">
         <v>600</v>
       </c>
       <c r="L51" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-600</v>
       </c>
       <c r="M51" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-600</v>
       </c>
       <c r="N51" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-600</v>
       </c>
       <c r="O51" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-600</v>
       </c>
       <c r="P51" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-600</v>
       </c>
     </row>
@@ -2988,23 +3008,23 @@
         <v>400</v>
       </c>
       <c r="L52" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-400</v>
       </c>
       <c r="M52" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-800</v>
       </c>
       <c r="N52" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-1600</v>
       </c>
       <c r="O52" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-1600</v>
       </c>
       <c r="P52" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-1600</v>
       </c>
     </row>
@@ -3017,81 +3037,63 @@
         <v>500</v>
       </c>
       <c r="L53" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-500</v>
       </c>
       <c r="M53" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-500</v>
       </c>
       <c r="N53" s="9">
-        <f t="shared" si="6"/>
-        <v>-1000</v>
+        <f t="shared" si="7"/>
+        <v>-1500</v>
       </c>
       <c r="O53" s="9">
-        <f t="shared" si="6"/>
-        <v>-1000</v>
+        <f t="shared" si="7"/>
+        <v>-1500</v>
       </c>
       <c r="P53" s="9">
-        <f t="shared" si="6"/>
-        <v>-1000</v>
+        <f t="shared" si="7"/>
+        <v>-1500</v>
       </c>
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>46</v>
-      </c>
-      <c r="D56" s="20">
+        <v>45</v>
+      </c>
+      <c r="D56" s="19">
         <v>0.1</v>
       </c>
       <c r="L56" s="9">
-        <f>-L15*$D$8/$B$1*$D$56</f>
-        <v>-2045.4545454545457</v>
+        <f>-L16*$D$8/$B$1*$D$56</f>
+        <v>-2556.818181818182</v>
       </c>
       <c r="M56" s="9">
-        <f>-M15*$D$8/$B$1*$D$56</f>
-        <v>-4090.9090909090914</v>
+        <f>-M16*$D$8/$B$1*$D$56</f>
+        <v>-5113.636363636364</v>
       </c>
       <c r="N56" s="9">
-        <f>-N15*$D$8/$B$1*$D$56</f>
-        <v>-8181.8181818181829</v>
+        <f>-N16*$D$8/$B$1*$D$56</f>
+        <v>-12784.09090909091</v>
       </c>
       <c r="O56" s="9">
-        <f>-O15*$D$8/$B$1*$D$56</f>
-        <v>-12272.727272727272</v>
+        <f>-O16*$D$8/$B$1*$D$56</f>
+        <v>-17897.727272727276</v>
       </c>
       <c r="P56" s="9">
-        <f>-P15*$D$8/$B$1*$D$56</f>
-        <v>-16363.636363636366</v>
+        <f>-P16*$D$8/$B$1*$D$56</f>
+        <v>-17897.727272727276</v>
       </c>
     </row>
     <row r="57" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C57"/>
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="K58" t="s">
-        <v>35</v>
-      </c>
-      <c r="L58" s="9">
-        <f>-L15*L5*$D$8/$B$1</f>
-        <v>0</v>
-      </c>
-      <c r="M58" s="9">
-        <f>-M15*M5*$D$8/$B$1</f>
-        <v>-2045.4545454545455</v>
-      </c>
-      <c r="N58" s="9">
-        <f>-N15*N5*$D$8/$B$1</f>
-        <v>-8181.818181818182</v>
-      </c>
-      <c r="O58" s="9">
-        <f>-O15*O5*$D$8/$B$1</f>
-        <v>-18409.090909090908</v>
-      </c>
-      <c r="P58" s="9">
-        <f>-P15*P5*$D$8/$B$1</f>
-        <v>-24545.454545454544</v>
-      </c>
+      <c r="L58" s="9"/>
+      <c r="M58" s="9"/>
+      <c r="N58" s="9"/>
+      <c r="O58" s="9"/>
+      <c r="P58" s="9"/>
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.25">
       <c r="M59" s="9"/>
@@ -3101,27 +3103,27 @@
     </row>
     <row r="62" spans="1:16" x14ac:dyDescent="0.25">
       <c r="K62" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L62" s="10">
         <f>SUM(L17:L60)</f>
-        <v>20711.237373737378</v>
+        <v>16369.318181818182</v>
       </c>
       <c r="M62" s="10">
         <f>SUM(M17:M60)</f>
-        <v>45347.601010101047</v>
+        <v>38455.934343434375</v>
       </c>
       <c r="N62" s="10">
         <f>SUM(N17:N60)</f>
-        <v>86108.20707070714</v>
+        <v>99580.429292929344</v>
       </c>
       <c r="O62" s="10">
         <f>SUM(O17:O60)</f>
-        <v>131644.5707070707</v>
+        <v>146469.31818181815</v>
       </c>
       <c r="P62" s="10">
         <f>SUM(P17:P60)</f>
-        <v>181271.84343434346</v>
+        <v>146469.31818181815</v>
       </c>
     </row>
     <row r="64" spans="1:16" x14ac:dyDescent="0.25">
@@ -3188,44 +3190,44 @@
     <col min="14" max="14" width="13.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="8" spans="1:14" s="18" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A8" s="19" t="s">
+    <row r="8" spans="1:14" s="17" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A8" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="B8" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="D8" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="E8" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="F8" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="G8" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="H8" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="I8" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="J8" s="18"/>
+      <c r="K8" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="L8" s="18"/>
+      <c r="M8" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="B8" s="19" t="s">
-        <v>42</v>
-      </c>
-      <c r="C8" s="19" t="s">
+      <c r="N8" s="18" t="s">
         <v>51</v>
-      </c>
-      <c r="D8" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="E8" s="19" t="s">
-        <v>53</v>
-      </c>
-      <c r="F8" s="19" t="s">
-        <v>57</v>
-      </c>
-      <c r="G8" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="H8" s="19" t="s">
-        <v>55</v>
-      </c>
-      <c r="I8" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="J8" s="19"/>
-      <c r="K8" s="19" t="s">
-        <v>56</v>
-      </c>
-      <c r="L8" s="19"/>
-      <c r="M8" s="19" t="s">
-        <v>50</v>
-      </c>
-      <c r="N8" s="19" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
@@ -3236,23 +3238,23 @@
         <v>1</v>
       </c>
       <c r="C9" s="9">
-        <v>125000</v>
+        <v>150000</v>
       </c>
       <c r="D9" s="9">
         <f>SUM(Main!L20:L27)*12*Main!D19</f>
-        <v>-95045.454545454544</v>
+        <v>-113287.87878787878</v>
       </c>
       <c r="E9" s="9">
-        <f>SUM(Main!L31:L37)*12</f>
-        <v>-24837.878787878788</v>
+        <f>SUM(Main!L31:L38)*12</f>
+        <v>-25837.878787878792</v>
       </c>
       <c r="M9" s="9">
         <f>SUM(C9:K9)</f>
-        <v>5116.6666666666679</v>
+        <v>10874.242424242424</v>
       </c>
       <c r="N9" s="9">
         <f>M9</f>
-        <v>5116.6666666666679</v>
+        <v>10874.242424242424</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
@@ -3268,26 +3270,26 @@
       </c>
       <c r="G10" s="9">
         <f>SUM(Main!$L$47:$L$53)</f>
-        <v>-20127.272727272728</v>
+        <v>-24184.090909090908</v>
       </c>
       <c r="H10" s="9">
         <v>-10000</v>
       </c>
       <c r="I10" s="9">
         <f>Main!$L$58+Main!$L$56</f>
-        <v>-2045.4545454545457</v>
+        <v>-2556.818181818182</v>
       </c>
       <c r="K10" s="9">
         <f>Main!$L$17</f>
-        <v>47454.545454545463</v>
+        <v>48068.181818181823</v>
       </c>
       <c r="M10" s="9">
         <f>SUM(C10:K10)</f>
-        <v>14365.15151515152</v>
+        <v>10410.606060606064</v>
       </c>
       <c r="N10" s="9">
         <f>N9+M10</f>
-        <v>19481.818181818187</v>
+        <v>21284.848484848488</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
@@ -3303,26 +3305,26 @@
       </c>
       <c r="G11" s="9">
         <f>SUM(Main!$L$47:$L$53)</f>
-        <v>-20127.272727272728</v>
+        <v>-24184.090909090908</v>
       </c>
       <c r="H11" s="9">
         <v>-10000</v>
       </c>
       <c r="I11" s="9">
         <f>Main!$L$58+Main!$L$56</f>
-        <v>-2045.4545454545457</v>
+        <v>-2556.818181818182</v>
       </c>
       <c r="K11" s="9">
         <f>Main!$L$17</f>
-        <v>47454.545454545463</v>
+        <v>48068.181818181823</v>
       </c>
       <c r="M11" s="9">
         <f t="shared" ref="M11:M68" si="0">SUM(C11:K11)</f>
-        <v>14365.15151515152</v>
+        <v>10410.606060606064</v>
       </c>
       <c r="N11" s="9">
         <f t="shared" ref="N11:N68" si="1">N10+M11</f>
-        <v>33846.969696969711</v>
+        <v>31695.454545454551</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
@@ -3338,26 +3340,26 @@
       </c>
       <c r="G12" s="9">
         <f>SUM(Main!$L$47:$L$53)</f>
-        <v>-20127.272727272728</v>
+        <v>-24184.090909090908</v>
       </c>
       <c r="H12" s="9">
         <v>-10000</v>
       </c>
       <c r="I12" s="9">
         <f>Main!$L$58+Main!$L$56</f>
-        <v>-2045.4545454545457</v>
+        <v>-2556.818181818182</v>
       </c>
       <c r="K12" s="9">
         <f>Main!$L$17</f>
-        <v>47454.545454545463</v>
+        <v>48068.181818181823</v>
       </c>
       <c r="M12" s="9">
         <f t="shared" si="0"/>
-        <v>14365.15151515152</v>
+        <v>10410.606060606064</v>
       </c>
       <c r="N12" s="9">
         <f t="shared" si="1"/>
-        <v>48212.12121212123</v>
+        <v>42106.060606060615</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
@@ -3373,26 +3375,26 @@
       </c>
       <c r="G13" s="9">
         <f>SUM(Main!$L$47:$L$53)</f>
-        <v>-20127.272727272728</v>
+        <v>-24184.090909090908</v>
       </c>
       <c r="H13" s="9">
         <v>-10000</v>
       </c>
       <c r="I13" s="9">
         <f>Main!$L$58+Main!$L$56</f>
-        <v>-2045.4545454545457</v>
+        <v>-2556.818181818182</v>
       </c>
       <c r="K13" s="9">
         <f>Main!$L$17</f>
-        <v>47454.545454545463</v>
+        <v>48068.181818181823</v>
       </c>
       <c r="M13" s="9">
         <f t="shared" si="0"/>
-        <v>14365.15151515152</v>
+        <v>10410.606060606064</v>
       </c>
       <c r="N13" s="9">
         <f t="shared" si="1"/>
-        <v>62577.27272727275</v>
+        <v>52516.666666666679</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
@@ -3408,26 +3410,26 @@
       </c>
       <c r="G14" s="9">
         <f>SUM(Main!$L$47:$L$53)</f>
-        <v>-20127.272727272728</v>
+        <v>-24184.090909090908</v>
       </c>
       <c r="H14" s="9">
         <v>-10000</v>
       </c>
       <c r="I14" s="9">
         <f>Main!$L$58+Main!$L$56</f>
-        <v>-2045.4545454545457</v>
+        <v>-2556.818181818182</v>
       </c>
       <c r="K14" s="9">
         <f>Main!$L$17</f>
-        <v>47454.545454545463</v>
+        <v>48068.181818181823</v>
       </c>
       <c r="M14" s="9">
         <f t="shared" si="0"/>
-        <v>14365.15151515152</v>
+        <v>10410.606060606064</v>
       </c>
       <c r="N14" s="9">
         <f t="shared" si="1"/>
-        <v>76942.424242424269</v>
+        <v>62927.272727272742</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
@@ -3443,26 +3445,26 @@
       </c>
       <c r="G15" s="9">
         <f>SUM(Main!$L$47:$L$53)</f>
-        <v>-20127.272727272728</v>
+        <v>-24184.090909090908</v>
       </c>
       <c r="H15" s="9">
         <v>-10000</v>
       </c>
       <c r="I15" s="9">
         <f>Main!$L$58+Main!$L$56</f>
-        <v>-2045.4545454545457</v>
+        <v>-2556.818181818182</v>
       </c>
       <c r="K15" s="9">
         <f>Main!$L$17</f>
-        <v>47454.545454545463</v>
+        <v>48068.181818181823</v>
       </c>
       <c r="M15" s="9">
         <f t="shared" si="0"/>
-        <v>14365.15151515152</v>
+        <v>10410.606060606064</v>
       </c>
       <c r="N15" s="9">
         <f t="shared" si="1"/>
-        <v>91307.575757575789</v>
+        <v>73337.878787878813</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
@@ -3478,26 +3480,26 @@
       </c>
       <c r="G16" s="9">
         <f>SUM(Main!$L$47:$L$53)</f>
-        <v>-20127.272727272728</v>
+        <v>-24184.090909090908</v>
       </c>
       <c r="H16" s="9">
         <v>-10000</v>
       </c>
       <c r="I16" s="9">
         <f>Main!$L$58+Main!$L$56</f>
-        <v>-2045.4545454545457</v>
+        <v>-2556.818181818182</v>
       </c>
       <c r="K16" s="9">
         <f>Main!$L$17</f>
-        <v>47454.545454545463</v>
+        <v>48068.181818181823</v>
       </c>
       <c r="M16" s="9">
         <f t="shared" si="0"/>
-        <v>14365.15151515152</v>
+        <v>10410.606060606064</v>
       </c>
       <c r="N16" s="9">
         <f t="shared" si="1"/>
-        <v>105672.72727272731</v>
+        <v>83748.484848484877</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
@@ -3513,26 +3515,26 @@
       </c>
       <c r="G17" s="9">
         <f>SUM(Main!$L$47:$L$53)</f>
-        <v>-20127.272727272728</v>
+        <v>-24184.090909090908</v>
       </c>
       <c r="H17" s="9">
         <v>-10000</v>
       </c>
       <c r="I17" s="9">
         <f>Main!$L$58+Main!$L$56</f>
-        <v>-2045.4545454545457</v>
+        <v>-2556.818181818182</v>
       </c>
       <c r="K17" s="9">
         <f>Main!$L$17</f>
-        <v>47454.545454545463</v>
+        <v>48068.181818181823</v>
       </c>
       <c r="M17" s="9">
         <f t="shared" si="0"/>
-        <v>14365.15151515152</v>
+        <v>10410.606060606064</v>
       </c>
       <c r="N17" s="9">
         <f t="shared" si="1"/>
-        <v>120037.87878787883</v>
+        <v>94159.090909090941</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
@@ -3548,26 +3550,26 @@
       </c>
       <c r="G18" s="9">
         <f>SUM(Main!$L$47:$L$53)</f>
-        <v>-20127.272727272728</v>
+        <v>-24184.090909090908</v>
       </c>
       <c r="H18" s="9">
         <v>-10000</v>
       </c>
       <c r="I18" s="9">
         <f>Main!$L$58+Main!$L$56</f>
-        <v>-2045.4545454545457</v>
+        <v>-2556.818181818182</v>
       </c>
       <c r="K18" s="9">
         <f>Main!$L$17</f>
-        <v>47454.545454545463</v>
+        <v>48068.181818181823</v>
       </c>
       <c r="M18" s="9">
         <f t="shared" si="0"/>
-        <v>14365.15151515152</v>
+        <v>10410.606060606064</v>
       </c>
       <c r="N18" s="9">
         <f t="shared" si="1"/>
-        <v>134403.03030303033</v>
+        <v>104569.696969697</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
@@ -3583,26 +3585,26 @@
       </c>
       <c r="G19" s="9">
         <f>SUM(Main!$L$47:$L$53)</f>
-        <v>-20127.272727272728</v>
+        <v>-24184.090909090908</v>
       </c>
       <c r="H19" s="9">
         <v>-10000</v>
       </c>
       <c r="I19" s="9">
         <f>Main!$L$58+Main!$L$56</f>
-        <v>-2045.4545454545457</v>
+        <v>-2556.818181818182</v>
       </c>
       <c r="K19" s="9">
         <f>Main!$L$17</f>
-        <v>47454.545454545463</v>
+        <v>48068.181818181823</v>
       </c>
       <c r="M19" s="9">
         <f t="shared" si="0"/>
-        <v>14365.15151515152</v>
+        <v>10410.606060606064</v>
       </c>
       <c r="N19" s="9">
         <f t="shared" si="1"/>
-        <v>148768.18181818185</v>
+        <v>114980.30303030307</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
@@ -3613,12 +3615,12 @@
         <v>1</v>
       </c>
       <c r="D20" s="9">
-        <f>SUM(Main!M20:M27)*12*Main!D19-D9</f>
-        <v>-58000.000000000015</v>
+        <f>SUM(Main!M20:M27)*12*Main!D19-D9+Main!M38*12</f>
+        <v>-76287.878787878784</v>
       </c>
       <c r="E20" s="9">
-        <f>SUM(Main!M31:M37)*12</f>
-        <v>-28837.878787878792</v>
+        <f>SUM(Main!M31:M38)*12</f>
+        <v>-34625.757575757576</v>
       </c>
       <c r="F20" s="9">
         <f>SUM(Main!$L$42:$L$43)</f>
@@ -3626,26 +3628,26 @@
       </c>
       <c r="G20" s="9">
         <f>SUM(Main!$L$47:$L$53)</f>
-        <v>-20127.272727272728</v>
+        <v>-24184.090909090908</v>
       </c>
       <c r="H20" s="9">
         <v>-10000</v>
       </c>
       <c r="I20" s="9">
         <f>Main!$L$58+Main!$L$56</f>
-        <v>-2045.4545454545457</v>
+        <v>-2556.818181818182</v>
       </c>
       <c r="K20" s="9">
         <f>Main!$L$17</f>
-        <v>47454.545454545463</v>
+        <v>48068.181818181823</v>
       </c>
       <c r="M20" s="9">
         <f t="shared" si="0"/>
-        <v>-72472.727272727294</v>
+        <v>-100503.03030303027</v>
       </c>
       <c r="N20" s="9">
         <f t="shared" si="1"/>
-        <v>76295.454545454559</v>
+        <v>14477.272727272793</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
@@ -3661,26 +3663,26 @@
       </c>
       <c r="G21" s="9">
         <f>SUM(Main!$M$47:$M$53)</f>
-        <v>-37554.545454545456</v>
+        <v>-45668.181818181816</v>
       </c>
       <c r="H21" s="9">
         <v>-10000</v>
       </c>
       <c r="I21" s="9">
         <f>Main!$M$58+Main!$M$56</f>
-        <v>-6136.3636363636369</v>
+        <v>-5113.636363636364</v>
       </c>
       <c r="K21" s="9">
         <f>Main!$M$17</f>
-        <v>94909.090909090926</v>
+        <v>96136.363636363647</v>
       </c>
       <c r="M21" s="9">
         <f t="shared" si="0"/>
-        <v>40301.515151515167</v>
+        <v>34437.878787878799</v>
       </c>
       <c r="N21" s="9">
         <f t="shared" si="1"/>
-        <v>116596.96969696973</v>
+        <v>48915.151515151592</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
@@ -3696,26 +3698,26 @@
       </c>
       <c r="G22" s="9">
         <f>SUM(Main!$M$47:$M$53)</f>
-        <v>-37554.545454545456</v>
+        <v>-45668.181818181816</v>
       </c>
       <c r="H22" s="9">
         <v>-10000</v>
       </c>
       <c r="I22" s="9">
         <f>Main!$M$58+Main!$M$56</f>
-        <v>-6136.3636363636369</v>
+        <v>-5113.636363636364</v>
       </c>
       <c r="K22" s="9">
         <f>Main!$M$17</f>
-        <v>94909.090909090926</v>
+        <v>96136.363636363647</v>
       </c>
       <c r="M22" s="9">
         <f t="shared" si="0"/>
-        <v>40301.515151515167</v>
+        <v>34437.878787878799</v>
       </c>
       <c r="N22" s="9">
         <f t="shared" si="1"/>
-        <v>156898.48484848489</v>
+        <v>83353.030303030391</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
@@ -3731,26 +3733,26 @@
       </c>
       <c r="G23" s="9">
         <f>SUM(Main!$M$47:$M$53)</f>
-        <v>-37554.545454545456</v>
+        <v>-45668.181818181816</v>
       </c>
       <c r="H23" s="9">
         <v>-10000</v>
       </c>
       <c r="I23" s="9">
         <f>Main!$M$58+Main!$M$56</f>
-        <v>-6136.3636363636369</v>
+        <v>-5113.636363636364</v>
       </c>
       <c r="K23" s="9">
         <f>Main!$M$17</f>
-        <v>94909.090909090926</v>
+        <v>96136.363636363647</v>
       </c>
       <c r="M23" s="9">
         <f t="shared" si="0"/>
-        <v>40301.515151515167</v>
+        <v>34437.878787878799</v>
       </c>
       <c r="N23" s="9">
         <f t="shared" si="1"/>
-        <v>197200.00000000006</v>
+        <v>117790.90909090919</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
@@ -3766,26 +3768,26 @@
       </c>
       <c r="G24" s="9">
         <f>SUM(Main!$M$47:$M$53)</f>
-        <v>-37554.545454545456</v>
+        <v>-45668.181818181816</v>
       </c>
       <c r="H24" s="9">
         <v>-10000</v>
       </c>
       <c r="I24" s="9">
         <f>Main!$M$58+Main!$M$56</f>
-        <v>-6136.3636363636369</v>
+        <v>-5113.636363636364</v>
       </c>
       <c r="K24" s="9">
         <f>Main!$M$17</f>
-        <v>94909.090909090926</v>
+        <v>96136.363636363647</v>
       </c>
       <c r="M24" s="9">
         <f t="shared" si="0"/>
-        <v>40301.515151515167</v>
+        <v>34437.878787878799</v>
       </c>
       <c r="N24" s="9">
         <f t="shared" si="1"/>
-        <v>237501.51515151522</v>
+        <v>152228.78787878799</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
@@ -3801,26 +3803,26 @@
       </c>
       <c r="G25" s="9">
         <f>SUM(Main!$M$47:$M$53)</f>
-        <v>-37554.545454545456</v>
+        <v>-45668.181818181816</v>
       </c>
       <c r="H25" s="9">
         <v>-10000</v>
       </c>
       <c r="I25" s="9">
         <f>Main!$M$58+Main!$M$56</f>
-        <v>-6136.3636363636369</v>
+        <v>-5113.636363636364</v>
       </c>
       <c r="K25" s="9">
         <f>Main!$M$17</f>
-        <v>94909.090909090926</v>
+        <v>96136.363636363647</v>
       </c>
       <c r="M25" s="9">
         <f t="shared" si="0"/>
-        <v>40301.515151515167</v>
+        <v>34437.878787878799</v>
       </c>
       <c r="N25" s="9">
         <f t="shared" si="1"/>
-        <v>277803.03030303039</v>
+        <v>186666.6666666668</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
@@ -3836,26 +3838,26 @@
       </c>
       <c r="G26" s="9">
         <f>SUM(Main!$M$47:$M$53)</f>
-        <v>-37554.545454545456</v>
+        <v>-45668.181818181816</v>
       </c>
       <c r="H26" s="9">
         <v>-10000</v>
       </c>
       <c r="I26" s="9">
         <f>Main!$M$58+Main!$M$56</f>
-        <v>-6136.3636363636369</v>
+        <v>-5113.636363636364</v>
       </c>
       <c r="K26" s="9">
         <f>Main!$M$17</f>
-        <v>94909.090909090926</v>
+        <v>96136.363636363647</v>
       </c>
       <c r="M26" s="9">
         <f t="shared" si="0"/>
-        <v>40301.515151515167</v>
+        <v>34437.878787878799</v>
       </c>
       <c r="N26" s="9">
         <f t="shared" si="1"/>
-        <v>318104.54545454553</v>
+        <v>221104.54545454559</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
@@ -3871,26 +3873,26 @@
       </c>
       <c r="G27" s="9">
         <f>SUM(Main!$M$47:$M$53)</f>
-        <v>-37554.545454545456</v>
+        <v>-45668.181818181816</v>
       </c>
       <c r="H27" s="9">
         <v>-10000</v>
       </c>
       <c r="I27" s="9">
         <f>Main!$M$58+Main!$M$56</f>
-        <v>-6136.3636363636369</v>
+        <v>-5113.636363636364</v>
       </c>
       <c r="K27" s="9">
         <f>Main!$M$17</f>
-        <v>94909.090909090926</v>
+        <v>96136.363636363647</v>
       </c>
       <c r="M27" s="9">
         <f t="shared" si="0"/>
-        <v>40301.515151515167</v>
+        <v>34437.878787878799</v>
       </c>
       <c r="N27" s="9">
         <f t="shared" si="1"/>
-        <v>358406.06060606067</v>
+        <v>255542.42424242437</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
@@ -3906,26 +3908,26 @@
       </c>
       <c r="G28" s="9">
         <f>SUM(Main!$M$47:$M$53)</f>
-        <v>-37554.545454545456</v>
+        <v>-45668.181818181816</v>
       </c>
       <c r="H28" s="9">
         <v>-10000</v>
       </c>
       <c r="I28" s="9">
         <f>Main!$M$58+Main!$M$56</f>
-        <v>-6136.3636363636369</v>
+        <v>-5113.636363636364</v>
       </c>
       <c r="K28" s="9">
         <f>Main!$M$17</f>
-        <v>94909.090909090926</v>
+        <v>96136.363636363647</v>
       </c>
       <c r="M28" s="9">
         <f t="shared" si="0"/>
-        <v>40301.515151515167</v>
+        <v>34437.878787878799</v>
       </c>
       <c r="N28" s="9">
         <f t="shared" si="1"/>
-        <v>398707.5757575758</v>
+        <v>289980.30303030316</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
@@ -3941,26 +3943,26 @@
       </c>
       <c r="G29" s="9">
         <f>SUM(Main!$M$47:$M$53)</f>
-        <v>-37554.545454545456</v>
+        <v>-45668.181818181816</v>
       </c>
       <c r="H29" s="9">
         <v>-10000</v>
       </c>
       <c r="I29" s="9">
         <f>Main!$M$58+Main!$M$56</f>
-        <v>-6136.3636363636369</v>
+        <v>-5113.636363636364</v>
       </c>
       <c r="K29" s="9">
         <f>Main!$M$17</f>
-        <v>94909.090909090926</v>
+        <v>96136.363636363647</v>
       </c>
       <c r="M29" s="9">
         <f t="shared" si="0"/>
-        <v>40301.515151515167</v>
+        <v>34437.878787878799</v>
       </c>
       <c r="N29" s="9">
         <f t="shared" si="1"/>
-        <v>439009.09090909094</v>
+        <v>324418.18181818194</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
@@ -3976,26 +3978,26 @@
       </c>
       <c r="G30" s="9">
         <f>SUM(Main!$M$47:$M$53)</f>
-        <v>-37554.545454545456</v>
+        <v>-45668.181818181816</v>
       </c>
       <c r="H30" s="9">
         <v>-10000</v>
       </c>
       <c r="I30" s="9">
         <f>Main!$M$58+Main!$M$56</f>
-        <v>-6136.3636363636369</v>
+        <v>-5113.636363636364</v>
       </c>
       <c r="K30" s="9">
         <f>Main!$M$17</f>
-        <v>94909.090909090926</v>
+        <v>96136.363636363647</v>
       </c>
       <c r="M30" s="9">
         <f t="shared" si="0"/>
-        <v>40301.515151515167</v>
+        <v>34437.878787878799</v>
       </c>
       <c r="N30" s="9">
         <f t="shared" si="1"/>
-        <v>479310.60606060608</v>
+        <v>358856.06060606072</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
@@ -4011,26 +4013,26 @@
       </c>
       <c r="G31" s="9">
         <f>SUM(Main!$M$47:$M$53)</f>
-        <v>-37554.545454545456</v>
+        <v>-45668.181818181816</v>
       </c>
       <c r="H31" s="9">
         <v>-10000</v>
       </c>
       <c r="I31" s="9">
         <f>Main!$M$58+Main!$M$56</f>
-        <v>-6136.3636363636369</v>
+        <v>-5113.636363636364</v>
       </c>
       <c r="K31" s="9">
         <f>Main!$M$17</f>
-        <v>94909.090909090926</v>
+        <v>96136.363636363647</v>
       </c>
       <c r="M31" s="9">
         <f t="shared" si="0"/>
-        <v>40301.515151515167</v>
+        <v>34437.878787878799</v>
       </c>
       <c r="N31" s="9">
         <f t="shared" si="1"/>
-        <v>519612.12121212122</v>
+        <v>393293.93939393951</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
@@ -4040,13 +4042,13 @@
       <c r="B32">
         <v>2</v>
       </c>
-      <c r="D32" s="17">
-        <f>SUM(Main!N20:N27)*12*Main!D19-D9-D20</f>
-        <v>-151000</v>
+      <c r="D32" s="9">
+        <f>SUM(Main!N20:N27)*12*Main!D19-D9-D20+Main!N38*12</f>
+        <v>-256287.87878787878</v>
       </c>
       <c r="E32" s="9">
-        <f>SUM(Main!N31:N37)*12</f>
-        <v>-56837.878787878792</v>
+        <f>SUM(Main!N31:N38)*12</f>
+        <v>-73413.636363636368</v>
       </c>
       <c r="F32" s="9">
         <f>SUM(Main!$M$42:$M$43)</f>
@@ -4054,26 +4056,26 @@
       </c>
       <c r="G32" s="9">
         <f>SUM(Main!$M$47:$M$53)</f>
-        <v>-37554.545454545456</v>
+        <v>-45668.181818181816</v>
       </c>
       <c r="H32" s="9">
         <v>-10000</v>
       </c>
       <c r="I32" s="9">
         <f>Main!$M$58+Main!$M$56</f>
-        <v>-6136.3636363636369</v>
+        <v>-5113.636363636364</v>
       </c>
       <c r="K32" s="9">
         <f>Main!$M$17</f>
-        <v>94909.090909090926</v>
+        <v>96136.363636363647</v>
       </c>
       <c r="M32" s="9">
         <f t="shared" si="0"/>
-        <v>-167536.36363636359</v>
+        <v>-295263.63636363635</v>
       </c>
       <c r="N32" s="9">
         <f t="shared" si="1"/>
-        <v>352075.75757575763</v>
+        <v>98030.303030303156</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
@@ -4089,26 +4091,26 @@
       </c>
       <c r="G33" s="9">
         <f>SUM(Main!$N$47:$N$53)</f>
-        <v>-75709.090909090912</v>
+        <v>-112720.45454545454</v>
       </c>
       <c r="H33" s="9">
         <v>-10000</v>
       </c>
       <c r="I33" s="9">
         <f>Main!$N$58+Main!$N$56</f>
-        <v>-16363.636363636364</v>
+        <v>-12784.09090909091</v>
       </c>
       <c r="K33" s="9">
         <f>Main!$N$17</f>
-        <v>189818.18181818185</v>
+        <v>240340.90909090912</v>
       </c>
       <c r="M33" s="9">
         <f t="shared" si="0"/>
-        <v>85912.121212121245</v>
+        <v>103003.03030303033</v>
       </c>
       <c r="N33" s="9">
         <f t="shared" si="1"/>
-        <v>437987.8787878789</v>
+        <v>201033.33333333349</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
@@ -4124,26 +4126,26 @@
       </c>
       <c r="G34" s="9">
         <f>SUM(Main!$N$47:$N$53)</f>
-        <v>-75709.090909090912</v>
+        <v>-112720.45454545454</v>
       </c>
       <c r="H34" s="9">
         <v>-10000</v>
       </c>
       <c r="I34" s="9">
         <f>Main!$N$58+Main!$N$56</f>
-        <v>-16363.636363636364</v>
+        <v>-12784.09090909091</v>
       </c>
       <c r="K34" s="9">
         <f>Main!$N$17</f>
-        <v>189818.18181818185</v>
+        <v>240340.90909090912</v>
       </c>
       <c r="M34" s="9">
         <f t="shared" si="0"/>
-        <v>85912.121212121245</v>
+        <v>103003.03030303033</v>
       </c>
       <c r="N34" s="9">
         <f t="shared" si="1"/>
-        <v>523900.00000000012</v>
+        <v>304036.36363636382</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
@@ -4159,26 +4161,26 @@
       </c>
       <c r="G35" s="9">
         <f>SUM(Main!$N$47:$N$53)</f>
-        <v>-75709.090909090912</v>
+        <v>-112720.45454545454</v>
       </c>
       <c r="H35" s="9">
         <v>-10000</v>
       </c>
       <c r="I35" s="9">
         <f>Main!$N$58+Main!$N$56</f>
-        <v>-16363.636363636364</v>
+        <v>-12784.09090909091</v>
       </c>
       <c r="K35" s="9">
         <f>Main!$N$17</f>
-        <v>189818.18181818185</v>
+        <v>240340.90909090912</v>
       </c>
       <c r="M35" s="9">
         <f t="shared" si="0"/>
-        <v>85912.121212121245</v>
+        <v>103003.03030303033</v>
       </c>
       <c r="N35" s="9">
         <f t="shared" si="1"/>
-        <v>609812.12121212133</v>
+        <v>407039.39393939415</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
@@ -4194,26 +4196,26 @@
       </c>
       <c r="G36" s="9">
         <f>SUM(Main!$N$47:$N$53)</f>
-        <v>-75709.090909090912</v>
+        <v>-112720.45454545454</v>
       </c>
       <c r="H36" s="9">
         <v>-10000</v>
       </c>
       <c r="I36" s="9">
         <f>Main!$N$58+Main!$N$56</f>
-        <v>-16363.636363636364</v>
+        <v>-12784.09090909091</v>
       </c>
       <c r="K36" s="9">
         <f>Main!$N$17</f>
-        <v>189818.18181818185</v>
+        <v>240340.90909090912</v>
       </c>
       <c r="M36" s="9">
         <f t="shared" si="0"/>
-        <v>85912.121212121245</v>
+        <v>103003.03030303033</v>
       </c>
       <c r="N36" s="9">
         <f t="shared" si="1"/>
-        <v>695724.24242424255</v>
+        <v>510042.42424242449</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
@@ -4229,26 +4231,26 @@
       </c>
       <c r="G37" s="9">
         <f>SUM(Main!$N$47:$N$53)</f>
-        <v>-75709.090909090912</v>
+        <v>-112720.45454545454</v>
       </c>
       <c r="H37" s="9">
         <v>-10000</v>
       </c>
       <c r="I37" s="9">
         <f>Main!$N$58+Main!$N$56</f>
-        <v>-16363.636363636364</v>
+        <v>-12784.09090909091</v>
       </c>
       <c r="K37" s="9">
         <f>Main!$N$17</f>
-        <v>189818.18181818185</v>
+        <v>240340.90909090912</v>
       </c>
       <c r="M37" s="9">
         <f t="shared" si="0"/>
-        <v>85912.121212121245</v>
+        <v>103003.03030303033</v>
       </c>
       <c r="N37" s="9">
         <f t="shared" si="1"/>
-        <v>781636.36363636376</v>
+        <v>613045.45454545482</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
@@ -4264,26 +4266,26 @@
       </c>
       <c r="G38" s="9">
         <f>SUM(Main!$N$47:$N$53)</f>
-        <v>-75709.090909090912</v>
+        <v>-112720.45454545454</v>
       </c>
       <c r="H38" s="9">
         <v>-10000</v>
       </c>
       <c r="I38" s="9">
         <f>Main!$N$58+Main!$N$56</f>
-        <v>-16363.636363636364</v>
+        <v>-12784.09090909091</v>
       </c>
       <c r="K38" s="9">
         <f>Main!$N$17</f>
-        <v>189818.18181818185</v>
+        <v>240340.90909090912</v>
       </c>
       <c r="M38" s="9">
         <f t="shared" si="0"/>
-        <v>85912.121212121245</v>
+        <v>103003.03030303033</v>
       </c>
       <c r="N38" s="9">
         <f t="shared" si="1"/>
-        <v>867548.48484848498</v>
+        <v>716048.4848484851</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
@@ -4299,26 +4301,26 @@
       </c>
       <c r="G39" s="9">
         <f>SUM(Main!$N$47:$N$53)</f>
-        <v>-75709.090909090912</v>
+        <v>-112720.45454545454</v>
       </c>
       <c r="H39" s="9">
         <v>-10000</v>
       </c>
       <c r="I39" s="9">
         <f>Main!$N$58+Main!$N$56</f>
-        <v>-16363.636363636364</v>
+        <v>-12784.09090909091</v>
       </c>
       <c r="K39" s="9">
         <f>Main!$N$17</f>
-        <v>189818.18181818185</v>
+        <v>240340.90909090912</v>
       </c>
       <c r="M39" s="9">
         <f t="shared" si="0"/>
-        <v>85912.121212121245</v>
+        <v>103003.03030303033</v>
       </c>
       <c r="N39" s="9">
         <f t="shared" si="1"/>
-        <v>953460.60606060619</v>
+        <v>819051.51515151537</v>
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
@@ -4334,26 +4336,26 @@
       </c>
       <c r="G40" s="9">
         <f>SUM(Main!$N$47:$N$53)</f>
-        <v>-75709.090909090912</v>
+        <v>-112720.45454545454</v>
       </c>
       <c r="H40" s="9">
         <v>-10000</v>
       </c>
       <c r="I40" s="9">
         <f>Main!$N$58+Main!$N$56</f>
-        <v>-16363.636363636364</v>
+        <v>-12784.09090909091</v>
       </c>
       <c r="K40" s="9">
         <f>Main!$N$17</f>
-        <v>189818.18181818185</v>
+        <v>240340.90909090912</v>
       </c>
       <c r="M40" s="9">
         <f t="shared" si="0"/>
-        <v>85912.121212121245</v>
+        <v>103003.03030303033</v>
       </c>
       <c r="N40" s="9">
         <f t="shared" si="1"/>
-        <v>1039372.7272727274</v>
+        <v>922054.54545454565</v>
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
@@ -4369,26 +4371,26 @@
       </c>
       <c r="G41" s="9">
         <f>SUM(Main!$N$47:$N$53)</f>
-        <v>-75709.090909090912</v>
+        <v>-112720.45454545454</v>
       </c>
       <c r="H41" s="9">
         <v>-10000</v>
       </c>
       <c r="I41" s="9">
         <f>Main!$N$58+Main!$N$56</f>
-        <v>-16363.636363636364</v>
+        <v>-12784.09090909091</v>
       </c>
       <c r="K41" s="9">
         <f>Main!$N$17</f>
-        <v>189818.18181818185</v>
+        <v>240340.90909090912</v>
       </c>
       <c r="M41" s="9">
         <f t="shared" si="0"/>
-        <v>85912.121212121245</v>
+        <v>103003.03030303033</v>
       </c>
       <c r="N41" s="9">
         <f t="shared" si="1"/>
-        <v>1125284.8484848486</v>
+        <v>1025057.5757575759</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
@@ -4404,26 +4406,26 @@
       </c>
       <c r="G42" s="9">
         <f>SUM(Main!$N$47:$N$53)</f>
-        <v>-75709.090909090912</v>
+        <v>-112720.45454545454</v>
       </c>
       <c r="H42" s="9">
         <v>-10000</v>
       </c>
       <c r="I42" s="9">
         <f>Main!$N$58+Main!$N$56</f>
-        <v>-16363.636363636364</v>
+        <v>-12784.09090909091</v>
       </c>
       <c r="K42" s="9">
         <f>Main!$N$17</f>
-        <v>189818.18181818185</v>
+        <v>240340.90909090912</v>
       </c>
       <c r="M42" s="9">
         <f t="shared" si="0"/>
-        <v>85912.121212121245</v>
+        <v>103003.03030303033</v>
       </c>
       <c r="N42" s="9">
         <f t="shared" si="1"/>
-        <v>1211196.96969697</v>
+        <v>1128060.6060606062</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
@@ -4439,26 +4441,26 @@
       </c>
       <c r="G43" s="9">
         <f>SUM(Main!$N$47:$N$53)</f>
-        <v>-75709.090909090912</v>
+        <v>-112720.45454545454</v>
       </c>
       <c r="H43" s="9">
         <v>-10000</v>
       </c>
       <c r="I43" s="9">
         <f>Main!$N$58+Main!$N$56</f>
-        <v>-16363.636363636364</v>
+        <v>-12784.09090909091</v>
       </c>
       <c r="K43" s="9">
         <f>Main!$N$17</f>
-        <v>189818.18181818185</v>
+        <v>240340.90909090912</v>
       </c>
       <c r="M43" s="9">
         <f t="shared" si="0"/>
-        <v>85912.121212121245</v>
+        <v>103003.03030303033</v>
       </c>
       <c r="N43" s="9">
         <f t="shared" si="1"/>
-        <v>1297109.0909090913</v>
+        <v>1231063.6363636365</v>
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.25">
@@ -4469,12 +4471,12 @@
         <v>3</v>
       </c>
       <c r="D44" s="9">
-        <f>SUM(Main!O20:O27)*12*Main!D19-D9-D20-D32</f>
-        <v>-116000.00000000006</v>
+        <f>SUM(Main!O20:O27)*12*Main!D19-D9-D20-D32+Main!O38*12</f>
+        <v>-148787.87878787867</v>
       </c>
       <c r="E44" s="9">
-        <f>SUM(Main!O31:O37)*12</f>
-        <v>-64837.878787878799</v>
+        <f>SUM(Main!O31:O38)*12</f>
+        <v>-87201.515151515167</v>
       </c>
       <c r="F44" s="9">
         <f>SUM(Main!$N$42:$N$43)</f>
@@ -4482,26 +4484,26 @@
       </c>
       <c r="G44" s="9">
         <f>SUM(Main!$N$47:$N$53)</f>
-        <v>-75709.090909090912</v>
+        <v>-112720.45454545454</v>
       </c>
       <c r="H44" s="9">
         <v>-10000</v>
       </c>
       <c r="I44" s="9">
         <f>Main!$N$58+Main!$N$56</f>
-        <v>-16363.636363636364</v>
+        <v>-12784.09090909091</v>
       </c>
       <c r="K44" s="9">
         <f>Main!$N$17</f>
-        <v>189818.18181818185</v>
+        <v>240340.90909090912</v>
       </c>
       <c r="M44" s="9">
         <f t="shared" si="0"/>
-        <v>-94925.757575757598</v>
+        <v>-132986.36363636347</v>
       </c>
       <c r="N44" s="9">
         <f t="shared" si="1"/>
-        <v>1202183.3333333337</v>
+        <v>1098077.2727272729</v>
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
@@ -4517,26 +4519,26 @@
       </c>
       <c r="G45" s="9">
         <f>SUM(Main!$O$47:$O$53)</f>
-        <v>-108163.63636363637</v>
+        <v>-153288.63636363635</v>
       </c>
       <c r="H45" s="9">
         <v>-10000</v>
       </c>
       <c r="I45" s="9">
         <f>Main!$O$58+Main!$O$56</f>
-        <v>-30681.81818181818</v>
+        <v>-17897.727272727276</v>
       </c>
       <c r="K45" s="9">
         <f>Main!$O$17</f>
-        <v>284727.27272727276</v>
+        <v>336477.27272727276</v>
       </c>
       <c r="M45" s="9">
         <f t="shared" si="0"/>
-        <v>134048.48484848489</v>
+        <v>153457.5757575758</v>
       </c>
       <c r="N45" s="9">
         <f t="shared" si="1"/>
-        <v>1336231.8181818186</v>
+        <v>1251534.8484848486</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
@@ -4552,26 +4554,26 @@
       </c>
       <c r="G46" s="9">
         <f>SUM(Main!$O$47:$O$53)</f>
-        <v>-108163.63636363637</v>
+        <v>-153288.63636363635</v>
       </c>
       <c r="H46" s="9">
         <v>-10000</v>
       </c>
       <c r="I46" s="9">
         <f>Main!$O$58+Main!$O$56</f>
-        <v>-30681.81818181818</v>
+        <v>-17897.727272727276</v>
       </c>
       <c r="K46" s="9">
         <f>Main!$O$17</f>
-        <v>284727.27272727276</v>
+        <v>336477.27272727276</v>
       </c>
       <c r="M46" s="9">
         <f t="shared" si="0"/>
-        <v>134048.48484848489</v>
+        <v>153457.5757575758</v>
       </c>
       <c r="N46" s="9">
         <f t="shared" si="1"/>
-        <v>1470280.3030303034</v>
+        <v>1404992.4242424243</v>
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.25">
@@ -4587,26 +4589,26 @@
       </c>
       <c r="G47" s="9">
         <f>SUM(Main!$O$47:$O$53)</f>
-        <v>-108163.63636363637</v>
+        <v>-153288.63636363635</v>
       </c>
       <c r="H47" s="9">
         <v>-10000</v>
       </c>
       <c r="I47" s="9">
         <f>Main!$O$58+Main!$O$56</f>
-        <v>-30681.81818181818</v>
+        <v>-17897.727272727276</v>
       </c>
       <c r="K47" s="9">
         <f>Main!$O$17</f>
-        <v>284727.27272727276</v>
+        <v>336477.27272727276</v>
       </c>
       <c r="M47" s="9">
         <f t="shared" si="0"/>
-        <v>134048.48484848489</v>
+        <v>153457.5757575758</v>
       </c>
       <c r="N47" s="9">
         <f t="shared" si="1"/>
-        <v>1604328.7878787883</v>
+        <v>1558450</v>
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.25">
@@ -4622,26 +4624,26 @@
       </c>
       <c r="G48" s="9">
         <f>SUM(Main!$O$47:$O$53)</f>
-        <v>-108163.63636363637</v>
+        <v>-153288.63636363635</v>
       </c>
       <c r="H48" s="9">
         <v>-10000</v>
       </c>
       <c r="I48" s="9">
         <f>Main!$O$58+Main!$O$56</f>
-        <v>-30681.81818181818</v>
+        <v>-17897.727272727276</v>
       </c>
       <c r="K48" s="9">
         <f>Main!$O$17</f>
-        <v>284727.27272727276</v>
+        <v>336477.27272727276</v>
       </c>
       <c r="M48" s="9">
         <f t="shared" si="0"/>
-        <v>134048.48484848489</v>
+        <v>153457.5757575758</v>
       </c>
       <c r="N48" s="9">
         <f t="shared" si="1"/>
-        <v>1738377.2727272732</v>
+        <v>1711907.5757575757</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
@@ -4657,26 +4659,26 @@
       </c>
       <c r="G49" s="9">
         <f>SUM(Main!$O$47:$O$53)</f>
-        <v>-108163.63636363637</v>
+        <v>-153288.63636363635</v>
       </c>
       <c r="H49" s="9">
         <v>-10000</v>
       </c>
       <c r="I49" s="9">
         <f>Main!$O$58+Main!$O$56</f>
-        <v>-30681.81818181818</v>
+        <v>-17897.727272727276</v>
       </c>
       <c r="K49" s="9">
         <f>Main!$O$17</f>
-        <v>284727.27272727276</v>
+        <v>336477.27272727276</v>
       </c>
       <c r="M49" s="9">
         <f t="shared" si="0"/>
-        <v>134048.48484848489</v>
+        <v>153457.5757575758</v>
       </c>
       <c r="N49" s="9">
         <f t="shared" si="1"/>
-        <v>1872425.757575758</v>
+        <v>1865365.1515151514</v>
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
@@ -4692,26 +4694,26 @@
       </c>
       <c r="G50" s="9">
         <f>SUM(Main!$O$47:$O$53)</f>
-        <v>-108163.63636363637</v>
+        <v>-153288.63636363635</v>
       </c>
       <c r="H50" s="9">
         <v>-10000</v>
       </c>
       <c r="I50" s="9">
         <f>Main!$O$58+Main!$O$56</f>
-        <v>-30681.81818181818</v>
+        <v>-17897.727272727276</v>
       </c>
       <c r="K50" s="9">
         <f>Main!$O$17</f>
-        <v>284727.27272727276</v>
+        <v>336477.27272727276</v>
       </c>
       <c r="M50" s="9">
         <f t="shared" si="0"/>
-        <v>134048.48484848489</v>
+        <v>153457.5757575758</v>
       </c>
       <c r="N50" s="9">
         <f t="shared" si="1"/>
-        <v>2006474.2424242429</v>
+        <v>2018822.7272727271</v>
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.25">
@@ -4727,26 +4729,26 @@
       </c>
       <c r="G51" s="9">
         <f>SUM(Main!$O$47:$O$53)</f>
-        <v>-108163.63636363637</v>
+        <v>-153288.63636363635</v>
       </c>
       <c r="H51" s="9">
         <v>-10000</v>
       </c>
       <c r="I51" s="9">
         <f>Main!$O$58+Main!$O$56</f>
-        <v>-30681.81818181818</v>
+        <v>-17897.727272727276</v>
       </c>
       <c r="K51" s="9">
         <f>Main!$O$17</f>
-        <v>284727.27272727276</v>
+        <v>336477.27272727276</v>
       </c>
       <c r="M51" s="9">
         <f t="shared" si="0"/>
-        <v>134048.48484848489</v>
+        <v>153457.5757575758</v>
       </c>
       <c r="N51" s="9">
         <f t="shared" si="1"/>
-        <v>2140522.727272728</v>
+        <v>2172280.3030303027</v>
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.25">
@@ -4762,26 +4764,26 @@
       </c>
       <c r="G52" s="9">
         <f>SUM(Main!$O$47:$O$53)</f>
-        <v>-108163.63636363637</v>
+        <v>-153288.63636363635</v>
       </c>
       <c r="H52" s="9">
         <v>-10000</v>
       </c>
       <c r="I52" s="9">
         <f>Main!$O$58+Main!$O$56</f>
-        <v>-30681.81818181818</v>
+        <v>-17897.727272727276</v>
       </c>
       <c r="K52" s="9">
         <f>Main!$O$17</f>
-        <v>284727.27272727276</v>
+        <v>336477.27272727276</v>
       </c>
       <c r="M52" s="9">
         <f t="shared" si="0"/>
-        <v>134048.48484848489</v>
+        <v>153457.5757575758</v>
       </c>
       <c r="N52" s="9">
         <f t="shared" si="1"/>
-        <v>2274571.2121212129</v>
+        <v>2325737.8787878784</v>
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.25">
@@ -4797,26 +4799,26 @@
       </c>
       <c r="G53" s="9">
         <f>SUM(Main!$O$47:$O$53)</f>
-        <v>-108163.63636363637</v>
+        <v>-153288.63636363635</v>
       </c>
       <c r="H53" s="9">
         <v>-10000</v>
       </c>
       <c r="I53" s="9">
         <f>Main!$O$58+Main!$O$56</f>
-        <v>-30681.81818181818</v>
+        <v>-17897.727272727276</v>
       </c>
       <c r="K53" s="9">
         <f>Main!$O$17</f>
-        <v>284727.27272727276</v>
+        <v>336477.27272727276</v>
       </c>
       <c r="M53" s="9">
         <f t="shared" si="0"/>
-        <v>134048.48484848489</v>
+        <v>153457.5757575758</v>
       </c>
       <c r="N53" s="9">
         <f t="shared" si="1"/>
-        <v>2408619.6969696977</v>
+        <v>2479195.4545454541</v>
       </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.25">
@@ -4832,26 +4834,26 @@
       </c>
       <c r="G54" s="9">
         <f>SUM(Main!$O$47:$O$53)</f>
-        <v>-108163.63636363637</v>
+        <v>-153288.63636363635</v>
       </c>
       <c r="H54" s="9">
         <v>-10000</v>
       </c>
       <c r="I54" s="9">
         <f>Main!$O$58+Main!$O$56</f>
-        <v>-30681.81818181818</v>
+        <v>-17897.727272727276</v>
       </c>
       <c r="K54" s="9">
         <f>Main!$O$17</f>
-        <v>284727.27272727276</v>
+        <v>336477.27272727276</v>
       </c>
       <c r="M54" s="9">
         <f t="shared" si="0"/>
-        <v>134048.48484848489</v>
+        <v>153457.5757575758</v>
       </c>
       <c r="N54" s="9">
         <f t="shared" si="1"/>
-        <v>2542668.1818181826</v>
+        <v>2632653.0303030298</v>
       </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.25">
@@ -4867,26 +4869,26 @@
       </c>
       <c r="G55" s="9">
         <f>SUM(Main!$O$47:$O$53)</f>
-        <v>-108163.63636363637</v>
+        <v>-153288.63636363635</v>
       </c>
       <c r="H55" s="9">
         <v>-10000</v>
       </c>
       <c r="I55" s="9">
         <f>Main!$O$58+Main!$O$56</f>
-        <v>-30681.81818181818</v>
+        <v>-17897.727272727276</v>
       </c>
       <c r="K55" s="9">
         <f>Main!$O$17</f>
-        <v>284727.27272727276</v>
+        <v>336477.27272727276</v>
       </c>
       <c r="M55" s="9">
         <f t="shared" si="0"/>
-        <v>134048.48484848489</v>
+        <v>153457.5757575758</v>
       </c>
       <c r="N55" s="9">
         <f t="shared" si="1"/>
-        <v>2676716.6666666674</v>
+        <v>2786110.6060606055</v>
       </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.25">
@@ -4897,12 +4899,12 @@
         <v>4</v>
       </c>
       <c r="D56" s="9">
-        <f>SUM(Main!P20:P27)*12*Main!D19-D9-D20-D32-D44</f>
-        <v>-115999.99999999988</v>
+        <f>SUM(Main!P20:P27)*12*Main!D19-D9-D20-D32-D44+Main!P38*12</f>
+        <v>0</v>
       </c>
       <c r="E56" s="9">
-        <f>SUM(Main!P31:P37)*12</f>
-        <v>-72837.878787878799</v>
+        <f>SUM(Main!P31:P38)*12</f>
+        <v>-87201.515151515167</v>
       </c>
       <c r="F56" s="9">
         <f>SUM(Main!$O$42:$O$43)</f>
@@ -4910,26 +4912,26 @@
       </c>
       <c r="G56" s="9">
         <f>SUM(Main!$O$47:$O$53)</f>
-        <v>-108163.63636363637</v>
+        <v>-153288.63636363635</v>
       </c>
       <c r="H56" s="9">
         <v>-10000</v>
       </c>
       <c r="I56" s="9">
         <f>Main!$O$58+Main!$O$56</f>
-        <v>-30681.81818181818</v>
+        <v>-17897.727272727276</v>
       </c>
       <c r="K56" s="9">
         <f>Main!$O$17</f>
-        <v>284727.27272727276</v>
+        <v>336477.27272727276</v>
       </c>
       <c r="M56" s="9">
         <f t="shared" si="0"/>
-        <v>-54789.393939393805</v>
+        <v>66256.060606060608</v>
       </c>
       <c r="N56" s="9">
         <f t="shared" si="1"/>
-        <v>2621927.2727272734</v>
+        <v>2852366.666666666</v>
       </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.25">
@@ -4945,26 +4947,26 @@
       </c>
       <c r="G57" s="9">
         <f>SUM(Main!$P$47:$P$53)</f>
-        <v>-140618.18181818182</v>
+        <v>-153288.63636363635</v>
       </c>
       <c r="H57" s="9">
         <v>-10000</v>
       </c>
       <c r="I57" s="9">
         <f>Main!$P$58+Main!$P$56</f>
-        <v>-40909.090909090912</v>
+        <v>-17897.727272727276</v>
       </c>
       <c r="K57" s="9">
         <f>Main!$P$17</f>
-        <v>379636.36363636371</v>
+        <v>336477.27272727276</v>
       </c>
       <c r="M57" s="9">
         <f t="shared" si="0"/>
-        <v>186275.75757575763</v>
+        <v>153457.5757575758</v>
       </c>
       <c r="N57" s="9">
         <f t="shared" si="1"/>
-        <v>2808203.0303030312</v>
+        <v>3005824.2424242417</v>
       </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.25">
@@ -4980,26 +4982,26 @@
       </c>
       <c r="G58" s="9">
         <f>SUM(Main!$P$47:$P$53)</f>
-        <v>-140618.18181818182</v>
+        <v>-153288.63636363635</v>
       </c>
       <c r="H58" s="9">
         <v>-10000</v>
       </c>
       <c r="I58" s="9">
         <f>Main!$P$58+Main!$P$56</f>
-        <v>-40909.090909090912</v>
+        <v>-17897.727272727276</v>
       </c>
       <c r="K58" s="9">
         <f>Main!$P$17</f>
-        <v>379636.36363636371</v>
+        <v>336477.27272727276</v>
       </c>
       <c r="M58" s="9">
         <f t="shared" si="0"/>
-        <v>186275.75757575763</v>
+        <v>153457.5757575758</v>
       </c>
       <c r="N58" s="9">
         <f t="shared" si="1"/>
-        <v>2994478.787878789</v>
+        <v>3159281.8181818174</v>
       </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.25">
@@ -5015,26 +5017,26 @@
       </c>
       <c r="G59" s="9">
         <f>SUM(Main!$P$47:$P$53)</f>
-        <v>-140618.18181818182</v>
+        <v>-153288.63636363635</v>
       </c>
       <c r="H59" s="9">
         <v>-10000</v>
       </c>
       <c r="I59" s="9">
         <f>Main!$P$58+Main!$P$56</f>
-        <v>-40909.090909090912</v>
+        <v>-17897.727272727276</v>
       </c>
       <c r="K59" s="9">
         <f>Main!$P$17</f>
-        <v>379636.36363636371</v>
+        <v>336477.27272727276</v>
       </c>
       <c r="M59" s="9">
         <f t="shared" si="0"/>
-        <v>186275.75757575763</v>
+        <v>153457.5757575758</v>
       </c>
       <c r="N59" s="9">
         <f t="shared" si="1"/>
-        <v>3180754.5454545468</v>
+        <v>3312739.3939393931</v>
       </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.25">
@@ -5050,26 +5052,26 @@
       </c>
       <c r="G60" s="9">
         <f>SUM(Main!$P$47:$P$53)</f>
-        <v>-140618.18181818182</v>
+        <v>-153288.63636363635</v>
       </c>
       <c r="H60" s="9">
         <v>-10000</v>
       </c>
       <c r="I60" s="9">
         <f>Main!$P$58+Main!$P$56</f>
-        <v>-40909.090909090912</v>
+        <v>-17897.727272727276</v>
       </c>
       <c r="K60" s="9">
         <f>Main!$P$17</f>
-        <v>379636.36363636371</v>
+        <v>336477.27272727276</v>
       </c>
       <c r="M60" s="9">
         <f t="shared" si="0"/>
-        <v>186275.75757575763</v>
+        <v>153457.5757575758</v>
       </c>
       <c r="N60" s="9">
         <f t="shared" si="1"/>
-        <v>3367030.3030303046</v>
+        <v>3466196.9696969688</v>
       </c>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.25">
@@ -5085,26 +5087,26 @@
       </c>
       <c r="G61" s="9">
         <f>SUM(Main!$P$47:$P$53)</f>
-        <v>-140618.18181818182</v>
+        <v>-153288.63636363635</v>
       </c>
       <c r="H61" s="9">
         <v>-10000</v>
       </c>
       <c r="I61" s="9">
         <f>Main!$P$58+Main!$P$56</f>
-        <v>-40909.090909090912</v>
+        <v>-17897.727272727276</v>
       </c>
       <c r="K61" s="9">
         <f>Main!$P$17</f>
-        <v>379636.36363636371</v>
+        <v>336477.27272727276</v>
       </c>
       <c r="M61" s="9">
         <f t="shared" si="0"/>
-        <v>186275.75757575763</v>
+        <v>153457.5757575758</v>
       </c>
       <c r="N61" s="9">
         <f t="shared" si="1"/>
-        <v>3553306.0606060624</v>
+        <v>3619654.5454545445</v>
       </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.25">
@@ -5120,26 +5122,26 @@
       </c>
       <c r="G62" s="9">
         <f>SUM(Main!$P$47:$P$53)</f>
-        <v>-140618.18181818182</v>
+        <v>-153288.63636363635</v>
       </c>
       <c r="H62" s="9">
         <v>-10000</v>
       </c>
       <c r="I62" s="9">
         <f>Main!$P$58+Main!$P$56</f>
-        <v>-40909.090909090912</v>
+        <v>-17897.727272727276</v>
       </c>
       <c r="K62" s="9">
         <f>Main!$P$17</f>
-        <v>379636.36363636371</v>
+        <v>336477.27272727276</v>
       </c>
       <c r="M62" s="9">
         <f t="shared" si="0"/>
-        <v>186275.75757575763</v>
+        <v>153457.5757575758</v>
       </c>
       <c r="N62" s="9">
         <f t="shared" si="1"/>
-        <v>3739581.8181818202</v>
+        <v>3773112.1212121202</v>
       </c>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.25">
@@ -5155,26 +5157,26 @@
       </c>
       <c r="G63" s="9">
         <f>SUM(Main!$P$47:$P$53)</f>
-        <v>-140618.18181818182</v>
+        <v>-153288.63636363635</v>
       </c>
       <c r="H63" s="9">
         <v>-10000</v>
       </c>
       <c r="I63" s="9">
         <f>Main!$P$58+Main!$P$56</f>
-        <v>-40909.090909090912</v>
+        <v>-17897.727272727276</v>
       </c>
       <c r="K63" s="9">
         <f>Main!$P$17</f>
-        <v>379636.36363636371</v>
+        <v>336477.27272727276</v>
       </c>
       <c r="M63" s="9">
         <f t="shared" si="0"/>
-        <v>186275.75757575763</v>
+        <v>153457.5757575758</v>
       </c>
       <c r="N63" s="9">
         <f t="shared" si="1"/>
-        <v>3925857.575757578</v>
+        <v>3926569.6969696959</v>
       </c>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.25">
@@ -5190,26 +5192,26 @@
       </c>
       <c r="G64" s="9">
         <f>SUM(Main!$P$47:$P$53)</f>
-        <v>-140618.18181818182</v>
+        <v>-153288.63636363635</v>
       </c>
       <c r="H64" s="9">
         <v>-10000</v>
       </c>
       <c r="I64" s="9">
         <f>Main!$P$58+Main!$P$56</f>
-        <v>-40909.090909090912</v>
+        <v>-17897.727272727276</v>
       </c>
       <c r="K64" s="9">
         <f>Main!$P$17</f>
-        <v>379636.36363636371</v>
+        <v>336477.27272727276</v>
       </c>
       <c r="M64" s="9">
         <f t="shared" si="0"/>
-        <v>186275.75757575763</v>
+        <v>153457.5757575758</v>
       </c>
       <c r="N64" s="9">
         <f t="shared" si="1"/>
-        <v>4112133.3333333358</v>
+        <v>4080027.2727272715</v>
       </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.25">
@@ -5225,26 +5227,26 @@
       </c>
       <c r="G65" s="9">
         <f>SUM(Main!$P$47:$P$53)</f>
-        <v>-140618.18181818182</v>
+        <v>-153288.63636363635</v>
       </c>
       <c r="H65" s="9">
         <v>-10000</v>
       </c>
       <c r="I65" s="9">
         <f>Main!$P$58+Main!$P$56</f>
-        <v>-40909.090909090912</v>
+        <v>-17897.727272727276</v>
       </c>
       <c r="K65" s="9">
         <f>Main!$P$17</f>
-        <v>379636.36363636371</v>
+        <v>336477.27272727276</v>
       </c>
       <c r="M65" s="9">
         <f t="shared" si="0"/>
-        <v>186275.75757575763</v>
+        <v>153457.5757575758</v>
       </c>
       <c r="N65" s="9">
         <f t="shared" si="1"/>
-        <v>4298409.0909090936</v>
+        <v>4233484.8484848477</v>
       </c>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.25">
@@ -5260,26 +5262,26 @@
       </c>
       <c r="G66" s="9">
         <f>SUM(Main!$P$47:$P$53)</f>
-        <v>-140618.18181818182</v>
+        <v>-153288.63636363635</v>
       </c>
       <c r="H66" s="9">
         <v>-10000</v>
       </c>
       <c r="I66" s="9">
         <f>Main!$P$58+Main!$P$56</f>
-        <v>-40909.090909090912</v>
+        <v>-17897.727272727276</v>
       </c>
       <c r="K66" s="9">
         <f>Main!$P$17</f>
-        <v>379636.36363636371</v>
+        <v>336477.27272727276</v>
       </c>
       <c r="M66" s="9">
         <f t="shared" si="0"/>
-        <v>186275.75757575763</v>
+        <v>153457.5757575758</v>
       </c>
       <c r="N66" s="9">
         <f t="shared" si="1"/>
-        <v>4484684.8484848514</v>
+        <v>4386942.4242424238</v>
       </c>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.25">
@@ -5295,26 +5297,26 @@
       </c>
       <c r="G67" s="9">
         <f>SUM(Main!$P$47:$P$53)</f>
-        <v>-140618.18181818182</v>
+        <v>-153288.63636363635</v>
       </c>
       <c r="H67" s="9">
         <v>-10000</v>
       </c>
       <c r="I67" s="9">
         <f>Main!$P$58+Main!$P$56</f>
-        <v>-40909.090909090912</v>
+        <v>-17897.727272727276</v>
       </c>
       <c r="K67" s="9">
         <f>Main!$P$17</f>
-        <v>379636.36363636371</v>
+        <v>336477.27272727276</v>
       </c>
       <c r="M67" s="9">
         <f t="shared" si="0"/>
-        <v>186275.75757575763</v>
+        <v>153457.5757575758</v>
       </c>
       <c r="N67" s="9">
         <f t="shared" si="1"/>
-        <v>4670960.6060606092</v>
+        <v>4540400</v>
       </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.25">
@@ -5330,26 +5332,26 @@
       </c>
       <c r="G68" s="9">
         <f>SUM(Main!$P$47:$P$53)</f>
-        <v>-140618.18181818182</v>
+        <v>-153288.63636363635</v>
       </c>
       <c r="H68" s="9">
         <v>-10000</v>
       </c>
       <c r="I68" s="9">
         <f>Main!$P$58+Main!$P$56</f>
-        <v>-40909.090909090912</v>
+        <v>-17897.727272727276</v>
       </c>
       <c r="K68" s="9">
         <f>Main!$P$17</f>
-        <v>379636.36363636371</v>
+        <v>336477.27272727276</v>
       </c>
       <c r="M68" s="9">
         <f t="shared" si="0"/>
-        <v>186275.75757575763</v>
+        <v>153457.5757575758</v>
       </c>
       <c r="N68" s="9">
         <f t="shared" si="1"/>
-        <v>4857236.363636367</v>
+        <v>4693857.5757575762</v>
       </c>
     </row>
   </sheetData>
@@ -5372,14 +5374,14 @@
   <sheetData>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>65</v>
-      </c>
-      <c r="B10" s="22">
+        <v>63</v>
+      </c>
+      <c r="B10" s="21">
         <f>Main!B1</f>
         <v>132</v>
       </c>
       <c r="D10" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E10" s="6">
         <v>10</v>
@@ -5395,39 +5397,39 @@
       <c r="A11" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="22">
+      <c r="B11" s="21">
         <f>Main!D8</f>
         <v>150</v>
       </c>
       <c r="D11" t="s">
-        <v>68</v>
-      </c>
-      <c r="E11" s="23">
+        <v>66</v>
+      </c>
+      <c r="E11" s="22">
         <f>E10*30*$B$11/$B$10*$B$13+$B$12</f>
         <v>320.4545454545455</v>
       </c>
-      <c r="F11" s="23">
+      <c r="F11" s="22">
         <f>F10*30*$B$11/$B$10*$B$13+$B$12</f>
         <v>405.68181818181819</v>
       </c>
-      <c r="G11" s="23">
+      <c r="G11" s="22">
         <f>G10*30*$B$11/$B$10*$B$13+$B$12</f>
         <v>490.90909090909093</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>63</v>
-      </c>
-      <c r="B12" s="24">
+        <v>61</v>
+      </c>
+      <c r="B12" s="23">
         <v>150</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>64</v>
-      </c>
-      <c r="B13" s="25">
+        <v>62</v>
+      </c>
+      <c r="B13" s="24">
         <v>0.5</v>
       </c>
     </row>

--- a/data/Delivery.xlsx
+++ b/data/Delivery.xlsx
@@ -112,9 +112,6 @@
     <t>POS Devices</t>
   </si>
   <si>
-    <t>Mobile Phones</t>
-  </si>
-  <si>
     <t>Server Rent</t>
   </si>
   <si>
@@ -227,6 +224,9 @@
   </si>
   <si>
     <t>Salary + Bonus</t>
+  </si>
+  <si>
+    <t>Mobile Phones, uniforms &amp; helmets</t>
   </si>
 </sst>
 </file>
@@ -690,184 +690,184 @@
                 <c:formatCode>_("$"* #,##0_);_("$"* \(#,##0\);_("$"* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="60"/>
                 <c:pt idx="0">
-                  <c:v>10874.242424242424</c:v>
+                  <c:v>3374.242424242424</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>21284.848484848488</c:v>
+                  <c:v>13784.848484848488</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>31695.454545454551</c:v>
+                  <c:v>24195.454545454551</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>42106.060606060615</c:v>
+                  <c:v>34606.060606060615</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>52516.666666666679</c:v>
+                  <c:v>45016.666666666679</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>62927.272727272742</c:v>
+                  <c:v>55427.272727272742</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>73337.878787878813</c:v>
+                  <c:v>65837.878787878813</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>83748.484848484877</c:v>
+                  <c:v>76248.484848484877</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>94159.090909090941</c:v>
+                  <c:v>86659.090909090941</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>104569.696969697</c:v>
+                  <c:v>97069.696969697005</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>114980.30303030307</c:v>
+                  <c:v>107480.30303030307</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>14477.272727272793</c:v>
+                  <c:v>-522.72727272720658</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>48915.151515151592</c:v>
+                  <c:v>33915.151515151592</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>83353.030303030391</c:v>
+                  <c:v>68353.030303030391</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>117790.90909090919</c:v>
+                  <c:v>102790.90909090919</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>152228.78787878799</c:v>
+                  <c:v>137228.78787878799</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>186666.6666666668</c:v>
+                  <c:v>171666.6666666668</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>221104.54545454559</c:v>
+                  <c:v>206104.54545454559</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>255542.42424242437</c:v>
+                  <c:v>240542.42424242437</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>289980.30303030316</c:v>
+                  <c:v>274980.30303030316</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>324418.18181818194</c:v>
+                  <c:v>309418.18181818194</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>358856.06060606072</c:v>
+                  <c:v>343856.06060606072</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>393293.93939393951</c:v>
+                  <c:v>378293.93939393951</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>98030.303030303156</c:v>
+                  <c:v>60530.303030303156</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>201033.33333333349</c:v>
+                  <c:v>163533.33333333349</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>304036.36363636382</c:v>
+                  <c:v>266536.36363636382</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>407039.39393939415</c:v>
+                  <c:v>369539.39393939415</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>510042.42424242449</c:v>
+                  <c:v>472542.42424242449</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>613045.45454545482</c:v>
+                  <c:v>575545.45454545482</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>716048.4848484851</c:v>
+                  <c:v>678548.4848484851</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>819051.51515151537</c:v>
+                  <c:v>781551.51515151537</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>922054.54545454565</c:v>
+                  <c:v>884554.54545454565</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>1025057.5757575759</c:v>
+                  <c:v>987557.57575757592</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>1128060.6060606062</c:v>
+                  <c:v>1090560.6060606062</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>1231063.6363636365</c:v>
+                  <c:v>1193563.6363636365</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>1098077.2727272729</c:v>
+                  <c:v>1045577.2727272729</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>1251534.8484848486</c:v>
+                  <c:v>1199034.8484848486</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>1404992.4242424243</c:v>
+                  <c:v>1352492.4242424243</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>1558450</c:v>
+                  <c:v>1505950</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>1711907.5757575757</c:v>
+                  <c:v>1659407.5757575757</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>1865365.1515151514</c:v>
+                  <c:v>1812865.1515151514</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>2018822.7272727271</c:v>
+                  <c:v>1966322.7272727271</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>2172280.3030303027</c:v>
+                  <c:v>2119780.3030303027</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>2325737.8787878784</c:v>
+                  <c:v>2273237.8787878784</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>2479195.4545454541</c:v>
+                  <c:v>2426695.4545454541</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>2632653.0303030298</c:v>
+                  <c:v>2580153.0303030298</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>2786110.6060606055</c:v>
+                  <c:v>2733610.6060606055</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>2852366.666666666</c:v>
+                  <c:v>2799866.666666666</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>3005824.2424242417</c:v>
+                  <c:v>2953324.2424242417</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>3159281.8181818174</c:v>
+                  <c:v>3106781.8181818174</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>3312739.3939393931</c:v>
+                  <c:v>3260239.3939393931</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>3466196.9696969688</c:v>
+                  <c:v>3413696.9696969688</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>3619654.5454545445</c:v>
+                  <c:v>3567154.5454545445</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>3773112.1212121202</c:v>
+                  <c:v>3720612.1212121202</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>3926569.6969696959</c:v>
+                  <c:v>3874069.6969696959</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>4080027.2727272715</c:v>
+                  <c:v>4027527.2727272715</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>4233484.8484848477</c:v>
+                  <c:v>4180984.8484848472</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>4386942.4242424238</c:v>
+                  <c:v>4334442.4242424229</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>4540400</c:v>
+                  <c:v>4487899.9999999991</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>4693857.5757575762</c:v>
+                  <c:v>4641357.5757575752</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1944,7 +1944,7 @@
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B1" s="14">
         <v>132</v>
@@ -1952,18 +1952,18 @@
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="K2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L2" t="s">
+        <v>41</v>
+      </c>
+      <c r="N2" t="s">
         <v>42</v>
-      </c>
-      <c r="N2" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="K3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="L3" s="16">
         <v>1</v>
@@ -1983,7 +1983,7 @@
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="K4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L4" s="7">
         <v>1</v>
@@ -2047,7 +2047,7 @@
         <v>150</v>
       </c>
       <c r="K8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L8" s="3">
         <v>2</v>
@@ -2099,7 +2099,7 @@
         <v>15</v>
       </c>
       <c r="K10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L10" s="3">
         <v>2</v>
@@ -2119,7 +2119,7 @@
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="K11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L11" s="3">
         <v>1</v>
@@ -2167,7 +2167,7 @@
         <v>1</v>
       </c>
       <c r="M13" s="3">
-        <f t="shared" ref="M13:P13" si="0">M3</f>
+        <f t="shared" ref="M13" si="0">M3</f>
         <v>1</v>
       </c>
       <c r="N13" s="3">
@@ -2182,7 +2182,7 @@
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="K15" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L15" s="25">
         <v>0</v>
@@ -2203,7 +2203,7 @@
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C16"/>
       <c r="K16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="L16" s="20">
         <f>L7*$D$10*30</f>
@@ -2254,7 +2254,7 @@
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L18" s="9"/>
       <c r="M18" s="9"/>
@@ -2444,35 +2444,36 @@
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>28</v>
+        <v>66</v>
       </c>
       <c r="D26" s="8">
-        <v>150</v>
+        <f>150+150</f>
+        <v>300</v>
       </c>
       <c r="L26" s="9">
         <f>-$D$26*L7/$D$19/12</f>
-        <v>-125</v>
+        <v>-250</v>
       </c>
       <c r="M26" s="9">
         <f>-$D$26*M7/$D$19/12</f>
-        <v>-250</v>
+        <v>-500</v>
       </c>
       <c r="N26" s="9">
         <f>-$D$26*N7/$D$19/12</f>
-        <v>-625</v>
+        <v>-1250</v>
       </c>
       <c r="O26" s="9">
         <f>-$D$26*O7/$D$19/12</f>
-        <v>-875</v>
+        <v>-1750</v>
       </c>
       <c r="P26" s="9">
         <f>-$D$26*P7/$D$19/12</f>
-        <v>-875</v>
+        <v>-1750</v>
       </c>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C27" s="14">
         <v>500000</v>
@@ -2505,16 +2506,16 @@
     <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="D28" s="10">
         <f>SUM(D21:D25)+D27+D20*C20+C20*D26</f>
-        <v>113287.87878787878</v>
+        <v>120787.87878787878</v>
       </c>
       <c r="E28" s="10">
         <f>D28-SUM(L31:L37)*12</f>
-        <v>139125.75757575757</v>
+        <v>146625.75757575757</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.25">
@@ -2581,7 +2582,7 @@
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C33"/>
       <c r="D33" s="5">
@@ -2613,13 +2614,13 @@
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D34" s="5">
         <v>500</v>
       </c>
       <c r="E34" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L34" s="9">
         <f>-$D$34/12</f>
@@ -2644,7 +2645,7 @@
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C35" s="14">
         <v>5000</v>
@@ -2741,7 +2742,7 @@
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L38" s="9">
         <f>-L15/$B$1/12</f>
@@ -2775,19 +2776,19 @@
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D41" s="10"/>
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D42" s="8">
         <v>500</v>
       </c>
       <c r="E42" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="L42" s="9">
         <f>-$D$42*L3</f>
@@ -2860,7 +2861,7 @@
         <v>0.5</v>
       </c>
       <c r="F47" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="L47" s="9">
         <f t="shared" ref="L47:P53" si="7">-$D47*L7</f>
@@ -2972,7 +2973,7 @@
     </row>
     <row r="51" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C51"/>
       <c r="D51" s="8">
@@ -3059,7 +3060,7 @@
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D56" s="19">
         <v>0.1</v>
@@ -3103,27 +3104,27 @@
     </row>
     <row r="62" spans="1:16" x14ac:dyDescent="0.25">
       <c r="K62" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="L62" s="10">
         <f>SUM(L17:L60)</f>
-        <v>16369.318181818182</v>
+        <v>16244.318181818182</v>
       </c>
       <c r="M62" s="10">
         <f>SUM(M17:M60)</f>
-        <v>38455.934343434375</v>
+        <v>38205.934343434375</v>
       </c>
       <c r="N62" s="10">
         <f>SUM(N17:N60)</f>
-        <v>99580.429292929344</v>
+        <v>98955.429292929344</v>
       </c>
       <c r="O62" s="10">
         <f>SUM(O17:O60)</f>
-        <v>146469.31818181815</v>
+        <v>145594.31818181815</v>
       </c>
       <c r="P62" s="10">
         <f>SUM(P17:P60)</f>
-        <v>146469.31818181815</v>
+        <v>145594.31818181815</v>
       </c>
     </row>
     <row r="64" spans="1:16" x14ac:dyDescent="0.25">
@@ -3192,42 +3193,42 @@
   <sheetData>
     <row r="8" spans="1:14" s="17" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="18" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D8" s="18" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E8" s="18" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F8" s="18" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G8" s="18" t="s">
         <v>22</v>
       </c>
       <c r="H8" s="18" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I8" s="18" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J8" s="18"/>
       <c r="K8" s="18" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L8" s="18"/>
       <c r="M8" s="18" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N8" s="18" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
@@ -3242,7 +3243,7 @@
       </c>
       <c r="D9" s="9">
         <f>SUM(Main!L20:L27)*12*Main!D19</f>
-        <v>-113287.87878787878</v>
+        <v>-120787.87878787878</v>
       </c>
       <c r="E9" s="9">
         <f>SUM(Main!L31:L38)*12</f>
@@ -3250,11 +3251,11 @@
       </c>
       <c r="M9" s="9">
         <f>SUM(C9:K9)</f>
-        <v>10874.242424242424</v>
+        <v>3374.242424242424</v>
       </c>
       <c r="N9" s="9">
         <f>M9</f>
-        <v>10874.242424242424</v>
+        <v>3374.242424242424</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
@@ -3289,7 +3290,7 @@
       </c>
       <c r="N10" s="9">
         <f>N9+M10</f>
-        <v>21284.848484848488</v>
+        <v>13784.848484848488</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
@@ -3324,7 +3325,7 @@
       </c>
       <c r="N11" s="9">
         <f t="shared" ref="N11:N68" si="1">N10+M11</f>
-        <v>31695.454545454551</v>
+        <v>24195.454545454551</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
@@ -3359,7 +3360,7 @@
       </c>
       <c r="N12" s="9">
         <f t="shared" si="1"/>
-        <v>42106.060606060615</v>
+        <v>34606.060606060615</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
@@ -3394,7 +3395,7 @@
       </c>
       <c r="N13" s="9">
         <f t="shared" si="1"/>
-        <v>52516.666666666679</v>
+        <v>45016.666666666679</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
@@ -3429,7 +3430,7 @@
       </c>
       <c r="N14" s="9">
         <f t="shared" si="1"/>
-        <v>62927.272727272742</v>
+        <v>55427.272727272742</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
@@ -3464,7 +3465,7 @@
       </c>
       <c r="N15" s="9">
         <f t="shared" si="1"/>
-        <v>73337.878787878813</v>
+        <v>65837.878787878813</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
@@ -3499,7 +3500,7 @@
       </c>
       <c r="N16" s="9">
         <f t="shared" si="1"/>
-        <v>83748.484848484877</v>
+        <v>76248.484848484877</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
@@ -3534,7 +3535,7 @@
       </c>
       <c r="N17" s="9">
         <f t="shared" si="1"/>
-        <v>94159.090909090941</v>
+        <v>86659.090909090941</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
@@ -3569,7 +3570,7 @@
       </c>
       <c r="N18" s="9">
         <f t="shared" si="1"/>
-        <v>104569.696969697</v>
+        <v>97069.696969697005</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
@@ -3604,7 +3605,7 @@
       </c>
       <c r="N19" s="9">
         <f t="shared" si="1"/>
-        <v>114980.30303030307</v>
+        <v>107480.30303030307</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
@@ -3616,7 +3617,7 @@
       </c>
       <c r="D20" s="9">
         <f>SUM(Main!M20:M27)*12*Main!D19-D9+Main!M38*12</f>
-        <v>-76287.878787878784</v>
+        <v>-83787.878787878784</v>
       </c>
       <c r="E20" s="9">
         <f>SUM(Main!M31:M38)*12</f>
@@ -3643,11 +3644,11 @@
       </c>
       <c r="M20" s="9">
         <f t="shared" si="0"/>
-        <v>-100503.03030303027</v>
+        <v>-108003.03030303027</v>
       </c>
       <c r="N20" s="9">
         <f t="shared" si="1"/>
-        <v>14477.272727272793</v>
+        <v>-522.72727272720658</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
@@ -3682,7 +3683,7 @@
       </c>
       <c r="N21" s="9">
         <f t="shared" si="1"/>
-        <v>48915.151515151592</v>
+        <v>33915.151515151592</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
@@ -3717,7 +3718,7 @@
       </c>
       <c r="N22" s="9">
         <f t="shared" si="1"/>
-        <v>83353.030303030391</v>
+        <v>68353.030303030391</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
@@ -3752,7 +3753,7 @@
       </c>
       <c r="N23" s="9">
         <f t="shared" si="1"/>
-        <v>117790.90909090919</v>
+        <v>102790.90909090919</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
@@ -3787,7 +3788,7 @@
       </c>
       <c r="N24" s="9">
         <f t="shared" si="1"/>
-        <v>152228.78787878799</v>
+        <v>137228.78787878799</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
@@ -3822,7 +3823,7 @@
       </c>
       <c r="N25" s="9">
         <f t="shared" si="1"/>
-        <v>186666.6666666668</v>
+        <v>171666.6666666668</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
@@ -3857,7 +3858,7 @@
       </c>
       <c r="N26" s="9">
         <f t="shared" si="1"/>
-        <v>221104.54545454559</v>
+        <v>206104.54545454559</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
@@ -3892,7 +3893,7 @@
       </c>
       <c r="N27" s="9">
         <f t="shared" si="1"/>
-        <v>255542.42424242437</v>
+        <v>240542.42424242437</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
@@ -3927,7 +3928,7 @@
       </c>
       <c r="N28" s="9">
         <f t="shared" si="1"/>
-        <v>289980.30303030316</v>
+        <v>274980.30303030316</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
@@ -3962,7 +3963,7 @@
       </c>
       <c r="N29" s="9">
         <f t="shared" si="1"/>
-        <v>324418.18181818194</v>
+        <v>309418.18181818194</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
@@ -3997,7 +3998,7 @@
       </c>
       <c r="N30" s="9">
         <f t="shared" si="1"/>
-        <v>358856.06060606072</v>
+        <v>343856.06060606072</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
@@ -4032,7 +4033,7 @@
       </c>
       <c r="N31" s="9">
         <f t="shared" si="1"/>
-        <v>393293.93939393951</v>
+        <v>378293.93939393951</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
@@ -4044,7 +4045,7 @@
       </c>
       <c r="D32" s="9">
         <f>SUM(Main!N20:N27)*12*Main!D19-D9-D20+Main!N38*12</f>
-        <v>-256287.87878787878</v>
+        <v>-278787.87878787878</v>
       </c>
       <c r="E32" s="9">
         <f>SUM(Main!N31:N38)*12</f>
@@ -4071,11 +4072,11 @@
       </c>
       <c r="M32" s="9">
         <f t="shared" si="0"/>
-        <v>-295263.63636363635</v>
+        <v>-317763.63636363635</v>
       </c>
       <c r="N32" s="9">
         <f t="shared" si="1"/>
-        <v>98030.303030303156</v>
+        <v>60530.303030303156</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
@@ -4110,7 +4111,7 @@
       </c>
       <c r="N33" s="9">
         <f t="shared" si="1"/>
-        <v>201033.33333333349</v>
+        <v>163533.33333333349</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
@@ -4145,7 +4146,7 @@
       </c>
       <c r="N34" s="9">
         <f t="shared" si="1"/>
-        <v>304036.36363636382</v>
+        <v>266536.36363636382</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
@@ -4180,7 +4181,7 @@
       </c>
       <c r="N35" s="9">
         <f t="shared" si="1"/>
-        <v>407039.39393939415</v>
+        <v>369539.39393939415</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
@@ -4215,7 +4216,7 @@
       </c>
       <c r="N36" s="9">
         <f t="shared" si="1"/>
-        <v>510042.42424242449</v>
+        <v>472542.42424242449</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
@@ -4250,7 +4251,7 @@
       </c>
       <c r="N37" s="9">
         <f t="shared" si="1"/>
-        <v>613045.45454545482</v>
+        <v>575545.45454545482</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
@@ -4285,7 +4286,7 @@
       </c>
       <c r="N38" s="9">
         <f t="shared" si="1"/>
-        <v>716048.4848484851</v>
+        <v>678548.4848484851</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
@@ -4320,7 +4321,7 @@
       </c>
       <c r="N39" s="9">
         <f t="shared" si="1"/>
-        <v>819051.51515151537</v>
+        <v>781551.51515151537</v>
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
@@ -4355,7 +4356,7 @@
       </c>
       <c r="N40" s="9">
         <f t="shared" si="1"/>
-        <v>922054.54545454565</v>
+        <v>884554.54545454565</v>
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
@@ -4390,7 +4391,7 @@
       </c>
       <c r="N41" s="9">
         <f t="shared" si="1"/>
-        <v>1025057.5757575759</v>
+        <v>987557.57575757592</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
@@ -4425,7 +4426,7 @@
       </c>
       <c r="N42" s="9">
         <f t="shared" si="1"/>
-        <v>1128060.6060606062</v>
+        <v>1090560.6060606062</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
@@ -4460,7 +4461,7 @@
       </c>
       <c r="N43" s="9">
         <f t="shared" si="1"/>
-        <v>1231063.6363636365</v>
+        <v>1193563.6363636365</v>
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.25">
@@ -4472,7 +4473,7 @@
       </c>
       <c r="D44" s="9">
         <f>SUM(Main!O20:O27)*12*Main!D19-D9-D20-D32+Main!O38*12</f>
-        <v>-148787.87878787867</v>
+        <v>-163787.87878787867</v>
       </c>
       <c r="E44" s="9">
         <f>SUM(Main!O31:O38)*12</f>
@@ -4499,11 +4500,11 @@
       </c>
       <c r="M44" s="9">
         <f t="shared" si="0"/>
-        <v>-132986.36363636347</v>
+        <v>-147986.36363636347</v>
       </c>
       <c r="N44" s="9">
         <f t="shared" si="1"/>
-        <v>1098077.2727272729</v>
+        <v>1045577.2727272729</v>
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
@@ -4538,7 +4539,7 @@
       </c>
       <c r="N45" s="9">
         <f t="shared" si="1"/>
-        <v>1251534.8484848486</v>
+        <v>1199034.8484848486</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
@@ -4573,7 +4574,7 @@
       </c>
       <c r="N46" s="9">
         <f t="shared" si="1"/>
-        <v>1404992.4242424243</v>
+        <v>1352492.4242424243</v>
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.25">
@@ -4608,7 +4609,7 @@
       </c>
       <c r="N47" s="9">
         <f t="shared" si="1"/>
-        <v>1558450</v>
+        <v>1505950</v>
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.25">
@@ -4643,7 +4644,7 @@
       </c>
       <c r="N48" s="9">
         <f t="shared" si="1"/>
-        <v>1711907.5757575757</v>
+        <v>1659407.5757575757</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
@@ -4678,7 +4679,7 @@
       </c>
       <c r="N49" s="9">
         <f t="shared" si="1"/>
-        <v>1865365.1515151514</v>
+        <v>1812865.1515151514</v>
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
@@ -4713,7 +4714,7 @@
       </c>
       <c r="N50" s="9">
         <f t="shared" si="1"/>
-        <v>2018822.7272727271</v>
+        <v>1966322.7272727271</v>
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.25">
@@ -4748,7 +4749,7 @@
       </c>
       <c r="N51" s="9">
         <f t="shared" si="1"/>
-        <v>2172280.3030303027</v>
+        <v>2119780.3030303027</v>
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.25">
@@ -4783,7 +4784,7 @@
       </c>
       <c r="N52" s="9">
         <f t="shared" si="1"/>
-        <v>2325737.8787878784</v>
+        <v>2273237.8787878784</v>
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.25">
@@ -4818,7 +4819,7 @@
       </c>
       <c r="N53" s="9">
         <f t="shared" si="1"/>
-        <v>2479195.4545454541</v>
+        <v>2426695.4545454541</v>
       </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.25">
@@ -4853,7 +4854,7 @@
       </c>
       <c r="N54" s="9">
         <f t="shared" si="1"/>
-        <v>2632653.0303030298</v>
+        <v>2580153.0303030298</v>
       </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.25">
@@ -4888,7 +4889,7 @@
       </c>
       <c r="N55" s="9">
         <f t="shared" si="1"/>
-        <v>2786110.6060606055</v>
+        <v>2733610.6060606055</v>
       </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.25">
@@ -4931,7 +4932,7 @@
       </c>
       <c r="N56" s="9">
         <f t="shared" si="1"/>
-        <v>2852366.666666666</v>
+        <v>2799866.666666666</v>
       </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.25">
@@ -4966,7 +4967,7 @@
       </c>
       <c r="N57" s="9">
         <f t="shared" si="1"/>
-        <v>3005824.2424242417</v>
+        <v>2953324.2424242417</v>
       </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.25">
@@ -5001,7 +5002,7 @@
       </c>
       <c r="N58" s="9">
         <f t="shared" si="1"/>
-        <v>3159281.8181818174</v>
+        <v>3106781.8181818174</v>
       </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.25">
@@ -5036,7 +5037,7 @@
       </c>
       <c r="N59" s="9">
         <f t="shared" si="1"/>
-        <v>3312739.3939393931</v>
+        <v>3260239.3939393931</v>
       </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.25">
@@ -5071,7 +5072,7 @@
       </c>
       <c r="N60" s="9">
         <f t="shared" si="1"/>
-        <v>3466196.9696969688</v>
+        <v>3413696.9696969688</v>
       </c>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.25">
@@ -5106,7 +5107,7 @@
       </c>
       <c r="N61" s="9">
         <f t="shared" si="1"/>
-        <v>3619654.5454545445</v>
+        <v>3567154.5454545445</v>
       </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.25">
@@ -5141,7 +5142,7 @@
       </c>
       <c r="N62" s="9">
         <f t="shared" si="1"/>
-        <v>3773112.1212121202</v>
+        <v>3720612.1212121202</v>
       </c>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.25">
@@ -5176,7 +5177,7 @@
       </c>
       <c r="N63" s="9">
         <f t="shared" si="1"/>
-        <v>3926569.6969696959</v>
+        <v>3874069.6969696959</v>
       </c>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.25">
@@ -5211,7 +5212,7 @@
       </c>
       <c r="N64" s="9">
         <f t="shared" si="1"/>
-        <v>4080027.2727272715</v>
+        <v>4027527.2727272715</v>
       </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.25">
@@ -5246,7 +5247,7 @@
       </c>
       <c r="N65" s="9">
         <f t="shared" si="1"/>
-        <v>4233484.8484848477</v>
+        <v>4180984.8484848472</v>
       </c>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.25">
@@ -5281,7 +5282,7 @@
       </c>
       <c r="N66" s="9">
         <f t="shared" si="1"/>
-        <v>4386942.4242424238</v>
+        <v>4334442.4242424229</v>
       </c>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.25">
@@ -5316,7 +5317,7 @@
       </c>
       <c r="N67" s="9">
         <f t="shared" si="1"/>
-        <v>4540400</v>
+        <v>4487899.9999999991</v>
       </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.25">
@@ -5351,7 +5352,7 @@
       </c>
       <c r="N68" s="9">
         <f t="shared" si="1"/>
-        <v>4693857.5757575762</v>
+        <v>4641357.5757575752</v>
       </c>
     </row>
   </sheetData>
@@ -5374,14 +5375,14 @@
   <sheetData>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B10" s="21">
         <f>Main!B1</f>
         <v>132</v>
       </c>
       <c r="D10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E10" s="6">
         <v>10</v>
@@ -5402,7 +5403,7 @@
         <v>150</v>
       </c>
       <c r="D11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E11" s="22">
         <f>E10*30*$B$11/$B$10*$B$13+$B$12</f>
@@ -5419,7 +5420,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B12" s="23">
         <v>150</v>
@@ -5427,7 +5428,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B13" s="24">
         <v>0.5</v>
